--- a/Excel/SkillTalentConfig.xlsx
+++ b/Excel/SkillTalentConfig.xlsx
@@ -440,43 +440,55 @@
     <t>每次计算伤害，削减敌人1点护甲</t>
   </si>
   <si>
+    <t>烈焰术</t>
+  </si>
+  <si>
+    <t>削减敌人50点护甲，最高3层</t>
+  </si>
+  <si>
+    <t>念力盾</t>
+  </si>
+  <si>
+    <t>冰心诀</t>
+  </si>
+  <si>
+    <t>冰封术</t>
+  </si>
+  <si>
+    <t>·霜寒</t>
+  </si>
+  <si>
+    <t>给敌人附加一个额外承受10%伤害的状态，最高3层</t>
+  </si>
+  <si>
+    <t>·魔体</t>
+  </si>
+  <si>
+    <t>增加{0}%魔法倍率</t>
+  </si>
+  <si>
+    <t>·狂潮</t>
+  </si>
+  <si>
+    <t>额外攻击一个敌人</t>
+  </si>
+  <si>
     <t>·炼狱火海</t>
   </si>
   <si>
     <t>火海的攻击范围增加一行一列</t>
   </si>
   <si>
-    <t>烈焰术</t>
-  </si>
-  <si>
-    <t>削减敌人50点护甲，最高3层</t>
-  </si>
-  <si>
-    <t>念力盾</t>
-  </si>
-  <si>
-    <t>冰心诀</t>
-  </si>
-  <si>
-    <t>冰封术</t>
-  </si>
-  <si>
-    <t>·霜寒</t>
-  </si>
-  <si>
-    <t>给敌人附加一个额外承受10%伤害的状态，最高3层</t>
-  </si>
-  <si>
-    <t>·魔体</t>
-  </si>
-  <si>
-    <t>增加{0}%魔法倍率</t>
-  </si>
-  <si>
-    <t>·狂潮</t>
-  </si>
-  <si>
-    <t>额外攻击一个敌人</t>
+    <t>·蚀魂</t>
+  </si>
+  <si>
+    <t>敌人附加一个额外承受20%伤害的状态，最高3层</t>
+  </si>
+  <si>
+    <t>·燃魂</t>
+  </si>
+  <si>
+    <t>自己附加一个额外增加5%伤害的状态，最高3层</t>
   </si>
   <si>
     <t>·蚀骨</t>
@@ -485,22 +497,10 @@
     <t>敌人附加一个额外承受10%伤害的状态，最高3层</t>
   </si>
   <si>
-    <t>·燃魂</t>
-  </si>
-  <si>
-    <t>自己附加一个额外增加5%伤害的状态，最高3层</t>
-  </si>
-  <si>
     <t>·冻结</t>
   </si>
   <si>
     <t>敌人降低20%的攻击速度</t>
-  </si>
-  <si>
-    <t>·蚀魂</t>
-  </si>
-  <si>
-    <t>敌人附加一个额外承受20%伤害的状态，最高3层</t>
   </si>
   <si>
     <t>·上古魔体</t>
@@ -1555,7 +1555,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:AD65"/>
+  <dimension ref="C1:AD68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="6" width="9" style="1"/>
@@ -1899,12 +1899,11 @@
         <v>0</v>
       </c>
       <c r="X6" s="1">
-        <v>1007</v>
+        <v>31</v>
       </c>
       <c r="Y6" s="1">
         <v>20</v>
       </c>
-      <c r="Z6" s="1"/>
       <c r="AC6" s="1">
         <v>1</v>
       </c>
@@ -2409,7 +2408,6 @@
       <c r="Y14" s="1">
         <v>5</v>
       </c>
-      <c r="Z14" s="1"/>
       <c r="AC14" s="1">
         <v>1</v>
       </c>
@@ -2496,7 +2494,7 @@
     </row>
     <row r="16" customHeight="1" spans="3:30">
       <c r="C16" s="1">
-        <v>10034</v>
+        <v>10032</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -3009,29 +3007,100 @@
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1"/>
     <row r="27" customHeight="1" spans="3:30">
-      <c r="U27" s="4"/>
+      <c r="C27" s="1">
+        <v>20011</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="4">
+        <v>2001</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="1">
+        <v>0</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1">
+        <v>0</v>
+      </c>
+      <c r="M27" s="1">
+        <v>0</v>
+      </c>
+      <c r="N27" s="1">
+        <v>0</v>
+      </c>
+      <c r="O27" s="1">
+        <v>5</v>
+      </c>
+      <c r="P27" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>0</v>
+      </c>
+      <c r="R27" s="1">
+        <v>0</v>
+      </c>
+      <c r="S27" s="1">
+        <v>0</v>
+      </c>
+      <c r="T27" s="1">
+        <v>0</v>
+      </c>
+      <c r="U27" s="4">
+        <v>0</v>
+      </c>
+      <c r="V27" s="1">
+        <v>0</v>
+      </c>
+      <c r="X27" s="1">
+        <v>32</v>
+      </c>
+      <c r="Y27" s="1">
+        <v>20</v>
+      </c>
+      <c r="AC27" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD27" s="1">
+        <v>5</v>
+      </c>
     </row>
     <row r="28" customHeight="1" spans="3:30">
       <c r="C28" s="1">
-        <v>20011</v>
+        <v>20021</v>
       </c>
       <c r="D28" s="1">
         <v>1</v>
       </c>
       <c r="E28" s="4">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="I28" s="1">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="J28" s="1">
         <v>0</v>
@@ -3049,7 +3118,7 @@
         <v>0</v>
       </c>
       <c r="O28" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P28" s="1">
         <v>0</v>
@@ -3072,13 +3141,6 @@
       <c r="V28" s="1">
         <v>0</v>
       </c>
-      <c r="X28" s="1">
-        <v>1008</v>
-      </c>
-      <c r="Y28" s="1">
-        <v>20</v>
-      </c>
-      <c r="Z28" s="1"/>
       <c r="AC28" s="1">
         <v>1</v>
       </c>
@@ -3088,25 +3150,25 @@
     </row>
     <row r="29" customHeight="1" spans="3:30">
       <c r="C29" s="1">
-        <v>20021</v>
+        <v>20031</v>
       </c>
       <c r="D29" s="1">
         <v>1</v>
       </c>
       <c r="E29" s="4">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="I29" s="1">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="J29" s="1">
         <v>0</v>
@@ -3145,6 +3207,15 @@
         <v>0</v>
       </c>
       <c r="V29" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA29" s="1">
+        <v>-1</v>
+      </c>
+      <c r="AB29" s="1">
         <v>0</v>
       </c>
       <c r="AC29" s="1">
@@ -3156,22 +3227,22 @@
     </row>
     <row r="30" customHeight="1" spans="3:30">
       <c r="C30" s="1">
-        <v>20031</v>
+        <v>20041</v>
       </c>
       <c r="D30" s="1">
         <v>1</v>
       </c>
       <c r="E30" s="4">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>59</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I30" s="1">
         <v>0</v>
@@ -3216,13 +3287,13 @@
         <v>0</v>
       </c>
       <c r="Z30" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA30" s="1">
-        <v>-1</v>
+        <v>-50</v>
       </c>
       <c r="AB30" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AC30" s="1">
         <v>1</v>
@@ -3233,28 +3304,28 @@
     </row>
     <row r="31" customHeight="1" spans="3:30">
       <c r="C31" s="1">
-        <v>20032</v>
+        <v>20051</v>
       </c>
       <c r="D31" s="1">
         <v>1</v>
       </c>
       <c r="E31" s="4">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="I31" s="1">
         <v>0</v>
       </c>
       <c r="J31" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K31" s="1">
         <v>0</v>
@@ -3263,10 +3334,10 @@
         <v>0</v>
       </c>
       <c r="M31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" s="1">
         <v>0</v>
@@ -3301,22 +3372,22 @@
     </row>
     <row r="32" customHeight="1" spans="3:30">
       <c r="C32" s="1">
-        <v>20041</v>
+        <v>20061</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
       </c>
       <c r="E32" s="4">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="I32" s="1">
         <v>0</v>
@@ -3337,7 +3408,7 @@
         <v>0</v>
       </c>
       <c r="O32" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P32" s="1">
         <v>0</v>
@@ -3359,15 +3430,6 @@
       </c>
       <c r="V32" s="1">
         <v>0</v>
-      </c>
-      <c r="Z32" s="1">
-        <v>2</v>
-      </c>
-      <c r="AA32" s="1">
-        <v>-50</v>
-      </c>
-      <c r="AB32" s="1">
-        <v>5</v>
       </c>
       <c r="AC32" s="1">
         <v>1</v>
@@ -3378,28 +3440,28 @@
     </row>
     <row r="33" customHeight="1" spans="3:30">
       <c r="C33" s="1">
-        <v>20051</v>
+        <v>20071</v>
       </c>
       <c r="D33" s="1">
         <v>1</v>
       </c>
       <c r="E33" s="4">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>92</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="I33" s="1">
         <v>0</v>
       </c>
       <c r="J33" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
         <v>0</v>
@@ -3437,6 +3499,13 @@
       <c r="V33" s="1">
         <v>0</v>
       </c>
+      <c r="Z33" s="1">
+        <v>6</v>
+      </c>
+      <c r="AA33" s="4">
+        <v>10</v>
+      </c>
+      <c r="AB33" s="4"/>
       <c r="AC33" s="1">
         <v>1</v>
       </c>
@@ -3445,85 +3514,21 @@
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:30">
-      <c r="C34" s="1">
-        <v>20061</v>
-      </c>
-      <c r="D34" s="1">
-        <v>1</v>
-      </c>
-      <c r="E34" s="4">
-        <v>2006</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I34" s="1">
-        <v>0</v>
-      </c>
-      <c r="J34" s="1">
-        <v>0</v>
-      </c>
-      <c r="K34" s="1">
-        <v>0</v>
-      </c>
-      <c r="L34" s="1">
-        <v>0</v>
-      </c>
-      <c r="M34" s="1">
-        <v>0</v>
-      </c>
-      <c r="N34" s="1">
-        <v>0</v>
-      </c>
-      <c r="O34" s="1">
-        <v>5</v>
-      </c>
-      <c r="P34" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="1">
-        <v>0</v>
-      </c>
-      <c r="R34" s="1">
-        <v>0</v>
-      </c>
-      <c r="S34" s="1">
-        <v>0</v>
-      </c>
-      <c r="T34" s="1">
-        <v>0</v>
-      </c>
-      <c r="U34" s="4">
-        <v>0</v>
-      </c>
-      <c r="V34" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC34" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD34" s="1">
-        <v>5</v>
-      </c>
+      <c r="F34" s="4"/>
+      <c r="U34" s="4"/>
     </row>
     <row r="35" customHeight="1" spans="3:30">
       <c r="C35" s="1">
-        <v>20071</v>
+        <v>20012</v>
       </c>
       <c r="D35" s="1">
         <v>1</v>
       </c>
       <c r="E35" s="4">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>95</v>
@@ -3550,7 +3555,7 @@
         <v>0</v>
       </c>
       <c r="O35" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P35" s="1">
         <v>0</v>
@@ -3573,13 +3578,12 @@
       <c r="V35" s="1">
         <v>0</v>
       </c>
-      <c r="Z35" s="1">
-        <v>6</v>
-      </c>
-      <c r="AA35" s="4">
-        <v>10</v>
-      </c>
-      <c r="AB35" s="4"/>
+      <c r="X35" s="1">
+        <v>10005</v>
+      </c>
+      <c r="Y35" s="1">
+        <v>5</v>
+      </c>
       <c r="AC35" s="1">
         <v>1</v>
       </c>
@@ -3588,27 +3592,91 @@
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:30">
-      <c r="F36" s="4"/>
-      <c r="U36" s="4"/>
+      <c r="C36" s="1">
+        <v>20022</v>
+      </c>
+      <c r="D36" s="1">
+        <v>1</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1002</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I36" s="1">
+        <v>0</v>
+      </c>
+      <c r="J36" s="1">
+        <v>0</v>
+      </c>
+      <c r="K36" s="1">
+        <v>0</v>
+      </c>
+      <c r="L36" s="1">
+        <v>1</v>
+      </c>
+      <c r="M36" s="1">
+        <v>0</v>
+      </c>
+      <c r="N36" s="1">
+        <v>0</v>
+      </c>
+      <c r="O36" s="1">
+        <v>0</v>
+      </c>
+      <c r="P36" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="1">
+        <v>0</v>
+      </c>
+      <c r="R36" s="1">
+        <v>0</v>
+      </c>
+      <c r="S36" s="1">
+        <v>0</v>
+      </c>
+      <c r="T36" s="1">
+        <v>0</v>
+      </c>
+      <c r="U36" s="4">
+        <v>0</v>
+      </c>
+      <c r="V36" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD36" s="1">
+        <v>5</v>
+      </c>
     </row>
     <row r="37" customHeight="1" spans="3:30">
       <c r="C37" s="1">
-        <v>20012</v>
+        <v>20032</v>
       </c>
       <c r="D37" s="1">
         <v>1</v>
       </c>
       <c r="E37" s="4">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I37" s="1">
         <v>0</v>
@@ -3623,13 +3691,13 @@
         <v>0</v>
       </c>
       <c r="M37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O37" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P37" s="1">
         <v>0</v>
@@ -3652,13 +3720,6 @@
       <c r="V37" s="1">
         <v>0</v>
       </c>
-      <c r="X37" s="1">
-        <v>10005</v>
-      </c>
-      <c r="Y37" s="1">
-        <v>5</v>
-      </c>
-      <c r="Z37" s="1"/>
       <c r="AC37" s="1">
         <v>1</v>
       </c>
@@ -3668,22 +3729,22 @@
     </row>
     <row r="38" customHeight="1" spans="3:30">
       <c r="C38" s="1">
-        <v>20022</v>
+        <v>20072</v>
       </c>
       <c r="D38" s="1">
         <v>1</v>
       </c>
       <c r="E38" s="1">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I38" s="1">
         <v>0</v>
@@ -3695,7 +3756,7 @@
         <v>0</v>
       </c>
       <c r="L38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="1">
         <v>0</v>
@@ -3727,93 +3788,25 @@
       <c r="V38" s="1">
         <v>0</v>
       </c>
+      <c r="Z38" s="1">
+        <v>6</v>
+      </c>
+      <c r="AA38" s="4">
+        <v>20</v>
+      </c>
+      <c r="AB38" s="1">
+        <v>3</v>
+      </c>
       <c r="AC38" s="1">
         <v>1</v>
       </c>
       <c r="AD38" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="3:30">
-      <c r="C39" s="1">
-        <v>20032</v>
-      </c>
-      <c r="D39" s="1">
-        <v>1</v>
-      </c>
-      <c r="E39" s="1">
-        <v>1003</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I39" s="1">
-        <v>0</v>
-      </c>
-      <c r="J39" s="1">
-        <v>0</v>
-      </c>
-      <c r="K39" s="1">
-        <v>0</v>
-      </c>
-      <c r="L39" s="1">
-        <v>0</v>
-      </c>
-      <c r="M39" s="1">
-        <v>0</v>
-      </c>
-      <c r="N39" s="1">
-        <v>0</v>
-      </c>
-      <c r="O39" s="1">
-        <v>0</v>
-      </c>
-      <c r="P39" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="1">
-        <v>0</v>
-      </c>
-      <c r="R39" s="1">
-        <v>0</v>
-      </c>
-      <c r="S39" s="1">
-        <v>0</v>
-      </c>
-      <c r="T39" s="1">
-        <v>0</v>
-      </c>
-      <c r="U39" s="4">
-        <v>0</v>
-      </c>
-      <c r="V39" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z39" s="1">
-        <v>6</v>
-      </c>
-      <c r="AA39" s="1">
-        <v>10</v>
-      </c>
-      <c r="AB39" s="1">
-        <v>3</v>
-      </c>
-      <c r="AC39" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD39" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:30">
       <c r="C40" s="1">
-        <v>20022</v>
+        <v>20023</v>
       </c>
       <c r="D40" s="1">
         <v>1</v>
@@ -3822,7 +3815,7 @@
         <v>1004</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>103</v>
@@ -3890,16 +3883,16 @@
     </row>
     <row r="41" customHeight="1" spans="3:30">
       <c r="C41" s="1">
-        <v>20042</v>
+        <v>20033</v>
       </c>
       <c r="D41" s="1">
         <v>1</v>
       </c>
       <c r="E41" s="1">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>105</v>
@@ -3950,13 +3943,13 @@
         <v>0</v>
       </c>
       <c r="Z41" s="1">
-        <v>4</v>
-      </c>
-      <c r="AA41" s="4">
-        <v>-20</v>
-      </c>
-      <c r="AB41" s="4">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="AA41" s="1">
+        <v>10</v>
+      </c>
+      <c r="AB41" s="1">
+        <v>3</v>
       </c>
       <c r="AC41" s="1">
         <v>1</v>
@@ -3967,16 +3960,16 @@
     </row>
     <row r="42" customHeight="1" spans="3:30">
       <c r="C42" s="1">
-        <v>20072</v>
+        <v>20043</v>
       </c>
       <c r="D42" s="1">
         <v>1</v>
       </c>
       <c r="E42" s="1">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>107</v>
@@ -4027,104 +4020,33 @@
         <v>0</v>
       </c>
       <c r="Z42" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AA42" s="4">
-        <v>20</v>
-      </c>
-      <c r="AB42" s="1">
-        <v>3</v>
+        <v>-20</v>
+      </c>
+      <c r="AB42" s="4">
+        <v>1</v>
       </c>
       <c r="AC42" s="1">
         <v>1</v>
       </c>
       <c r="AD42" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="3:30">
-      <c r="C44" s="1">
-        <v>20023</v>
-      </c>
-      <c r="D44" s="1">
-        <v>1</v>
-      </c>
-      <c r="E44" s="1">
-        <v>1002</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="I44" s="1">
-        <v>0</v>
-      </c>
-      <c r="J44" s="1">
-        <v>0</v>
-      </c>
-      <c r="K44" s="1">
-        <v>1</v>
-      </c>
-      <c r="L44" s="1">
-        <v>0</v>
-      </c>
-      <c r="M44" s="1">
-        <v>0</v>
-      </c>
-      <c r="N44" s="1">
-        <v>0</v>
-      </c>
-      <c r="O44" s="1">
-        <v>0</v>
-      </c>
-      <c r="P44" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="1">
-        <v>0</v>
-      </c>
-      <c r="R44" s="1">
-        <v>0</v>
-      </c>
-      <c r="S44" s="1">
-        <v>0</v>
-      </c>
-      <c r="T44" s="1">
-        <v>0</v>
-      </c>
-      <c r="U44" s="4">
-        <v>0</v>
-      </c>
-      <c r="V44" s="1">
-        <v>0</v>
-      </c>
-      <c r="W44" s="1">
-        <v>100</v>
-      </c>
-      <c r="AC44" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD44" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:30">
       <c r="C45" s="1">
-        <v>20033</v>
+        <v>20024</v>
       </c>
       <c r="D45" s="1">
         <v>1</v>
       </c>
       <c r="E45" s="1">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>109</v>
@@ -4139,7 +4061,7 @@
         <v>0</v>
       </c>
       <c r="K45" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="1">
         <v>0</v>
@@ -4184,168 +4106,97 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" s="2" customFormat="1" customHeight="1"/>
-    <row r="49" customHeight="1" spans="3:30">
-      <c r="C49" s="1">
-        <v>30011</v>
-      </c>
-      <c r="D49" s="1">
-        <v>1</v>
-      </c>
-      <c r="E49" s="4">
-        <v>3001</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="I49" s="1">
-        <v>0</v>
-      </c>
-      <c r="J49" s="1">
-        <v>0</v>
-      </c>
-      <c r="K49" s="1">
-        <v>0</v>
-      </c>
-      <c r="L49" s="1">
-        <v>0</v>
-      </c>
-      <c r="M49" s="1">
-        <v>0</v>
-      </c>
-      <c r="N49" s="1">
-        <v>0</v>
-      </c>
-      <c r="O49" s="1">
-        <v>5</v>
-      </c>
-      <c r="P49" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="1">
-        <v>0</v>
-      </c>
-      <c r="R49" s="1">
-        <v>0</v>
-      </c>
-      <c r="S49" s="1">
-        <v>0</v>
-      </c>
-      <c r="T49" s="1">
-        <v>0</v>
-      </c>
-      <c r="U49" s="4">
-        <v>0</v>
-      </c>
-      <c r="V49" s="1">
-        <v>0</v>
-      </c>
-      <c r="X49" s="1">
-        <v>1009</v>
-      </c>
-      <c r="Y49" s="1">
-        <v>20</v>
-      </c>
-      <c r="Z49" s="1"/>
-      <c r="AC49" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD49" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:30">
-      <c r="C50" s="1">
-        <v>30021</v>
-      </c>
-      <c r="D50" s="1">
-        <v>1</v>
-      </c>
-      <c r="E50" s="4">
-        <v>3002</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I50" s="1">
-        <v>0</v>
-      </c>
-      <c r="J50" s="1">
-        <v>0</v>
-      </c>
-      <c r="K50" s="1">
-        <v>0</v>
-      </c>
-      <c r="L50" s="1">
-        <v>0</v>
-      </c>
-      <c r="M50" s="1">
-        <v>0</v>
-      </c>
-      <c r="N50" s="1">
-        <v>0</v>
-      </c>
-      <c r="O50" s="1">
-        <v>0</v>
-      </c>
-      <c r="P50" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="1">
-        <v>0</v>
-      </c>
-      <c r="R50" s="1">
-        <v>0</v>
-      </c>
-      <c r="S50" s="1">
-        <v>0</v>
-      </c>
-      <c r="T50" s="1">
-        <v>0</v>
-      </c>
-      <c r="U50" s="4">
-        <v>0</v>
-      </c>
-      <c r="V50" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC50" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD50" s="1">
-        <v>5</v>
-      </c>
-    </row>
+    <row r="46" customHeight="1" spans="3:30">
+      <c r="C46" s="1">
+        <v>20034</v>
+      </c>
+      <c r="D46" s="1">
+        <v>1</v>
+      </c>
+      <c r="E46" s="1">
+        <v>1003</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I46" s="1">
+        <v>0</v>
+      </c>
+      <c r="J46" s="1">
+        <v>0</v>
+      </c>
+      <c r="K46" s="1">
+        <v>0</v>
+      </c>
+      <c r="L46" s="1">
+        <v>0</v>
+      </c>
+      <c r="M46" s="1">
+        <v>0</v>
+      </c>
+      <c r="N46" s="1">
+        <v>0</v>
+      </c>
+      <c r="O46" s="1">
+        <v>0</v>
+      </c>
+      <c r="P46" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="1">
+        <v>0</v>
+      </c>
+      <c r="R46" s="1">
+        <v>0</v>
+      </c>
+      <c r="S46" s="1">
+        <v>0</v>
+      </c>
+      <c r="T46" s="1">
+        <v>0</v>
+      </c>
+      <c r="U46" s="4">
+        <v>0</v>
+      </c>
+      <c r="V46" s="1">
+        <v>0</v>
+      </c>
+      <c r="W46" s="1">
+        <v>100</v>
+      </c>
+      <c r="AC46" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD46" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" customHeight="1"/>
+    <row r="50" s="2" customFormat="1" customHeight="1"/>
     <row r="51" customHeight="1" spans="3:30">
       <c r="C51" s="1">
-        <v>30031</v>
+        <v>30011</v>
       </c>
       <c r="D51" s="1">
         <v>1</v>
       </c>
       <c r="E51" s="4">
-        <v>3003</v>
+        <v>3001</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="I51" s="1">
         <v>0</v>
@@ -4366,7 +4217,7 @@
         <v>0</v>
       </c>
       <c r="O51" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P51" s="1">
         <v>0</v>
@@ -4389,14 +4240,11 @@
       <c r="V51" s="1">
         <v>0</v>
       </c>
-      <c r="Z51" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA51" s="4">
-        <v>-1</v>
-      </c>
-      <c r="AB51" s="4">
-        <v>0</v>
+      <c r="X51" s="1">
+        <v>33</v>
+      </c>
+      <c r="Y51" s="1">
+        <v>20</v>
       </c>
       <c r="AC51" s="1">
         <v>1</v>
@@ -4407,22 +4255,22 @@
     </row>
     <row r="52" customHeight="1" spans="3:30">
       <c r="C52" s="1">
-        <v>30041</v>
+        <v>30021</v>
       </c>
       <c r="D52" s="1">
         <v>1</v>
       </c>
       <c r="E52" s="4">
-        <v>3004</v>
+        <v>3002</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>118</v>
+        <v>57</v>
       </c>
       <c r="I52" s="1">
         <v>0</v>
@@ -4465,15 +4313,6 @@
       </c>
       <c r="V52" s="1">
         <v>0</v>
-      </c>
-      <c r="Z52" s="1">
-        <v>8</v>
-      </c>
-      <c r="AA52" s="1">
-        <v>100</v>
-      </c>
-      <c r="AB52" s="1">
-        <v>1</v>
       </c>
       <c r="AC52" s="1">
         <v>1</v>
@@ -4484,22 +4323,22 @@
     </row>
     <row r="53" customHeight="1" spans="3:30">
       <c r="C53" s="1">
-        <v>30051</v>
+        <v>30031</v>
       </c>
       <c r="D53" s="1">
         <v>1</v>
       </c>
       <c r="E53" s="4">
-        <v>3005</v>
+        <v>3003</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="I53" s="1">
         <v>0</v>
@@ -4541,6 +4380,15 @@
         <v>0</v>
       </c>
       <c r="V53" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AB53" s="4">
         <v>0</v>
       </c>
       <c r="AC53" s="1">
@@ -4552,22 +4400,22 @@
     </row>
     <row r="54" customHeight="1" spans="3:30">
       <c r="C54" s="1">
-        <v>30061</v>
+        <v>30041</v>
       </c>
       <c r="D54" s="1">
         <v>1</v>
       </c>
       <c r="E54" s="4">
-        <v>3006</v>
+        <v>3004</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I54" s="1">
         <v>0</v>
@@ -4588,7 +4436,7 @@
         <v>0</v>
       </c>
       <c r="O54" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P54" s="1">
         <v>0</v>
@@ -4610,6 +4458,15 @@
       </c>
       <c r="V54" s="1">
         <v>0</v>
+      </c>
+      <c r="Z54" s="1">
+        <v>8</v>
+      </c>
+      <c r="AA54" s="1">
+        <v>100</v>
+      </c>
+      <c r="AB54" s="1">
+        <v>1</v>
       </c>
       <c r="AC54" s="1">
         <v>1</v>
@@ -4620,22 +4477,22 @@
     </row>
     <row r="55" customHeight="1" spans="3:30">
       <c r="C55" s="1">
-        <v>30071</v>
+        <v>30051</v>
       </c>
       <c r="D55" s="1">
         <v>1</v>
       </c>
       <c r="E55" s="4">
-        <v>3007</v>
+        <v>3005</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>124</v>
+        <v>64</v>
       </c>
       <c r="I55" s="1">
         <v>0</v>
@@ -4647,7 +4504,7 @@
         <v>0</v>
       </c>
       <c r="L55" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" s="1">
         <v>0</v>
@@ -4683,27 +4540,95 @@
         <v>1</v>
       </c>
       <c r="AD55" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:30">
+      <c r="C56" s="1">
+        <v>30061</v>
+      </c>
+      <c r="D56" s="1">
+        <v>1</v>
+      </c>
+      <c r="E56" s="4">
+        <v>3006</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I56" s="1">
+        <v>0</v>
+      </c>
+      <c r="J56" s="1">
+        <v>0</v>
+      </c>
+      <c r="K56" s="1">
+        <v>0</v>
+      </c>
+      <c r="L56" s="1">
+        <v>0</v>
+      </c>
+      <c r="M56" s="1">
+        <v>0</v>
+      </c>
+      <c r="N56" s="1">
+        <v>0</v>
+      </c>
+      <c r="O56" s="1">
+        <v>5</v>
+      </c>
+      <c r="P56" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="1">
+        <v>0</v>
+      </c>
+      <c r="R56" s="1">
+        <v>0</v>
+      </c>
+      <c r="S56" s="1">
+        <v>0</v>
+      </c>
+      <c r="T56" s="1">
+        <v>0</v>
+      </c>
+      <c r="U56" s="4">
+        <v>0</v>
+      </c>
+      <c r="V56" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC56" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD56" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:30">
       <c r="C57" s="1">
-        <v>30012</v>
+        <v>30071</v>
       </c>
       <c r="D57" s="1">
         <v>1</v>
       </c>
       <c r="E57" s="4">
-        <v>3001</v>
+        <v>3007</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I57" s="1">
         <v>0</v>
@@ -4715,7 +4640,7 @@
         <v>0</v>
       </c>
       <c r="L57" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" s="1">
         <v>0</v>
@@ -4724,7 +4649,7 @@
         <v>0</v>
       </c>
       <c r="O57" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P57" s="1">
         <v>0</v>
@@ -4747,106 +4672,31 @@
       <c r="V57" s="1">
         <v>0</v>
       </c>
-      <c r="X57" s="1">
-        <v>10006</v>
-      </c>
-      <c r="Y57" s="1">
-        <v>5</v>
-      </c>
-      <c r="Z57" s="1"/>
       <c r="AC57" s="1">
         <v>1</v>
       </c>
       <c r="AD57" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58" customHeight="1" spans="3:30">
-      <c r="C58" s="1">
-        <v>30022</v>
-      </c>
-      <c r="D58" s="1">
-        <v>1</v>
-      </c>
-      <c r="E58" s="4">
-        <v>3002</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="I58" s="1">
-        <v>0</v>
-      </c>
-      <c r="J58" s="1">
-        <v>0</v>
-      </c>
-      <c r="K58" s="1">
-        <v>0</v>
-      </c>
-      <c r="L58" s="1">
-        <v>1</v>
-      </c>
-      <c r="M58" s="1">
-        <v>0</v>
-      </c>
-      <c r="N58" s="1">
-        <v>0</v>
-      </c>
-      <c r="O58" s="1">
-        <v>0</v>
-      </c>
-      <c r="P58" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="1">
-        <v>0</v>
-      </c>
-      <c r="R58" s="1">
-        <v>0</v>
-      </c>
-      <c r="S58" s="1">
-        <v>0</v>
-      </c>
-      <c r="T58" s="1">
-        <v>0</v>
-      </c>
-      <c r="U58" s="4">
-        <v>0</v>
-      </c>
-      <c r="V58" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC58" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD58" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:30">
       <c r="C59" s="1">
-        <v>30032</v>
+        <v>30012</v>
       </c>
       <c r="D59" s="1">
         <v>1</v>
       </c>
       <c r="E59" s="4">
-        <v>3003</v>
+        <v>3001</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="I59" s="1">
         <v>0</v>
@@ -4867,7 +4717,7 @@
         <v>0</v>
       </c>
       <c r="O59" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P59" s="1">
         <v>0</v>
@@ -4890,14 +4740,11 @@
       <c r="V59" s="1">
         <v>0</v>
       </c>
-      <c r="Z59" s="1">
-        <v>6</v>
-      </c>
-      <c r="AA59" s="1">
-        <v>10</v>
-      </c>
-      <c r="AB59" s="1">
-        <v>3</v>
+      <c r="X59" s="1">
+        <v>10006</v>
+      </c>
+      <c r="Y59" s="1">
+        <v>5</v>
       </c>
       <c r="AC59" s="1">
         <v>1</v>
@@ -4908,22 +4755,22 @@
     </row>
     <row r="60" customHeight="1" spans="3:30">
       <c r="C60" s="1">
-        <v>30033</v>
+        <v>30022</v>
       </c>
       <c r="D60" s="1">
         <v>1</v>
       </c>
       <c r="E60" s="4">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="I60" s="1">
         <v>0</v>
@@ -4935,7 +4782,7 @@
         <v>0</v>
       </c>
       <c r="L60" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M60" s="1">
         <v>0</v>
@@ -4976,22 +4823,22 @@
     </row>
     <row r="61" customHeight="1" spans="3:30">
       <c r="C61" s="1">
-        <v>30042</v>
+        <v>30032</v>
       </c>
       <c r="D61" s="1">
         <v>1</v>
       </c>
       <c r="E61" s="4">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="I61" s="1">
         <v>0</v>
@@ -5036,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="Z61" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AA61" s="1">
         <v>10</v>
@@ -5051,95 +4898,92 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" customHeight="1" spans="3:30">
-      <c r="C62" s="1">
-        <v>30072</v>
-      </c>
-      <c r="D62" s="1">
-        <v>1</v>
-      </c>
-      <c r="E62" s="4">
-        <v>2007</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="I62" s="1">
-        <v>0</v>
-      </c>
-      <c r="J62" s="1">
-        <v>0</v>
-      </c>
-      <c r="K62" s="1">
-        <v>0</v>
-      </c>
-      <c r="L62" s="1">
-        <v>0</v>
-      </c>
-      <c r="M62" s="1">
-        <v>0</v>
-      </c>
-      <c r="N62" s="1">
-        <v>0</v>
-      </c>
-      <c r="O62" s="1">
-        <v>0</v>
-      </c>
-      <c r="P62" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="1">
-        <v>0</v>
-      </c>
-      <c r="R62" s="1">
-        <v>0</v>
-      </c>
-      <c r="S62" s="1">
-        <v>0</v>
-      </c>
-      <c r="T62" s="1">
-        <v>0</v>
-      </c>
-      <c r="U62" s="4">
-        <v>0</v>
-      </c>
-      <c r="V62" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z62" s="4">
-        <v>1001</v>
-      </c>
-      <c r="AC62" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD62" s="1">
+    <row r="63" customHeight="1" spans="3:30">
+      <c r="C63" s="1">
+        <v>30033</v>
+      </c>
+      <c r="D63" s="1">
+        <v>1</v>
+      </c>
+      <c r="E63" s="4">
+        <v>3003</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I63" s="1">
+        <v>0</v>
+      </c>
+      <c r="J63" s="1">
+        <v>0</v>
+      </c>
+      <c r="K63" s="1">
+        <v>0</v>
+      </c>
+      <c r="L63" s="1">
+        <v>3</v>
+      </c>
+      <c r="M63" s="1">
+        <v>0</v>
+      </c>
+      <c r="N63" s="1">
+        <v>0</v>
+      </c>
+      <c r="O63" s="1">
+        <v>0</v>
+      </c>
+      <c r="P63" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="1">
+        <v>0</v>
+      </c>
+      <c r="R63" s="1">
+        <v>0</v>
+      </c>
+      <c r="S63" s="1">
+        <v>0</v>
+      </c>
+      <c r="T63" s="1">
+        <v>0</v>
+      </c>
+      <c r="U63" s="4">
+        <v>0</v>
+      </c>
+      <c r="V63" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD63" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:30">
       <c r="C64" s="1">
-        <v>30022</v>
+        <v>30043</v>
       </c>
       <c r="D64" s="1">
         <v>1</v>
       </c>
       <c r="E64" s="4">
-        <v>3002</v>
+        <v>3004</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="I64" s="1">
         <v>0</v>
@@ -5151,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="L64" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" s="1">
         <v>0</v>
@@ -5183,8 +5027,14 @@
       <c r="V64" s="1">
         <v>0</v>
       </c>
-      <c r="W64" s="1">
-        <v>100</v>
+      <c r="Z64" s="1">
+        <v>9</v>
+      </c>
+      <c r="AA64" s="1">
+        <v>10</v>
+      </c>
+      <c r="AB64" s="1">
+        <v>3</v>
       </c>
       <c r="AC64" s="1">
         <v>1</v>
@@ -5195,72 +5045,214 @@
     </row>
     <row r="65" customHeight="1" spans="3:30">
       <c r="C65" s="1">
-        <v>30032</v>
+        <v>30073</v>
       </c>
       <c r="D65" s="1">
         <v>1</v>
       </c>
       <c r="E65" s="4">
+        <v>2007</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I65" s="1">
+        <v>0</v>
+      </c>
+      <c r="J65" s="1">
+        <v>0</v>
+      </c>
+      <c r="K65" s="1">
+        <v>0</v>
+      </c>
+      <c r="L65" s="1">
+        <v>0</v>
+      </c>
+      <c r="M65" s="1">
+        <v>0</v>
+      </c>
+      <c r="N65" s="1">
+        <v>0</v>
+      </c>
+      <c r="O65" s="1">
+        <v>0</v>
+      </c>
+      <c r="P65" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="1">
+        <v>0</v>
+      </c>
+      <c r="R65" s="1">
+        <v>0</v>
+      </c>
+      <c r="S65" s="1">
+        <v>0</v>
+      </c>
+      <c r="T65" s="1">
+        <v>0</v>
+      </c>
+      <c r="U65" s="4">
+        <v>0</v>
+      </c>
+      <c r="V65" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="4">
+        <v>1001</v>
+      </c>
+      <c r="AC65" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD65" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:30">
+      <c r="C67" s="1">
+        <v>30024</v>
+      </c>
+      <c r="D67" s="1">
+        <v>1</v>
+      </c>
+      <c r="E67" s="4">
+        <v>3002</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I67" s="1">
+        <v>0</v>
+      </c>
+      <c r="J67" s="1">
+        <v>0</v>
+      </c>
+      <c r="K67" s="1">
+        <v>0</v>
+      </c>
+      <c r="L67" s="1">
+        <v>1</v>
+      </c>
+      <c r="M67" s="1">
+        <v>0</v>
+      </c>
+      <c r="N67" s="1">
+        <v>0</v>
+      </c>
+      <c r="O67" s="1">
+        <v>0</v>
+      </c>
+      <c r="P67" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="1">
+        <v>0</v>
+      </c>
+      <c r="R67" s="1">
+        <v>0</v>
+      </c>
+      <c r="S67" s="1">
+        <v>0</v>
+      </c>
+      <c r="T67" s="1">
+        <v>0</v>
+      </c>
+      <c r="U67" s="4">
+        <v>0</v>
+      </c>
+      <c r="V67" s="1">
+        <v>0</v>
+      </c>
+      <c r="W67" s="1">
+        <v>100</v>
+      </c>
+      <c r="AC67" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD67" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:30">
+      <c r="C68" s="1">
+        <v>30034</v>
+      </c>
+      <c r="D68" s="1">
+        <v>1</v>
+      </c>
+      <c r="E68" s="4">
         <v>3003</v>
       </c>
-      <c r="F65" s="4" t="s">
+      <c r="F68" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="G65" s="1" t="s">
+      <c r="G68" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="H65" s="1" t="s">
+      <c r="H68" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="I65" s="1">
-        <v>0</v>
-      </c>
-      <c r="J65" s="1">
-        <v>0</v>
-      </c>
-      <c r="K65" s="1">
-        <v>0</v>
-      </c>
-      <c r="L65" s="1">
-        <v>0</v>
-      </c>
-      <c r="M65" s="1">
-        <v>0</v>
-      </c>
-      <c r="N65" s="1">
-        <v>0</v>
-      </c>
-      <c r="O65" s="1">
-        <v>0</v>
-      </c>
-      <c r="P65" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="1">
-        <v>0</v>
-      </c>
-      <c r="R65" s="1">
-        <v>0</v>
-      </c>
-      <c r="S65" s="1">
-        <v>0</v>
-      </c>
-      <c r="T65" s="1">
-        <v>0</v>
-      </c>
-      <c r="U65" s="4">
-        <v>0</v>
-      </c>
-      <c r="V65" s="1">
-        <v>0</v>
-      </c>
-      <c r="W65" s="1">
+      <c r="I68" s="1">
+        <v>0</v>
+      </c>
+      <c r="J68" s="1">
+        <v>0</v>
+      </c>
+      <c r="K68" s="1">
+        <v>0</v>
+      </c>
+      <c r="L68" s="1">
+        <v>0</v>
+      </c>
+      <c r="M68" s="1">
+        <v>0</v>
+      </c>
+      <c r="N68" s="1">
+        <v>0</v>
+      </c>
+      <c r="O68" s="1">
+        <v>0</v>
+      </c>
+      <c r="P68" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="1">
+        <v>0</v>
+      </c>
+      <c r="R68" s="1">
+        <v>0</v>
+      </c>
+      <c r="S68" s="1">
+        <v>0</v>
+      </c>
+      <c r="T68" s="1">
+        <v>0</v>
+      </c>
+      <c r="U68" s="4">
+        <v>0</v>
+      </c>
+      <c r="V68" s="1">
+        <v>0</v>
+      </c>
+      <c r="W68" s="1">
         <v>100</v>
       </c>
-      <c r="AC65" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD65" s="1">
+      <c r="AC68" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD68" s="1">
         <v>5</v>
       </c>
     </row>

--- a/Excel/SkillTalentConfig.xlsx
+++ b/Excel/SkillTalentConfig.xlsx
@@ -383,7 +383,7 @@
     <t>火麟剑诀</t>
   </si>
   <si>
-    <t>增加5%物攻倍率</t>
+    <t>增加5%物攻增幅</t>
   </si>
   <si>
     <t>·吸血</t>
@@ -464,7 +464,7 @@
     <t>·魔体</t>
   </si>
   <si>
-    <t>增加{0}%魔法倍率</t>
+    <t>增加{0}%魔法增幅</t>
   </si>
   <si>
     <t>·狂潮</t>
@@ -554,7 +554,7 @@
     <t>·神体</t>
   </si>
   <si>
-    <t>增加{0}%道术倍率</t>
+    <t>增加{0}%道术增幅</t>
   </si>
   <si>
     <t>·符引双生</t>
@@ -2403,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="X14" s="1">
-        <v>10004</v>
+        <v>2004</v>
       </c>
       <c r="Y14" s="1">
         <v>5</v>
@@ -3579,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="X35" s="1">
-        <v>10005</v>
+        <v>2005</v>
       </c>
       <c r="Y35" s="1">
         <v>5</v>
@@ -4741,7 +4741,7 @@
         <v>0</v>
       </c>
       <c r="X59" s="1">
-        <v>10006</v>
+        <v>2006</v>
       </c>
       <c r="Y59" s="1">
         <v>5</v>

--- a/Excel/SkillTalentConfig.xlsx
+++ b/Excel/SkillTalentConfig.xlsx
@@ -101,7 +101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z4" authorId="1">
+    <comment ref="AC4" authorId="1">
       <text>
         <r>
           <rPr>
@@ -123,7 +123,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA4" authorId="1">
+    <comment ref="AD4" authorId="1">
       <text>
         <r>
           <rPr>
@@ -145,7 +145,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB4" authorId="1">
+    <comment ref="AE4" authorId="1">
       <text>
         <r>
           <rPr>
@@ -174,7 +174,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="138">
   <si>
     <t>#</t>
   </si>
@@ -227,6 +227,12 @@
     <t>暴击倍率</t>
   </si>
   <si>
+    <t>致命率</t>
+  </si>
+  <si>
+    <t>致命伤害</t>
+  </si>
+  <si>
     <t>伤害加成</t>
   </si>
   <si>
@@ -236,6 +242,9 @@
     <t>最终加成</t>
   </si>
   <si>
+    <t>Accuracy</t>
+  </si>
+  <si>
     <t>Speed</t>
   </si>
   <si>
@@ -299,7 +308,13 @@
     <t>CritDamage</t>
   </si>
   <si>
-    <t>DamageIncrea</t>
+    <t>DeadlyRate</t>
+  </si>
+  <si>
+    <t>DeadlyDamage</t>
+  </si>
+  <si>
+    <t>RateDamage</t>
   </si>
   <si>
     <t>AttrIncrea</t>
@@ -356,13 +371,13 @@
     <t>·破甲</t>
   </si>
   <si>
-    <t>每次计算伤害，削减敌人1点护甲，无叠加上限</t>
+    <t>每次伤害削减敌人1点护甲，无上限</t>
   </si>
   <si>
     <t>重击剑术</t>
   </si>
   <si>
-    <t>削减敌人100点护甲，生效一次</t>
+    <t>削减敌人100点护甲</t>
   </si>
   <si>
     <t>武神盾</t>
@@ -392,7 +407,7 @@
     <t>回复1%伤害的生命</t>
   </si>
   <si>
-    <t>·千里断江</t>
+    <t>·断河</t>
   </si>
   <si>
     <t>剑阵的攻击范围增加一行一列</t>
@@ -407,16 +422,19 @@
     <t>削减敌人20%护甲</t>
   </si>
   <si>
+    <t>·斩江</t>
+  </si>
+  <si>
     <t>攻击距离加2格</t>
   </si>
   <si>
     <t>·焚魂</t>
   </si>
   <si>
-    <t>灼烧敌人20%的伤害，按攻速结算，最高3层</t>
-  </si>
-  <si>
-    <t>·剑心通明</t>
+    <t>额外灼烧敌人20%的伤害，最高3层</t>
+  </si>
+  <si>
+    <t>·剑心</t>
   </si>
   <si>
     <t>此技能攻击速度增加100%</t>
@@ -458,7 +476,7 @@
     <t>·霜寒</t>
   </si>
   <si>
-    <t>给敌人附加一个额外承受10%伤害的状态，最高3层</t>
+    <t>敌人额外承受10%伤害，最高3层</t>
   </si>
   <si>
     <t>·魔体</t>
@@ -473,7 +491,7 @@
     <t>额外攻击一个敌人</t>
   </si>
   <si>
-    <t>·炼狱火海</t>
+    <t>·炼狱</t>
   </si>
   <si>
     <t>火海的攻击范围增加一行一列</t>
@@ -482,30 +500,24 @@
     <t>·蚀魂</t>
   </si>
   <si>
-    <t>敌人附加一个额外承受20%伤害的状态，最高3层</t>
+    <t>敌人额外承受20%伤害，最高3层</t>
   </si>
   <si>
     <t>·燃魂</t>
   </si>
   <si>
-    <t>自己附加一个额外增加5%伤害的状态，最高3层</t>
+    <t>自己个额外增加5%伤害，最高3层</t>
   </si>
   <si>
     <t>·蚀骨</t>
   </si>
   <si>
-    <t>敌人附加一个额外承受10%伤害的状态，最高3层</t>
-  </si>
-  <si>
     <t>·冻结</t>
   </si>
   <si>
     <t>敌人降低20%的攻击速度</t>
   </si>
   <si>
-    <t>·上古魔体</t>
-  </si>
-  <si>
     <t>祈福心法</t>
   </si>
   <si>
@@ -557,10 +569,10 @@
     <t>增加{0}%道术增幅</t>
   </si>
   <si>
-    <t>·符引双生</t>
-  </si>
-  <si>
-    <t>·万蛊噬体</t>
+    <t>·双生</t>
+  </si>
+  <si>
+    <t>·蛊体</t>
   </si>
   <si>
     <t>增加3个攻击目标</t>
@@ -569,16 +581,13 @@
     <t>·太清</t>
   </si>
   <si>
-    <t>自己永久附加一个额外增加10%免伤的状态，最高3层</t>
+    <t>自己额外增加10%免伤，最高3层</t>
   </si>
   <si>
     <t>·同心</t>
   </si>
   <si>
     <t>神兽获得人物的灭魂符</t>
-  </si>
-  <si>
-    <t>·天生道体</t>
   </si>
 </sst>
 </file>
@@ -1555,7 +1564,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:AD68"/>
+  <dimension ref="C1:AG68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="6" width="9" style="1"/>
@@ -1570,26 +1579,28 @@
     <col min="16" max="17" width="7.75" style="1" customWidth="1"/>
     <col min="18" max="18" width="7.50833333333333" style="1" customWidth="1"/>
     <col min="19" max="19" width="10.625" style="1" customWidth="1"/>
-    <col min="20" max="21" width="9.83333333333333" style="1" customWidth="1"/>
-    <col min="22" max="25" width="10.0833333333333" style="1" customWidth="1"/>
-    <col min="26" max="27" width="9" style="1" customWidth="1"/>
-    <col min="28" max="28" width="7.58333333333333" style="1" customWidth="1"/>
-    <col min="29" max="29" width="11" style="1" customWidth="1"/>
-    <col min="30" max="30" width="11.9166666666667" style="1" customWidth="1"/>
-    <col min="31" max="16384" width="9" style="1"/>
+    <col min="20" max="20" width="11.25" style="1" customWidth="1"/>
+    <col min="21" max="21" width="10.625" style="1" customWidth="1"/>
+    <col min="22" max="23" width="9.83333333333333" style="1" customWidth="1"/>
+    <col min="24" max="28" width="10.0833333333333" style="1" customWidth="1"/>
+    <col min="29" max="30" width="9" style="1" customWidth="1"/>
+    <col min="31" max="31" width="7.58333333333333" style="1" customWidth="1"/>
+    <col min="32" max="32" width="11" style="1" customWidth="1"/>
+    <col min="33" max="33" width="11.9166666666667" style="1" customWidth="1"/>
+    <col min="34" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:30">
+    <row r="1" customHeight="1" spans="3:33">
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="3:30">
+    <row r="2" customHeight="1" spans="3:33">
       <c r="F2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:30">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1660,184 +1671,211 @@
       <c r="Z3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AA3" s="3"/>
-      <c r="AB3" s="3"/>
+      <c r="AA3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="AC3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD3" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:30">
+        <v>26</v>
+      </c>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG3" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD4" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="AF4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="U4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="V4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="W4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="X4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y4" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD4" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:30">
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C5" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="Y5" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Z5" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="AA5" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="AB5" s="3" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="AC5" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="AD5" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:30">
+        <v>54</v>
+      </c>
+      <c r="AE5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG5" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="3:33">
       <c r="C6" s="1">
         <v>10011</v>
       </c>
@@ -1848,13 +1886,13 @@
         <v>1001</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
@@ -1892,26 +1930,32 @@
       <c r="T6" s="1">
         <v>0</v>
       </c>
-      <c r="U6" s="4">
+      <c r="U6" s="1">
         <v>0</v>
       </c>
       <c r="V6" s="1">
         <v>0</v>
       </c>
+      <c r="W6" s="4">
+        <v>0</v>
+      </c>
       <c r="X6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="1">
         <v>31</v>
       </c>
-      <c r="Y6" s="1">
+      <c r="AB6" s="1">
         <v>20</v>
       </c>
-      <c r="AC6" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD6" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:30">
+      <c r="AF6" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG6" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="3:33">
       <c r="C7" s="1">
         <v>10021</v>
       </c>
@@ -1922,13 +1966,13 @@
         <v>1002</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I7" s="1">
         <v>99</v>
@@ -1966,20 +2010,26 @@
       <c r="T7" s="1">
         <v>0</v>
       </c>
-      <c r="U7" s="4">
+      <c r="U7" s="1">
         <v>0</v>
       </c>
       <c r="V7" s="1">
         <v>0</v>
       </c>
-      <c r="AC7" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD7" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:30">
+      <c r="W7" s="4">
+        <v>0</v>
+      </c>
+      <c r="X7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG7" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:33">
       <c r="C8" s="1">
         <v>10031</v>
       </c>
@@ -1990,13 +2040,13 @@
         <v>1003</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
@@ -2034,29 +2084,35 @@
       <c r="T8" s="1">
         <v>0</v>
       </c>
-      <c r="U8" s="4">
+      <c r="U8" s="1">
         <v>0</v>
       </c>
       <c r="V8" s="1">
         <v>0</v>
       </c>
-      <c r="Z8" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="4">
+      <c r="W8" s="4">
+        <v>0</v>
+      </c>
+      <c r="X8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="4">
         <v>-1</v>
       </c>
-      <c r="AB8" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD8" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:30">
+      <c r="AE8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG8" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:33">
       <c r="C9" s="1">
         <v>10041</v>
       </c>
@@ -2067,13 +2123,13 @@
         <v>1004</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="I9" s="1">
         <v>0</v>
@@ -2111,29 +2167,35 @@
       <c r="T9" s="1">
         <v>0</v>
       </c>
-      <c r="U9" s="4">
+      <c r="U9" s="1">
         <v>0</v>
       </c>
       <c r="V9" s="1">
         <v>0</v>
       </c>
-      <c r="Z9" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="4">
+      <c r="W9" s="4">
+        <v>0</v>
+      </c>
+      <c r="X9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="4">
         <v>-100</v>
       </c>
-      <c r="AB9" s="4">
+      <c r="AE9" s="4">
         <v>2</v>
       </c>
-      <c r="AC9" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD9" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:30">
+      <c r="AF9" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG9" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:33">
       <c r="C10" s="1">
         <v>10051</v>
       </c>
@@ -2144,13 +2206,13 @@
         <v>1005</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I10" s="1">
         <v>0</v>
@@ -2188,20 +2250,26 @@
       <c r="T10" s="1">
         <v>0</v>
       </c>
-      <c r="U10" s="4">
+      <c r="U10" s="1">
         <v>0</v>
       </c>
       <c r="V10" s="1">
         <v>0</v>
       </c>
-      <c r="AC10" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD10" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:30">
+      <c r="W10" s="4">
+        <v>0</v>
+      </c>
+      <c r="X10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="3:33">
       <c r="C11" s="1">
         <v>10061</v>
       </c>
@@ -2212,13 +2280,13 @@
         <v>1006</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
@@ -2253,23 +2321,23 @@
       <c r="S11" s="1">
         <v>0</v>
       </c>
-      <c r="T11" s="1">
-        <v>0</v>
-      </c>
-      <c r="U11" s="4">
-        <v>0</v>
-      </c>
       <c r="V11" s="1">
         <v>0</v>
       </c>
-      <c r="AC11" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD11" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="3:30">
+      <c r="W11" s="4">
+        <v>0</v>
+      </c>
+      <c r="X11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="3:33">
       <c r="C12" s="1">
         <v>10071</v>
       </c>
@@ -2280,13 +2348,13 @@
         <v>1007</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I12" s="1">
         <v>99</v>
@@ -2324,24 +2392,36 @@
       <c r="T12" s="1">
         <v>0</v>
       </c>
-      <c r="U12" s="4">
+      <c r="U12" s="1">
         <v>0</v>
       </c>
       <c r="V12" s="1">
         <v>0</v>
       </c>
-      <c r="AC12" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD12" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:30">
+      <c r="W12" s="4">
+        <v>0</v>
+      </c>
+      <c r="X12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG12" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:33">
       <c r="F13" s="4"/>
-      <c r="U13" s="4"/>
-    </row>
-    <row r="14" customHeight="1" spans="3:30">
+      <c r="T13" s="1">
+        <v>0</v>
+      </c>
+      <c r="U13" s="1">
+        <v>0</v>
+      </c>
+      <c r="W13" s="4"/>
+    </row>
+    <row r="14" customHeight="1" spans="3:33">
       <c r="C14" s="1">
         <v>10012</v>
       </c>
@@ -2352,13 +2432,13 @@
         <v>1001</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
@@ -2396,26 +2476,32 @@
       <c r="T14" s="1">
         <v>0</v>
       </c>
-      <c r="U14" s="4">
+      <c r="U14" s="1">
         <v>0</v>
       </c>
       <c r="V14" s="1">
         <v>0</v>
       </c>
+      <c r="W14" s="4">
+        <v>0</v>
+      </c>
       <c r="X14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="1">
         <v>2004</v>
       </c>
-      <c r="Y14" s="1">
-        <v>5</v>
-      </c>
-      <c r="AC14" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD14" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:30">
+      <c r="AB14" s="1">
+        <v>5</v>
+      </c>
+      <c r="AF14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG14" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:33">
       <c r="C15" s="1">
         <v>10022</v>
       </c>
@@ -2426,13 +2512,13 @@
         <v>1002</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I15" s="1">
         <v>0</v>
@@ -2470,29 +2556,35 @@
       <c r="T15" s="1">
         <v>0</v>
       </c>
-      <c r="U15" s="4">
+      <c r="U15" s="1">
         <v>0</v>
       </c>
       <c r="V15" s="1">
         <v>0</v>
       </c>
-      <c r="Z15" s="1">
+      <c r="W15" s="4">
+        <v>0</v>
+      </c>
+      <c r="X15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="1">
         <v>3</v>
       </c>
-      <c r="AA15" s="4">
-        <v>1</v>
-      </c>
-      <c r="AB15" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD15" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:30">
+      <c r="AD15" s="4">
+        <v>1</v>
+      </c>
+      <c r="AE15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG15" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:33">
       <c r="C16" s="1">
         <v>10032</v>
       </c>
@@ -2503,13 +2595,13 @@
         <v>1003</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
@@ -2547,20 +2639,26 @@
       <c r="T16" s="1">
         <v>0</v>
       </c>
-      <c r="U16" s="4">
+      <c r="U16" s="1">
         <v>0</v>
       </c>
       <c r="V16" s="1">
         <v>0</v>
       </c>
-      <c r="AC16" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD16" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:30">
+      <c r="W16" s="4">
+        <v>0</v>
+      </c>
+      <c r="X16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG16" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:33">
       <c r="C17" s="1">
         <v>10042</v>
       </c>
@@ -2571,13 +2669,13 @@
         <v>1004</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
@@ -2615,29 +2713,35 @@
       <c r="T17" s="1">
         <v>0</v>
       </c>
-      <c r="U17" s="4">
+      <c r="U17" s="1">
         <v>0</v>
       </c>
       <c r="V17" s="1">
         <v>0</v>
       </c>
-      <c r="Z17" s="1">
+      <c r="W17" s="4">
+        <v>0</v>
+      </c>
+      <c r="X17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="1">
         <v>4</v>
       </c>
-      <c r="AA17" s="4">
+      <c r="AD17" s="4">
         <v>-20</v>
       </c>
-      <c r="AB17" s="4">
-        <v>1</v>
-      </c>
-      <c r="AC17" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD17" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:30">
+      <c r="AE17" s="4">
+        <v>1</v>
+      </c>
+      <c r="AF17" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG17" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:33">
       <c r="C18" s="1">
         <v>10072</v>
       </c>
@@ -2648,13 +2752,13 @@
         <v>1007</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="I18" s="1">
         <v>0</v>
@@ -2689,30 +2793,38 @@
       <c r="S18" s="1">
         <v>0</v>
       </c>
-      <c r="T18" s="1">
-        <v>0</v>
-      </c>
-      <c r="U18" s="4">
-        <v>0</v>
-      </c>
       <c r="V18" s="1">
         <v>0</v>
       </c>
-      <c r="Z18" s="1">
+      <c r="W18" s="4">
+        <v>0</v>
+      </c>
+      <c r="X18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="1">
         <v>2</v>
       </c>
-      <c r="AA18" s="4">
+      <c r="AD18" s="4">
         <v>20</v>
       </c>
-      <c r="AB18" s="4"/>
-      <c r="AC18" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD18" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:30">
+      <c r="AE18" s="4"/>
+      <c r="AF18" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:33">
+      <c r="T19" s="1">
+        <v>10</v>
+      </c>
+      <c r="U19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:33">
       <c r="C20" s="1">
         <v>10023</v>
       </c>
@@ -2723,13 +2835,13 @@
         <v>1002</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I20" s="1">
         <v>0</v>
@@ -2765,22 +2877,28 @@
         <v>0</v>
       </c>
       <c r="T20" s="1">
-        <v>0</v>
-      </c>
-      <c r="U20" s="4">
+        <v>10</v>
+      </c>
+      <c r="U20" s="1">
         <v>0</v>
       </c>
       <c r="V20" s="1">
         <v>0</v>
       </c>
-      <c r="AC20" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD20" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:30">
+      <c r="W20" s="4">
+        <v>0</v>
+      </c>
+      <c r="X20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG20" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:33">
       <c r="C21" s="1">
         <v>10073</v>
       </c>
@@ -2791,13 +2909,13 @@
         <v>1007</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="I21" s="1">
         <v>0</v>
@@ -2833,34 +2951,46 @@
         <v>0</v>
       </c>
       <c r="T21" s="1">
-        <v>0</v>
-      </c>
-      <c r="U21" s="4">
+        <v>10</v>
+      </c>
+      <c r="U21" s="1">
         <v>0</v>
       </c>
       <c r="V21" s="1">
         <v>0</v>
       </c>
-      <c r="AC21" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD21" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:30">
-      <c r="U22" s="4"/>
-      <c r="Z22" s="1">
-        <v>5</v>
-      </c>
-      <c r="AA22" s="1">
+      <c r="W21" s="4">
+        <v>0</v>
+      </c>
+      <c r="X21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG21" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:33">
+      <c r="T22" s="1">
+        <v>10</v>
+      </c>
+      <c r="U22" s="1">
+        <v>0</v>
+      </c>
+      <c r="W22" s="4"/>
+      <c r="AC22" s="1">
+        <v>5</v>
+      </c>
+      <c r="AD22" s="1">
         <v>20</v>
       </c>
-      <c r="AB22" s="1">
+      <c r="AE22" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="3:30">
+    <row r="23" customHeight="1" spans="3:33">
       <c r="C23" s="1">
         <v>10024</v>
       </c>
@@ -2871,13 +3001,13 @@
         <v>1002</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="I23" s="1">
         <v>0</v>
@@ -2912,26 +3042,26 @@
       <c r="S23" s="1">
         <v>0</v>
       </c>
-      <c r="T23" s="1">
-        <v>0</v>
-      </c>
-      <c r="U23" s="4">
-        <v>0</v>
-      </c>
       <c r="V23" s="1">
         <v>0</v>
       </c>
-      <c r="W23" s="1">
+      <c r="W23" s="4">
+        <v>0</v>
+      </c>
+      <c r="X23" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="1">
         <v>100</v>
       </c>
-      <c r="AC23" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD23" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:30">
+      <c r="AF23" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG23" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:33">
       <c r="C24" s="1">
         <v>10034</v>
       </c>
@@ -2942,13 +3072,13 @@
         <v>1003</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="I24" s="1">
         <v>0</v>
@@ -2983,30 +3113,37 @@
       <c r="S24" s="1">
         <v>0</v>
       </c>
-      <c r="T24" s="1">
-        <v>0</v>
-      </c>
-      <c r="U24" s="4">
-        <v>0</v>
-      </c>
       <c r="V24" s="1">
         <v>0</v>
       </c>
-      <c r="W24" s="1">
+      <c r="W24" s="4">
+        <v>0</v>
+      </c>
+      <c r="X24" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="1">
         <v>100</v>
       </c>
-      <c r="AC24" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD24" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:30">
-      <c r="U25" s="4"/>
-    </row>
-    <row r="26" s="2" customFormat="1" customHeight="1"/>
-    <row r="27" customHeight="1" spans="3:30">
+      <c r="AF24" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG24" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:33">
+      <c r="W25" s="4"/>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:33">
+      <c r="T26" s="1">
+        <v>0</v>
+      </c>
+      <c r="U26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:33">
       <c r="C27" s="1">
         <v>20011</v>
       </c>
@@ -3017,13 +3154,13 @@
         <v>2001</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I27" s="1">
         <v>0</v>
@@ -3061,26 +3198,32 @@
       <c r="T27" s="1">
         <v>0</v>
       </c>
-      <c r="U27" s="4">
+      <c r="U27" s="1">
         <v>0</v>
       </c>
       <c r="V27" s="1">
         <v>0</v>
       </c>
+      <c r="W27" s="4">
+        <v>0</v>
+      </c>
       <c r="X27" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="1">
         <v>32</v>
       </c>
-      <c r="Y27" s="1">
+      <c r="AB27" s="1">
         <v>20</v>
       </c>
-      <c r="AC27" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD27" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:30">
+      <c r="AF27" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG27" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:33">
       <c r="C28" s="1">
         <v>20021</v>
       </c>
@@ -3091,13 +3234,13 @@
         <v>2002</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I28" s="1">
         <v>99</v>
@@ -3135,20 +3278,26 @@
       <c r="T28" s="1">
         <v>0</v>
       </c>
-      <c r="U28" s="4">
+      <c r="U28" s="1">
         <v>0</v>
       </c>
       <c r="V28" s="1">
         <v>0</v>
       </c>
-      <c r="AC28" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD28" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:30">
+      <c r="W28" s="4">
+        <v>0</v>
+      </c>
+      <c r="X28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG28" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:33">
       <c r="C29" s="1">
         <v>20031</v>
       </c>
@@ -3159,13 +3308,13 @@
         <v>2003</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="I29" s="1">
         <v>0</v>
@@ -3203,29 +3352,35 @@
       <c r="T29" s="1">
         <v>0</v>
       </c>
-      <c r="U29" s="4">
+      <c r="U29" s="1">
         <v>0</v>
       </c>
       <c r="V29" s="1">
         <v>0</v>
       </c>
-      <c r="Z29" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA29" s="1">
+      <c r="W29" s="4">
+        <v>0</v>
+      </c>
+      <c r="X29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD29" s="1">
         <v>-1</v>
       </c>
-      <c r="AB29" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD29" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:30">
+      <c r="AE29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG29" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:33">
       <c r="C30" s="1">
         <v>20041</v>
       </c>
@@ -3236,13 +3391,13 @@
         <v>2004</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="I30" s="1">
         <v>0</v>
@@ -3280,29 +3435,35 @@
       <c r="T30" s="1">
         <v>0</v>
       </c>
-      <c r="U30" s="4">
+      <c r="U30" s="1">
         <v>0</v>
       </c>
       <c r="V30" s="1">
         <v>0</v>
       </c>
-      <c r="Z30" s="1">
+      <c r="W30" s="4">
+        <v>0</v>
+      </c>
+      <c r="X30" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="1">
         <v>2</v>
       </c>
-      <c r="AA30" s="1">
+      <c r="AD30" s="1">
         <v>-50</v>
       </c>
-      <c r="AB30" s="1">
-        <v>5</v>
-      </c>
-      <c r="AC30" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD30" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:30">
+      <c r="AE30" s="1">
+        <v>5</v>
+      </c>
+      <c r="AF30" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG30" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:33">
       <c r="C31" s="1">
         <v>20051</v>
       </c>
@@ -3313,13 +3474,13 @@
         <v>2005</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I31" s="1">
         <v>0</v>
@@ -3354,23 +3515,23 @@
       <c r="S31" s="1">
         <v>0</v>
       </c>
-      <c r="T31" s="1">
-        <v>0</v>
-      </c>
-      <c r="U31" s="4">
-        <v>0</v>
-      </c>
       <c r="V31" s="1">
         <v>0</v>
       </c>
-      <c r="AC31" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD31" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:30">
+      <c r="W31" s="4">
+        <v>0</v>
+      </c>
+      <c r="X31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG31" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:33">
       <c r="C32" s="1">
         <v>20061</v>
       </c>
@@ -3381,13 +3542,13 @@
         <v>2006</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I32" s="1">
         <v>0</v>
@@ -3425,20 +3586,26 @@
       <c r="T32" s="1">
         <v>0</v>
       </c>
-      <c r="U32" s="4">
+      <c r="U32" s="1">
         <v>0</v>
       </c>
       <c r="V32" s="1">
         <v>0</v>
       </c>
-      <c r="AC32" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD32" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:30">
+      <c r="W32" s="4">
+        <v>0</v>
+      </c>
+      <c r="X32" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG32" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:33">
       <c r="C33" s="1">
         <v>20071</v>
       </c>
@@ -3449,13 +3616,13 @@
         <v>2007</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I33" s="1">
         <v>0</v>
@@ -3493,31 +3660,43 @@
       <c r="T33" s="1">
         <v>0</v>
       </c>
-      <c r="U33" s="4">
+      <c r="U33" s="1">
         <v>0</v>
       </c>
       <c r="V33" s="1">
         <v>0</v>
       </c>
-      <c r="Z33" s="1">
+      <c r="W33" s="4">
+        <v>0</v>
+      </c>
+      <c r="X33" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="1">
         <v>6</v>
       </c>
-      <c r="AA33" s="4">
+      <c r="AD33" s="4">
         <v>10</v>
       </c>
-      <c r="AB33" s="4"/>
-      <c r="AC33" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD33" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:30">
+      <c r="AE33" s="4"/>
+      <c r="AF33" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG33" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:33">
       <c r="F34" s="4"/>
-      <c r="U34" s="4"/>
-    </row>
-    <row r="35" customHeight="1" spans="3:30">
+      <c r="T34" s="1">
+        <v>0</v>
+      </c>
+      <c r="U34" s="1">
+        <v>0</v>
+      </c>
+      <c r="W34" s="4"/>
+    </row>
+    <row r="35" customHeight="1" spans="3:33">
       <c r="C35" s="1">
         <v>20012</v>
       </c>
@@ -3528,13 +3707,13 @@
         <v>2001</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="I35" s="1">
         <v>0</v>
@@ -3572,26 +3751,32 @@
       <c r="T35" s="1">
         <v>0</v>
       </c>
-      <c r="U35" s="4">
+      <c r="U35" s="1">
         <v>0</v>
       </c>
       <c r="V35" s="1">
         <v>0</v>
       </c>
+      <c r="W35" s="4">
+        <v>0</v>
+      </c>
       <c r="X35" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="1">
         <v>2005</v>
       </c>
-      <c r="Y35" s="1">
-        <v>5</v>
-      </c>
-      <c r="AC35" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD35" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:30">
+      <c r="AB35" s="1">
+        <v>5</v>
+      </c>
+      <c r="AF35" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG35" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:33">
       <c r="C36" s="1">
         <v>20022</v>
       </c>
@@ -3599,16 +3784,16 @@
         <v>1</v>
       </c>
       <c r="E36" s="1">
-        <v>1002</v>
+        <v>2002</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="I36" s="1">
         <v>0</v>
@@ -3646,20 +3831,26 @@
       <c r="T36" s="1">
         <v>0</v>
       </c>
-      <c r="U36" s="4">
+      <c r="U36" s="1">
         <v>0</v>
       </c>
       <c r="V36" s="1">
         <v>0</v>
       </c>
-      <c r="AC36" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD36" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:30">
+      <c r="W36" s="4">
+        <v>0</v>
+      </c>
+      <c r="X36" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG36" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:33">
       <c r="C37" s="1">
         <v>20032</v>
       </c>
@@ -3670,13 +3861,13 @@
         <v>2003</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="I37" s="1">
         <v>0</v>
@@ -3714,20 +3905,26 @@
       <c r="T37" s="1">
         <v>0</v>
       </c>
-      <c r="U37" s="4">
+      <c r="U37" s="1">
         <v>0</v>
       </c>
       <c r="V37" s="1">
         <v>0</v>
       </c>
-      <c r="AC37" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD37" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:30">
+      <c r="W37" s="4">
+        <v>0</v>
+      </c>
+      <c r="X37" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF37" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG37" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:33">
       <c r="C38" s="1">
         <v>20072</v>
       </c>
@@ -3735,16 +3932,16 @@
         <v>1</v>
       </c>
       <c r="E38" s="1">
-        <v>1007</v>
+        <v>2007</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="I38" s="1">
         <v>0</v>
@@ -3779,32 +3976,40 @@
       <c r="S38" s="1">
         <v>0</v>
       </c>
-      <c r="T38" s="1">
-        <v>0</v>
-      </c>
-      <c r="U38" s="4">
-        <v>0</v>
-      </c>
       <c r="V38" s="1">
         <v>0</v>
       </c>
-      <c r="Z38" s="1">
+      <c r="W38" s="4">
+        <v>0</v>
+      </c>
+      <c r="X38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="1">
         <v>6</v>
       </c>
-      <c r="AA38" s="4">
+      <c r="AD38" s="4">
         <v>20</v>
       </c>
-      <c r="AB38" s="1">
+      <c r="AE38" s="1">
         <v>3</v>
       </c>
-      <c r="AC38" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD38" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:30">
+      <c r="AF38" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG38" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:33">
+      <c r="T39" s="1">
+        <v>10</v>
+      </c>
+      <c r="U39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:33">
       <c r="C40" s="1">
         <v>20023</v>
       </c>
@@ -3812,16 +4017,16 @@
         <v>1</v>
       </c>
       <c r="E40" s="1">
-        <v>1004</v>
+        <v>2004</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="I40" s="1">
         <v>0</v>
@@ -3857,31 +4062,37 @@
         <v>0</v>
       </c>
       <c r="T40" s="1">
-        <v>0</v>
-      </c>
-      <c r="U40" s="4">
+        <v>10</v>
+      </c>
+      <c r="U40" s="1">
         <v>0</v>
       </c>
       <c r="V40" s="1">
         <v>0</v>
       </c>
-      <c r="Z40" s="1">
+      <c r="W40" s="4">
+        <v>0</v>
+      </c>
+      <c r="X40" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="1">
         <v>7</v>
       </c>
-      <c r="AA40" s="1">
-        <v>5</v>
-      </c>
-      <c r="AB40" s="1">
+      <c r="AD40" s="1">
+        <v>5</v>
+      </c>
+      <c r="AE40" s="1">
         <v>3</v>
       </c>
-      <c r="AC40" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD40" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:30">
+      <c r="AF40" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG40" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:33">
       <c r="C41" s="1">
         <v>20033</v>
       </c>
@@ -3889,16 +4100,16 @@
         <v>1</v>
       </c>
       <c r="E41" s="1">
-        <v>1003</v>
+        <v>2003</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="I41" s="1">
         <v>0</v>
@@ -3934,31 +4145,37 @@
         <v>0</v>
       </c>
       <c r="T41" s="1">
-        <v>0</v>
-      </c>
-      <c r="U41" s="4">
+        <v>10</v>
+      </c>
+      <c r="U41" s="1">
         <v>0</v>
       </c>
       <c r="V41" s="1">
         <v>0</v>
       </c>
-      <c r="Z41" s="1">
+      <c r="W41" s="4">
+        <v>0</v>
+      </c>
+      <c r="X41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="1">
         <v>6</v>
       </c>
-      <c r="AA41" s="1">
+      <c r="AD41" s="1">
         <v>10</v>
       </c>
-      <c r="AB41" s="1">
+      <c r="AE41" s="1">
         <v>3</v>
       </c>
-      <c r="AC41" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD41" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:30">
+      <c r="AF41" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG41" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:33">
       <c r="C42" s="1">
         <v>20043</v>
       </c>
@@ -3966,16 +4183,16 @@
         <v>1</v>
       </c>
       <c r="E42" s="1">
-        <v>1004</v>
+        <v>2004</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I42" s="1">
         <v>0</v>
@@ -4011,31 +4228,37 @@
         <v>0</v>
       </c>
       <c r="T42" s="1">
-        <v>0</v>
-      </c>
-      <c r="U42" s="4">
+        <v>10</v>
+      </c>
+      <c r="U42" s="1">
         <v>0</v>
       </c>
       <c r="V42" s="1">
         <v>0</v>
       </c>
-      <c r="Z42" s="1">
+      <c r="W42" s="4">
+        <v>0</v>
+      </c>
+      <c r="X42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="1">
         <v>4</v>
       </c>
-      <c r="AA42" s="4">
+      <c r="AD42" s="4">
         <v>-20</v>
       </c>
-      <c r="AB42" s="4">
-        <v>1</v>
-      </c>
-      <c r="AC42" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD42" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="3:30">
+      <c r="AE42" s="4">
+        <v>1</v>
+      </c>
+      <c r="AF42" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG42" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:33">
       <c r="C45" s="1">
         <v>20024</v>
       </c>
@@ -4043,16 +4266,16 @@
         <v>1</v>
       </c>
       <c r="E45" s="1">
-        <v>1002</v>
+        <v>2002</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="I45" s="1">
         <v>0</v>
@@ -4087,26 +4310,26 @@
       <c r="S45" s="1">
         <v>0</v>
       </c>
-      <c r="T45" s="1">
-        <v>0</v>
-      </c>
-      <c r="U45" s="4">
-        <v>0</v>
-      </c>
       <c r="V45" s="1">
         <v>0</v>
       </c>
-      <c r="W45" s="1">
+      <c r="W45" s="4">
+        <v>0</v>
+      </c>
+      <c r="X45" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="1">
         <v>100</v>
       </c>
-      <c r="AC45" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD45" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:30">
+      <c r="AF45" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG45" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:33">
       <c r="C46" s="1">
         <v>20034</v>
       </c>
@@ -4114,16 +4337,16 @@
         <v>1</v>
       </c>
       <c r="E46" s="1">
-        <v>1003</v>
+        <v>2003</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="I46" s="1">
         <v>0</v>
@@ -4161,25 +4384,41 @@
       <c r="T46" s="1">
         <v>0</v>
       </c>
-      <c r="U46" s="4">
+      <c r="U46" s="1">
         <v>0</v>
       </c>
       <c r="V46" s="1">
         <v>0</v>
       </c>
-      <c r="W46" s="1">
+      <c r="W46" s="4">
+        <v>0</v>
+      </c>
+      <c r="X46" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="1">
         <v>100</v>
       </c>
-      <c r="AC46" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD46" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" customFormat="1" customHeight="1"/>
-    <row r="50" s="2" customFormat="1" customHeight="1"/>
-    <row r="51" customHeight="1" spans="3:30">
+      <c r="AF46" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG46" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" customHeight="1" spans="3:33">
+      <c r="T49" s="1"/>
+      <c r="U49" s="1"/>
+    </row>
+    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:33">
+      <c r="T50" s="1">
+        <v>0</v>
+      </c>
+      <c r="U50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:33">
       <c r="C51" s="1">
         <v>30011</v>
       </c>
@@ -4190,13 +4429,13 @@
         <v>3001</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="I51" s="1">
         <v>0</v>
@@ -4231,29 +4470,29 @@
       <c r="S51" s="1">
         <v>0</v>
       </c>
-      <c r="T51" s="1">
-        <v>0</v>
-      </c>
-      <c r="U51" s="4">
-        <v>0</v>
-      </c>
       <c r="V51" s="1">
         <v>0</v>
       </c>
+      <c r="W51" s="4">
+        <v>0</v>
+      </c>
       <c r="X51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="1">
         <v>33</v>
       </c>
-      <c r="Y51" s="1">
+      <c r="AB51" s="1">
         <v>20</v>
       </c>
-      <c r="AC51" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD51" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:30">
+      <c r="AF51" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG51" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:33">
       <c r="C52" s="1">
         <v>30021</v>
       </c>
@@ -4264,13 +4503,13 @@
         <v>3002</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I52" s="1">
         <v>0</v>
@@ -4308,20 +4547,26 @@
       <c r="T52" s="1">
         <v>0</v>
       </c>
-      <c r="U52" s="4">
+      <c r="U52" s="1">
         <v>0</v>
       </c>
       <c r="V52" s="1">
         <v>0</v>
       </c>
-      <c r="AC52" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD52" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:30">
+      <c r="W52" s="4">
+        <v>0</v>
+      </c>
+      <c r="X52" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG52" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:33">
       <c r="C53" s="1">
         <v>30031</v>
       </c>
@@ -4332,13 +4577,13 @@
         <v>3003</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="I53" s="1">
         <v>0</v>
@@ -4376,29 +4621,35 @@
       <c r="T53" s="1">
         <v>0</v>
       </c>
-      <c r="U53" s="4">
+      <c r="U53" s="1">
         <v>0</v>
       </c>
       <c r="V53" s="1">
         <v>0</v>
       </c>
-      <c r="Z53" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA53" s="4">
+      <c r="W53" s="4">
+        <v>0</v>
+      </c>
+      <c r="X53" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD53" s="4">
         <v>-1</v>
       </c>
-      <c r="AB53" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC53" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD53" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" customHeight="1" spans="3:30">
+      <c r="AE53" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG53" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:33">
       <c r="C54" s="1">
         <v>30041</v>
       </c>
@@ -4409,13 +4660,13 @@
         <v>3004</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="I54" s="1">
         <v>0</v>
@@ -4453,29 +4704,35 @@
       <c r="T54" s="1">
         <v>0</v>
       </c>
-      <c r="U54" s="4">
+      <c r="U54" s="1">
         <v>0</v>
       </c>
       <c r="V54" s="1">
         <v>0</v>
       </c>
-      <c r="Z54" s="1">
+      <c r="W54" s="4">
+        <v>0</v>
+      </c>
+      <c r="X54" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC54" s="1">
         <v>8</v>
       </c>
-      <c r="AA54" s="1">
+      <c r="AD54" s="1">
         <v>100</v>
       </c>
-      <c r="AB54" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC54" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD54" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:30">
+      <c r="AE54" s="1">
+        <v>1</v>
+      </c>
+      <c r="AF54" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG54" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:33">
       <c r="C55" s="1">
         <v>30051</v>
       </c>
@@ -4486,13 +4743,13 @@
         <v>3005</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I55" s="1">
         <v>0</v>
@@ -4530,20 +4787,26 @@
       <c r="T55" s="1">
         <v>0</v>
       </c>
-      <c r="U55" s="4">
+      <c r="U55" s="1">
         <v>0</v>
       </c>
       <c r="V55" s="1">
         <v>0</v>
       </c>
-      <c r="AC55" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD55" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="3:30">
+      <c r="W55" s="4">
+        <v>0</v>
+      </c>
+      <c r="X55" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF55" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG55" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:33">
       <c r="C56" s="1">
         <v>30061</v>
       </c>
@@ -4554,13 +4817,13 @@
         <v>3006</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I56" s="1">
         <v>0</v>
@@ -4598,20 +4861,26 @@
       <c r="T56" s="1">
         <v>0</v>
       </c>
-      <c r="U56" s="4">
+      <c r="U56" s="1">
         <v>0</v>
       </c>
       <c r="V56" s="1">
         <v>0</v>
       </c>
-      <c r="AC56" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD56" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" customHeight="1" spans="3:30">
+      <c r="W56" s="4">
+        <v>0</v>
+      </c>
+      <c r="X56" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF56" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG56" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:33">
       <c r="C57" s="1">
         <v>30071</v>
       </c>
@@ -4622,13 +4891,13 @@
         <v>3007</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I57" s="1">
         <v>0</v>
@@ -4666,20 +4935,26 @@
       <c r="T57" s="1">
         <v>0</v>
       </c>
-      <c r="U57" s="4">
+      <c r="U57" s="1">
         <v>0</v>
       </c>
       <c r="V57" s="1">
         <v>0</v>
       </c>
-      <c r="AC57" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD57" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" customHeight="1" spans="3:30">
+      <c r="W57" s="4">
+        <v>0</v>
+      </c>
+      <c r="X57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF57" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG57" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:33">
       <c r="C59" s="1">
         <v>30012</v>
       </c>
@@ -4690,13 +4965,13 @@
         <v>3001</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="I59" s="1">
         <v>0</v>
@@ -4732,28 +5007,34 @@
         <v>0</v>
       </c>
       <c r="T59" s="1">
-        <v>0</v>
-      </c>
-      <c r="U59" s="4">
+        <v>10</v>
+      </c>
+      <c r="U59" s="1">
         <v>0</v>
       </c>
       <c r="V59" s="1">
         <v>0</v>
       </c>
+      <c r="W59" s="4">
+        <v>0</v>
+      </c>
       <c r="X59" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="1">
         <v>2006</v>
       </c>
-      <c r="Y59" s="1">
-        <v>5</v>
-      </c>
-      <c r="AC59" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD59" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" customHeight="1" spans="3:30">
+      <c r="AB59" s="1">
+        <v>5</v>
+      </c>
+      <c r="AF59" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG59" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:33">
       <c r="C60" s="1">
         <v>30022</v>
       </c>
@@ -4764,13 +5045,13 @@
         <v>3002</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="I60" s="1">
         <v>0</v>
@@ -4806,22 +5087,28 @@
         <v>0</v>
       </c>
       <c r="T60" s="1">
-        <v>0</v>
-      </c>
-      <c r="U60" s="4">
+        <v>10</v>
+      </c>
+      <c r="U60" s="1">
         <v>0</v>
       </c>
       <c r="V60" s="1">
         <v>0</v>
       </c>
-      <c r="AC60" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD60" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="3:30">
+      <c r="W60" s="4">
+        <v>0</v>
+      </c>
+      <c r="X60" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF60" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG60" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:33">
       <c r="C61" s="1">
         <v>30032</v>
       </c>
@@ -4832,13 +5119,13 @@
         <v>3003</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="I61" s="1">
         <v>0</v>
@@ -4874,31 +5161,37 @@
         <v>0</v>
       </c>
       <c r="T61" s="1">
-        <v>0</v>
-      </c>
-      <c r="U61" s="4">
+        <v>10</v>
+      </c>
+      <c r="U61" s="1">
         <v>0</v>
       </c>
       <c r="V61" s="1">
         <v>0</v>
       </c>
-      <c r="Z61" s="1">
+      <c r="W61" s="4">
+        <v>0</v>
+      </c>
+      <c r="X61" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="1">
         <v>6</v>
       </c>
-      <c r="AA61" s="1">
+      <c r="AD61" s="1">
         <v>10</v>
       </c>
-      <c r="AB61" s="1">
+      <c r="AE61" s="1">
         <v>3</v>
       </c>
-      <c r="AC61" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD61" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" customHeight="1" spans="3:30">
+      <c r="AF61" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG61" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:33">
       <c r="C63" s="1">
         <v>30033</v>
       </c>
@@ -4909,13 +5202,13 @@
         <v>3003</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="I63" s="1">
         <v>0</v>
@@ -4950,23 +5243,23 @@
       <c r="S63" s="1">
         <v>0</v>
       </c>
-      <c r="T63" s="1">
-        <v>0</v>
-      </c>
-      <c r="U63" s="4">
-        <v>0</v>
-      </c>
       <c r="V63" s="1">
         <v>0</v>
       </c>
-      <c r="AC63" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD63" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" spans="3:30">
+      <c r="W63" s="4">
+        <v>0</v>
+      </c>
+      <c r="X63" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF63" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG63" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:33">
       <c r="C64" s="1">
         <v>30043</v>
       </c>
@@ -4977,13 +5270,13 @@
         <v>3004</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="I64" s="1">
         <v>0</v>
@@ -5018,32 +5311,32 @@
       <c r="S64" s="1">
         <v>0</v>
       </c>
-      <c r="T64" s="1">
-        <v>0</v>
-      </c>
-      <c r="U64" s="4">
-        <v>0</v>
-      </c>
       <c r="V64" s="1">
         <v>0</v>
       </c>
-      <c r="Z64" s="1">
+      <c r="W64" s="4">
+        <v>0</v>
+      </c>
+      <c r="X64" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="1">
         <v>9</v>
       </c>
-      <c r="AA64" s="1">
+      <c r="AD64" s="1">
         <v>10</v>
       </c>
-      <c r="AB64" s="1">
+      <c r="AE64" s="1">
         <v>3</v>
       </c>
-      <c r="AC64" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD64" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="3:30">
+      <c r="AF64" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG64" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:33">
       <c r="C65" s="1">
         <v>30073</v>
       </c>
@@ -5054,13 +5347,13 @@
         <v>2007</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="I65" s="1">
         <v>0</v>
@@ -5095,26 +5388,26 @@
       <c r="S65" s="1">
         <v>0</v>
       </c>
-      <c r="T65" s="1">
-        <v>0</v>
-      </c>
-      <c r="U65" s="4">
-        <v>0</v>
-      </c>
       <c r="V65" s="1">
         <v>0</v>
       </c>
-      <c r="Z65" s="4">
+      <c r="W65" s="4">
+        <v>0</v>
+      </c>
+      <c r="X65" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="4">
         <v>1001</v>
       </c>
-      <c r="AC65" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD65" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" customHeight="1" spans="3:30">
+      <c r="AF65" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG65" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:33">
       <c r="C67" s="1">
         <v>30024</v>
       </c>
@@ -5125,13 +5418,13 @@
         <v>3002</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="I67" s="1">
         <v>0</v>
@@ -5166,26 +5459,26 @@
       <c r="S67" s="1">
         <v>0</v>
       </c>
-      <c r="T67" s="1">
-        <v>0</v>
-      </c>
-      <c r="U67" s="4">
-        <v>0</v>
-      </c>
       <c r="V67" s="1">
         <v>0</v>
       </c>
-      <c r="W67" s="1">
+      <c r="W67" s="4">
+        <v>0</v>
+      </c>
+      <c r="X67" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z67" s="1">
         <v>100</v>
       </c>
-      <c r="AC67" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD67" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="68" customHeight="1" spans="3:30">
+      <c r="AF67" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG67" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:33">
       <c r="C68" s="1">
         <v>30034</v>
       </c>
@@ -5196,13 +5489,13 @@
         <v>3003</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="I68" s="1">
         <v>0</v>
@@ -5237,22 +5530,22 @@
       <c r="S68" s="1">
         <v>0</v>
       </c>
-      <c r="T68" s="1">
-        <v>0</v>
-      </c>
-      <c r="U68" s="4">
-        <v>0</v>
-      </c>
       <c r="V68" s="1">
         <v>0</v>
       </c>
-      <c r="W68" s="1">
+      <c r="W68" s="4">
+        <v>0</v>
+      </c>
+      <c r="X68" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="1">
         <v>100</v>
       </c>
-      <c r="AC68" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD68" s="1">
+      <c r="AF68" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG68" s="1">
         <v>5</v>
       </c>
     </row>

--- a/Excel/SkillTalentConfig.xlsx
+++ b/Excel/SkillTalentConfig.xlsx
@@ -174,7 +174,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="140">
   <si>
     <t>#</t>
   </si>
@@ -398,6 +398,12 @@
     <t>火麟剑诀</t>
   </si>
   <si>
+    <t>·迅疾</t>
+  </si>
+  <si>
+    <t>施法减少5秒CD</t>
+  </si>
+  <si>
     <t>增加5%物攻增幅</t>
   </si>
   <si>
@@ -419,7 +425,7 @@
     <t>降低敌人20%的攻击速度</t>
   </si>
   <si>
-    <t>削减敌人20%护甲</t>
+    <t>削减敌人50%护甲</t>
   </si>
   <si>
     <t>·斩江</t>
@@ -2351,13 +2357,13 @@
         <v>73</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="I12" s="1">
-        <v>99</v>
+        <v>5</v>
       </c>
       <c r="J12" s="1">
         <v>0</v>
@@ -2438,7 +2444,7 @@
         <v>71</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
@@ -2515,10 +2521,10 @@
         <v>60</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I15" s="1">
         <v>0</v>
@@ -2598,10 +2604,10 @@
         <v>63</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
@@ -2672,10 +2678,10 @@
         <v>66</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
@@ -2758,7 +2764,7 @@
         <v>64</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I18" s="1">
         <v>0</v>
@@ -2806,7 +2812,7 @@
         <v>2</v>
       </c>
       <c r="AD18" s="4">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="AE18" s="4"/>
       <c r="AF18" s="1">
@@ -2838,10 +2844,10 @@
         <v>60</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I20" s="1">
         <v>0</v>
@@ -2912,10 +2918,10 @@
         <v>73</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I21" s="1">
         <v>0</v>
@@ -3004,10 +3010,10 @@
         <v>60</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I23" s="1">
         <v>0</v>
@@ -3075,10 +3081,10 @@
         <v>63</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I24" s="1">
         <v>0</v>
@@ -3154,13 +3160,13 @@
         <v>2001</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I27" s="1">
         <v>0</v>
@@ -3234,7 +3240,7 @@
         <v>2002</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>61</v>
@@ -3308,13 +3314,13 @@
         <v>2003</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>64</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I29" s="1">
         <v>0</v>
@@ -3391,13 +3397,13 @@
         <v>2004</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>64</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I30" s="1">
         <v>0</v>
@@ -3474,7 +3480,7 @@
         <v>2005</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>61</v>
@@ -3542,7 +3548,7 @@
         <v>2006</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>71</v>
@@ -3616,13 +3622,13 @@
         <v>2007</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I33" s="1">
         <v>0</v>
@@ -3707,13 +3713,13 @@
         <v>2001</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I35" s="1">
         <v>0</v>
@@ -3787,13 +3793,13 @@
         <v>2002</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I36" s="1">
         <v>0</v>
@@ -3861,13 +3867,13 @@
         <v>2003</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I37" s="1">
         <v>0</v>
@@ -3935,13 +3941,13 @@
         <v>2007</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I38" s="1">
         <v>0</v>
@@ -4020,13 +4026,13 @@
         <v>2004</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I40" s="1">
         <v>0</v>
@@ -4103,13 +4109,13 @@
         <v>2003</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I41" s="1">
         <v>0</v>
@@ -4186,13 +4192,13 @@
         <v>2004</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I42" s="1">
         <v>0</v>
@@ -4269,13 +4275,13 @@
         <v>2002</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I45" s="1">
         <v>0</v>
@@ -4340,13 +4346,13 @@
         <v>2003</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I46" s="1">
         <v>0</v>
@@ -4429,13 +4435,13 @@
         <v>3001</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I51" s="1">
         <v>0</v>
@@ -4503,7 +4509,7 @@
         <v>3002</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>61</v>
@@ -4577,10 +4583,10 @@
         <v>3003</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>65</v>
@@ -4660,13 +4666,13 @@
         <v>3004</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I54" s="1">
         <v>0</v>
@@ -4743,7 +4749,7 @@
         <v>3005</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>61</v>
@@ -4817,13 +4823,13 @@
         <v>3006</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I56" s="1">
         <v>0</v>
@@ -4891,13 +4897,13 @@
         <v>3007</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I57" s="1">
         <v>0</v>
@@ -4965,13 +4971,13 @@
         <v>3001</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I59" s="1">
         <v>0</v>
@@ -5045,13 +5051,13 @@
         <v>3002</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I60" s="1">
         <v>0</v>
@@ -5119,13 +5125,13 @@
         <v>3003</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I61" s="1">
         <v>0</v>
@@ -5202,13 +5208,13 @@
         <v>3003</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I63" s="1">
         <v>0</v>
@@ -5270,13 +5276,13 @@
         <v>3004</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I64" s="1">
         <v>0</v>
@@ -5347,13 +5353,13 @@
         <v>2007</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I65" s="1">
         <v>0</v>
@@ -5418,13 +5424,13 @@
         <v>3002</v>
       </c>
       <c r="F67" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="G67" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="G67" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="H67" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I67" s="1">
         <v>0</v>
@@ -5489,13 +5495,13 @@
         <v>3003</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I68" s="1">
         <v>0</v>

--- a/Excel/SkillTalentConfig.xlsx
+++ b/Excel/SkillTalentConfig.xlsx
@@ -440,7 +440,7 @@
     <t>额外灼烧敌人20%的伤害，最高3层</t>
   </si>
   <si>
-    <t>·剑心</t>
+    <t>·疾速</t>
   </si>
   <si>
     <t>此技能攻击速度增加100%</t>
@@ -4278,7 +4278,7 @@
         <v>93</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>89</v>
@@ -4349,7 +4349,7 @@
         <v>94</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>89</v>
@@ -5427,7 +5427,7 @@
         <v>119</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>89</v>
@@ -5498,7 +5498,7 @@
         <v>120</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>89</v>

--- a/Excel/SkillTalentConfig.xlsx
+++ b/Excel/SkillTalentConfig.xlsx
@@ -772,12 +772,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3154,7 +3154,7 @@
         <v>20011</v>
       </c>
       <c r="D27" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="4">
         <v>2001</v>
@@ -3234,7 +3234,7 @@
         <v>20021</v>
       </c>
       <c r="D28" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="4">
         <v>2002</v>
@@ -3308,7 +3308,7 @@
         <v>20031</v>
       </c>
       <c r="D29" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="4">
         <v>2003</v>
@@ -3391,7 +3391,7 @@
         <v>20041</v>
       </c>
       <c r="D30" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="4">
         <v>2004</v>
@@ -3474,7 +3474,7 @@
         <v>20051</v>
       </c>
       <c r="D31" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" s="4">
         <v>2005</v>
@@ -3542,7 +3542,7 @@
         <v>20061</v>
       </c>
       <c r="D32" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" s="4">
         <v>2006</v>
@@ -3616,7 +3616,7 @@
         <v>20071</v>
       </c>
       <c r="D33" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="4">
         <v>2007</v>
@@ -3707,7 +3707,7 @@
         <v>20012</v>
       </c>
       <c r="D35" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" s="4">
         <v>2001</v>
@@ -3787,7 +3787,7 @@
         <v>20022</v>
       </c>
       <c r="D36" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" s="1">
         <v>2002</v>
@@ -3861,7 +3861,7 @@
         <v>20032</v>
       </c>
       <c r="D37" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" s="4">
         <v>2003</v>
@@ -3935,7 +3935,7 @@
         <v>20072</v>
       </c>
       <c r="D38" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" s="1">
         <v>2007</v>
@@ -4020,7 +4020,7 @@
         <v>20023</v>
       </c>
       <c r="D40" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" s="1">
         <v>2004</v>
@@ -4103,7 +4103,7 @@
         <v>20033</v>
       </c>
       <c r="D41" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" s="1">
         <v>2003</v>
@@ -4186,7 +4186,7 @@
         <v>20043</v>
       </c>
       <c r="D42" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" s="1">
         <v>2004</v>
@@ -4269,7 +4269,7 @@
         <v>20024</v>
       </c>
       <c r="D45" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" s="1">
         <v>2002</v>
@@ -4340,7 +4340,7 @@
         <v>20034</v>
       </c>
       <c r="D46" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" s="1">
         <v>2003</v>
@@ -4429,7 +4429,7 @@
         <v>30011</v>
       </c>
       <c r="D51" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E51" s="4">
         <v>3001</v>
@@ -4503,7 +4503,7 @@
         <v>30021</v>
       </c>
       <c r="D52" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E52" s="4">
         <v>3002</v>
@@ -4577,7 +4577,7 @@
         <v>30031</v>
       </c>
       <c r="D53" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E53" s="4">
         <v>3003</v>
@@ -4660,7 +4660,7 @@
         <v>30041</v>
       </c>
       <c r="D54" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E54" s="4">
         <v>3004</v>
@@ -4743,7 +4743,7 @@
         <v>30051</v>
       </c>
       <c r="D55" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E55" s="4">
         <v>3005</v>
@@ -4817,7 +4817,7 @@
         <v>30061</v>
       </c>
       <c r="D56" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E56" s="4">
         <v>3006</v>
@@ -4891,7 +4891,7 @@
         <v>30071</v>
       </c>
       <c r="D57" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E57" s="4">
         <v>3007</v>
@@ -4965,7 +4965,7 @@
         <v>30012</v>
       </c>
       <c r="D59" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E59" s="4">
         <v>3001</v>
@@ -5045,7 +5045,7 @@
         <v>30022</v>
       </c>
       <c r="D60" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E60" s="4">
         <v>3002</v>
@@ -5119,7 +5119,7 @@
         <v>30032</v>
       </c>
       <c r="D61" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E61" s="4">
         <v>3003</v>
@@ -5202,7 +5202,7 @@
         <v>30033</v>
       </c>
       <c r="D63" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E63" s="4">
         <v>3003</v>
@@ -5270,7 +5270,7 @@
         <v>30043</v>
       </c>
       <c r="D64" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E64" s="4">
         <v>3004</v>
@@ -5347,7 +5347,7 @@
         <v>30073</v>
       </c>
       <c r="D65" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E65" s="4">
         <v>2007</v>
@@ -5418,7 +5418,7 @@
         <v>30024</v>
       </c>
       <c r="D67" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E67" s="4">
         <v>3002</v>
@@ -5489,7 +5489,7 @@
         <v>30034</v>
       </c>
       <c r="D68" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E68" s="4">
         <v>3003</v>

--- a/Excel/SkillTalentConfig.xlsx
+++ b/Excel/SkillTalentConfig.xlsx
@@ -772,12 +772,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/SkillTalentConfig.xlsx
+++ b/Excel/SkillTalentConfig.xlsx
@@ -359,30 +359,33 @@
     <t>流光剑诀</t>
   </si>
   <si>
+    <t>·灵动</t>
+  </si>
+  <si>
+    <t>减少技能50%冷却时间</t>
+  </si>
+  <si>
+    <t>四方剑阵</t>
+  </si>
+  <si>
+    <t>·破甲</t>
+  </si>
+  <si>
+    <t>每次伤害削减敌人1点护甲，无上限</t>
+  </si>
+  <si>
+    <t>重击剑术</t>
+  </si>
+  <si>
+    <t>削减敌人100点护甲</t>
+  </si>
+  <si>
+    <t>武神盾</t>
+  </si>
+  <si>
     <t>·无断</t>
   </si>
   <si>
-    <t>施法没有CD</t>
-  </si>
-  <si>
-    <t>四方剑阵</t>
-  </si>
-  <si>
-    <t>·破甲</t>
-  </si>
-  <si>
-    <t>每次伤害削减敌人1点护甲，无上限</t>
-  </si>
-  <si>
-    <t>重击剑术</t>
-  </si>
-  <si>
-    <t>削减敌人100点护甲</t>
-  </si>
-  <si>
-    <t>武神盾</t>
-  </si>
-  <si>
     <t>增加30秒持续时间</t>
   </si>
   <si>
@@ -398,10 +401,7 @@
     <t>火麟剑诀</t>
   </si>
   <si>
-    <t>·迅疾</t>
-  </si>
-  <si>
-    <t>施法减少5秒CD</t>
+    <t>减少技能20%冷却时间</t>
   </si>
   <si>
     <t>增加5%物攻增幅</t>
@@ -440,7 +440,7 @@
     <t>额外灼烧敌人20%的伤害，最高3层</t>
   </si>
   <si>
-    <t>·疾速</t>
+    <t>·疾风</t>
   </si>
   <si>
     <t>此技能攻击速度增加100%</t>
@@ -1981,7 +1981,7 @@
         <v>62</v>
       </c>
       <c r="I7" s="1">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="J7" s="1">
         <v>0</v>
@@ -2215,10 +2215,10 @@
         <v>68</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I10" s="1">
         <v>0</v>
@@ -2286,13 +2286,13 @@
         <v>1006</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
@@ -2354,16 +2354,16 @@
         <v>1007</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>75</v>
       </c>
       <c r="I12" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J12" s="1">
         <v>0</v>
@@ -2441,7 +2441,7 @@
         <v>57</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>76</v>
@@ -2758,7 +2758,7 @@
         <v>1007</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>64</v>
@@ -2915,7 +2915,7 @@
         <v>1007</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>86</v>
@@ -3249,7 +3249,7 @@
         <v>62</v>
       </c>
       <c r="I28" s="1">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="J28" s="1">
         <v>0</v>
@@ -3483,10 +3483,10 @@
         <v>98</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I31" s="1">
         <v>0</v>
@@ -3551,10 +3551,10 @@
         <v>99</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I32" s="1">
         <v>0</v>
@@ -4518,7 +4518,7 @@
         <v>62</v>
       </c>
       <c r="I52" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J52" s="1">
         <v>0</v>
@@ -4752,10 +4752,10 @@
         <v>125</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I55" s="1">
         <v>0</v>

--- a/Excel/SkillTalentConfig.xlsx
+++ b/Excel/SkillTalentConfig.xlsx
@@ -174,7 +174,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="139">
   <si>
     <t>#</t>
   </si>
@@ -371,13 +371,13 @@
     <t>·破甲</t>
   </si>
   <si>
-    <t>每次伤害削减敌人1点护甲，无上限</t>
+    <t>每次削减敌人1%护甲，可叠加</t>
   </si>
   <si>
     <t>重击剑术</t>
   </si>
   <si>
-    <t>削减敌人100点护甲</t>
+    <t>削减敌人80%护甲</t>
   </si>
   <si>
     <t>武神盾</t>
@@ -461,13 +461,10 @@
     <t>火海术</t>
   </si>
   <si>
-    <t>每次计算伤害，削减敌人1点护甲</t>
-  </si>
-  <si>
     <t>烈焰术</t>
   </si>
   <si>
-    <t>削减敌人50点护甲，最高3层</t>
+    <t>每次削减敌人20%护甲，叠加3层</t>
   </si>
   <si>
     <t>念力盾</t>
@@ -542,13 +539,16 @@
     <t>·蚀甲</t>
   </si>
   <si>
+    <t>每次削减敌人1%护甲</t>
+  </si>
+  <si>
     <t>疗伤术</t>
   </si>
   <si>
     <t>·御甲</t>
   </si>
   <si>
-    <t>增加100点护甲</t>
+    <t>增加100%护甲</t>
   </si>
   <si>
     <t>护魂盾</t>
@@ -564,9 +564,6 @@
   </si>
   <si>
     <t>·御灵</t>
-  </si>
-  <si>
-    <t>额外多召唤一个</t>
   </si>
   <si>
     <t>·神体</t>
@@ -2735,7 +2732,7 @@
         <v>4</v>
       </c>
       <c r="AD17" s="4">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="AE17" s="4">
         <v>1</v>
@@ -3320,7 +3317,7 @@
         <v>64</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="I29" s="1">
         <v>0</v>
@@ -3397,13 +3394,13 @@
         <v>2004</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>64</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I30" s="1">
         <v>0</v>
@@ -3480,7 +3477,7 @@
         <v>2005</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>69</v>
@@ -3548,7 +3545,7 @@
         <v>2006</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>72</v>
@@ -3622,13 +3619,13 @@
         <v>2007</v>
       </c>
       <c r="F33" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G33" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="H33" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="I33" s="1">
         <v>0</v>
@@ -3716,10 +3713,10 @@
         <v>90</v>
       </c>
       <c r="G35" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="I35" s="1">
         <v>0</v>
@@ -3796,10 +3793,10 @@
         <v>93</v>
       </c>
       <c r="G36" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="I36" s="1">
         <v>0</v>
@@ -3870,10 +3867,10 @@
         <v>94</v>
       </c>
       <c r="G37" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="I37" s="1">
         <v>0</v>
@@ -3941,13 +3938,13 @@
         <v>2007</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G38" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="I38" s="1">
         <v>0</v>
@@ -4026,13 +4023,13 @@
         <v>2004</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G40" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H40" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="I40" s="1">
         <v>0</v>
@@ -4112,10 +4109,10 @@
         <v>94</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I41" s="1">
         <v>0</v>
@@ -4192,13 +4189,13 @@
         <v>2004</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G42" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H42" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="I42" s="1">
         <v>0</v>
@@ -4435,13 +4432,13 @@
         <v>3001</v>
       </c>
       <c r="F51" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G51" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="H51" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="I51" s="1">
         <v>0</v>
@@ -4509,7 +4506,7 @@
         <v>3002</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>61</v>
@@ -4583,13 +4580,13 @@
         <v>3003</v>
       </c>
       <c r="F53" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="G53" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="H53" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="I53" s="1">
         <v>0</v>
@@ -4826,7 +4823,7 @@
         <v>126</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>127</v>
@@ -4903,7 +4900,7 @@
         <v>129</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I57" s="1">
         <v>0</v>
@@ -4971,13 +4968,13 @@
         <v>3001</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G59" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H59" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="I59" s="1">
         <v>0</v>
@@ -5051,13 +5048,13 @@
         <v>3002</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I60" s="1">
         <v>0</v>
@@ -5125,13 +5122,13 @@
         <v>3003</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I61" s="1">
         <v>0</v>
@@ -5208,13 +5205,13 @@
         <v>3003</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G63" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="H63" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="I63" s="1">
         <v>0</v>
@@ -5279,10 +5276,10 @@
         <v>122</v>
       </c>
       <c r="G64" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H64" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="I64" s="1">
         <v>0</v>
@@ -5356,10 +5353,10 @@
         <v>128</v>
       </c>
       <c r="G65" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H65" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>139</v>
       </c>
       <c r="I65" s="1">
         <v>0</v>
@@ -5424,7 +5421,7 @@
         <v>3002</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>88</v>
@@ -5495,7 +5492,7 @@
         <v>3003</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>88</v>

--- a/Excel/SkillTalentConfig.xlsx
+++ b/Excel/SkillTalentConfig.xlsx
@@ -422,7 +422,7 @@
     <t>·致残</t>
   </si>
   <si>
-    <t>降低敌人20%的攻击速度</t>
+    <t>降低敌人50%的攻击速度</t>
   </si>
   <si>
     <t>削减敌人50%护甲</t>
@@ -494,16 +494,16 @@
     <t>额外攻击一个敌人</t>
   </si>
   <si>
-    <t>·炼狱</t>
+    <t>·火狱</t>
   </si>
   <si>
     <t>火海的攻击范围增加一行一列</t>
   </si>
   <si>
-    <t>·蚀魂</t>
-  </si>
-  <si>
-    <t>敌人额外承受20%伤害，最高3层</t>
+    <t>·冰狱</t>
+  </si>
+  <si>
+    <t>冰封的攻击范围增加一行一列</t>
   </si>
   <si>
     <t>·燃魂</t>
@@ -2324,6 +2324,12 @@
       <c r="S11" s="1">
         <v>0</v>
       </c>
+      <c r="T11" s="1">
+        <v>0</v>
+      </c>
+      <c r="U11" s="1">
+        <v>0</v>
+      </c>
       <c r="V11" s="1">
         <v>0</v>
       </c>
@@ -2416,12 +2422,6 @@
     </row>
     <row r="13" customHeight="1" spans="3:33">
       <c r="F13" s="4"/>
-      <c r="T13" s="1">
-        <v>0</v>
-      </c>
-      <c r="U13" s="1">
-        <v>0</v>
-      </c>
       <c r="W13" s="4"/>
     </row>
     <row r="14" customHeight="1" spans="3:33">
@@ -2796,6 +2796,12 @@
       <c r="S18" s="1">
         <v>0</v>
       </c>
+      <c r="T18" s="1">
+        <v>0</v>
+      </c>
+      <c r="U18" s="1">
+        <v>0</v>
+      </c>
       <c r="V18" s="1">
         <v>0</v>
       </c>
@@ -2817,14 +2823,6 @@
       </c>
       <c r="AG18" s="1">
         <v>5</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:33">
-      <c r="T19" s="1">
-        <v>10</v>
-      </c>
-      <c r="U19" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:33">
@@ -2880,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="T20" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U20" s="1">
         <v>0</v>
@@ -2954,7 +2952,7 @@
         <v>0</v>
       </c>
       <c r="T21" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U21" s="1">
         <v>0</v>
@@ -2976,12 +2974,6 @@
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:33">
-      <c r="T22" s="1">
-        <v>10</v>
-      </c>
-      <c r="U22" s="1">
-        <v>0</v>
-      </c>
       <c r="W22" s="4"/>
       <c r="AC22" s="1">
         <v>5</v>
@@ -3045,6 +3037,12 @@
       <c r="S23" s="1">
         <v>0</v>
       </c>
+      <c r="T23" s="1">
+        <v>0</v>
+      </c>
+      <c r="U23" s="1">
+        <v>0</v>
+      </c>
       <c r="V23" s="1">
         <v>0</v>
       </c>
@@ -3116,6 +3114,12 @@
       <c r="S24" s="1">
         <v>0</v>
       </c>
+      <c r="T24" s="1">
+        <v>0</v>
+      </c>
+      <c r="U24" s="1">
+        <v>0</v>
+      </c>
       <c r="V24" s="1">
         <v>0</v>
       </c>
@@ -3138,14 +3142,7 @@
     <row r="25" customHeight="1" spans="3:33">
       <c r="W25" s="4"/>
     </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:33">
-      <c r="T26" s="1">
-        <v>0</v>
-      </c>
-      <c r="U26" s="1">
-        <v>0</v>
-      </c>
-    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1"/>
     <row r="27" customHeight="1" spans="3:33">
       <c r="C27" s="1">
         <v>20011</v>
@@ -3518,6 +3515,12 @@
       <c r="S31" s="1">
         <v>0</v>
       </c>
+      <c r="T31" s="1">
+        <v>0</v>
+      </c>
+      <c r="U31" s="1">
+        <v>0</v>
+      </c>
       <c r="V31" s="1">
         <v>0</v>
       </c>
@@ -3681,7 +3684,9 @@
       <c r="AD33" s="4">
         <v>10</v>
       </c>
-      <c r="AE33" s="4"/>
+      <c r="AE33" s="4">
+        <v>3</v>
+      </c>
       <c r="AF33" s="1">
         <v>1</v>
       </c>
@@ -3691,12 +3696,6 @@
     </row>
     <row r="34" customHeight="1" spans="3:33">
       <c r="F34" s="4"/>
-      <c r="T34" s="1">
-        <v>0</v>
-      </c>
-      <c r="U34" s="1">
-        <v>0</v>
-      </c>
       <c r="W34" s="4"/>
     </row>
     <row r="35" customHeight="1" spans="3:33">
@@ -3959,10 +3958,10 @@
         <v>0</v>
       </c>
       <c r="M38" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O38" s="1">
         <v>0</v>
@@ -3979,6 +3978,12 @@
       <c r="S38" s="1">
         <v>0</v>
       </c>
+      <c r="T38" s="1">
+        <v>0</v>
+      </c>
+      <c r="U38" s="1">
+        <v>0</v>
+      </c>
       <c r="V38" s="1">
         <v>0</v>
       </c>
@@ -3988,25 +3993,17 @@
       <c r="X38" s="1">
         <v>0</v>
       </c>
-      <c r="AC38" s="1">
-        <v>6</v>
-      </c>
-      <c r="AD38" s="4">
-        <v>20</v>
-      </c>
-      <c r="AE38" s="1">
-        <v>3</v>
-      </c>
-      <c r="AF38" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG38" s="1">
-        <v>5</v>
-      </c>
+      <c r="AD38" s="4"/>
     </row>
     <row r="39" customHeight="1" spans="3:33">
+      <c r="R39" s="1">
+        <v>0</v>
+      </c>
+      <c r="S39" s="1">
+        <v>0</v>
+      </c>
       <c r="T39" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U39" s="1">
         <v>0</v>
@@ -4065,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="T40" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U40" s="1">
         <v>0</v>
@@ -4148,7 +4145,7 @@
         <v>0</v>
       </c>
       <c r="T41" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U41" s="1">
         <v>0</v>
@@ -4186,7 +4183,7 @@
         <v>2</v>
       </c>
       <c r="E42" s="1">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>99</v>
@@ -4231,7 +4228,7 @@
         <v>0</v>
       </c>
       <c r="T42" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U42" s="1">
         <v>0</v>
@@ -4313,6 +4310,12 @@
       <c r="S45" s="1">
         <v>0</v>
       </c>
+      <c r="T45" s="1">
+        <v>0</v>
+      </c>
+      <c r="U45" s="1">
+        <v>0</v>
+      </c>
       <c r="V45" s="1">
         <v>0</v>
       </c>
@@ -4413,14 +4416,7 @@
       <c r="T49" s="1"/>
       <c r="U49" s="1"/>
     </row>
-    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:33">
-      <c r="T50" s="1">
-        <v>0</v>
-      </c>
-      <c r="U50" s="1">
-        <v>0</v>
-      </c>
-    </row>
+    <row r="50" s="2" customFormat="1" customHeight="1"/>
     <row r="51" customHeight="1" spans="3:33">
       <c r="C51" s="1">
         <v>30011</v>
@@ -4473,6 +4469,12 @@
       <c r="S51" s="1">
         <v>0</v>
       </c>
+      <c r="T51" s="1">
+        <v>0</v>
+      </c>
+      <c r="U51" s="1">
+        <v>0</v>
+      </c>
       <c r="V51" s="1">
         <v>0</v>
       </c>
@@ -5010,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="T59" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U59" s="1">
         <v>0</v>
@@ -5090,7 +5092,7 @@
         <v>0</v>
       </c>
       <c r="T60" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U60" s="1">
         <v>0</v>
@@ -5164,7 +5166,7 @@
         <v>0</v>
       </c>
       <c r="T61" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U61" s="1">
         <v>0</v>
@@ -5246,6 +5248,12 @@
       <c r="S63" s="1">
         <v>0</v>
       </c>
+      <c r="T63" s="1">
+        <v>0</v>
+      </c>
+      <c r="U63" s="1">
+        <v>0</v>
+      </c>
       <c r="V63" s="1">
         <v>0</v>
       </c>
@@ -5314,6 +5322,12 @@
       <c r="S64" s="1">
         <v>0</v>
       </c>
+      <c r="T64" s="1">
+        <v>0</v>
+      </c>
+      <c r="U64" s="1">
+        <v>0</v>
+      </c>
       <c r="V64" s="1">
         <v>0</v>
       </c>
@@ -5347,7 +5361,7 @@
         <v>3</v>
       </c>
       <c r="E65" s="4">
-        <v>2007</v>
+        <v>3007</v>
       </c>
       <c r="F65" s="4" t="s">
         <v>128</v>
@@ -5389,6 +5403,12 @@
         <v>0</v>
       </c>
       <c r="S65" s="1">
+        <v>0</v>
+      </c>
+      <c r="T65" s="1">
+        <v>0</v>
+      </c>
+      <c r="U65" s="1">
         <v>0</v>
       </c>
       <c r="V65" s="1">
@@ -5462,6 +5482,12 @@
       <c r="S67" s="1">
         <v>0</v>
       </c>
+      <c r="T67" s="1">
+        <v>0</v>
+      </c>
+      <c r="U67" s="1">
+        <v>0</v>
+      </c>
       <c r="V67" s="1">
         <v>0</v>
       </c>
@@ -5531,6 +5557,12 @@
         <v>0</v>
       </c>
       <c r="S68" s="1">
+        <v>0</v>
+      </c>
+      <c r="T68" s="1">
+        <v>0</v>
+      </c>
+      <c r="U68" s="1">
         <v>0</v>
       </c>
       <c r="V68" s="1">

--- a/Excel/SkillTalentConfig.xlsx
+++ b/Excel/SkillTalentConfig.xlsx
@@ -174,7 +174,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="138">
   <si>
     <t>#</t>
   </si>
@@ -365,22 +365,22 @@
     <t>减少技能50%冷却时间</t>
   </si>
   <si>
-    <t>四方剑阵</t>
+    <t>月华剑阵</t>
   </si>
   <si>
     <t>·破甲</t>
   </si>
   <si>
-    <t>每次削减敌人1%护甲，可叠加</t>
-  </si>
-  <si>
-    <t>重击剑术</t>
-  </si>
-  <si>
-    <t>削减敌人80%护甲</t>
-  </si>
-  <si>
-    <t>武神盾</t>
+    <t>每次削减敌人1%护甲倍率，最高90层</t>
+  </si>
+  <si>
+    <t>蛮牛冲撞</t>
+  </si>
+  <si>
+    <t>削减敌人80%护甲倍率</t>
+  </si>
+  <si>
+    <t>龙魂护体</t>
   </si>
   <si>
     <t>·无断</t>
@@ -425,7 +425,7 @@
     <t>降低敌人50%的攻击速度</t>
   </si>
   <si>
-    <t>削减敌人50%护甲</t>
+    <t>削减敌人50%护甲倍率</t>
   </si>
   <si>
     <t>·斩江</t>
@@ -455,25 +455,25 @@
     <t>增加{0}%魔法伤害</t>
   </si>
   <si>
-    <t>神雷术</t>
-  </si>
-  <si>
-    <t>火海术</t>
-  </si>
-  <si>
-    <t>烈焰术</t>
-  </si>
-  <si>
-    <t>每次削减敌人20%护甲，叠加3层</t>
-  </si>
-  <si>
-    <t>念力盾</t>
-  </si>
-  <si>
-    <t>冰心诀</t>
-  </si>
-  <si>
-    <t>冰封术</t>
+    <t>紫电神雷</t>
+  </si>
+  <si>
+    <t>火狱阵法</t>
+  </si>
+  <si>
+    <t>烈焰焚天</t>
+  </si>
+  <si>
+    <t>每次削减敌人20%护甲倍率，叠加3层</t>
+  </si>
+  <si>
+    <t>炎凰法盾</t>
+  </si>
+  <si>
+    <t>万法归宗</t>
+  </si>
+  <si>
+    <t>极寒冰暴</t>
   </si>
   <si>
     <t>·霜寒</t>
@@ -506,22 +506,22 @@
     <t>冰封的攻击范围增加一行一列</t>
   </si>
   <si>
+    <t>·蚀骨</t>
+  </si>
+  <si>
     <t>·燃魂</t>
   </si>
   <si>
     <t>自己个额外增加5%伤害，最高3层</t>
   </si>
   <si>
-    <t>·蚀骨</t>
-  </si>
-  <si>
     <t>·冻结</t>
   </si>
   <si>
-    <t>敌人降低20%的攻击速度</t>
-  </si>
-  <si>
-    <t>祈福心法</t>
+    <t>敌人降低30%的攻击速度</t>
+  </si>
+  <si>
+    <t>清心咒</t>
   </si>
   <si>
     <t>·道体</t>
@@ -530,7 +530,7 @@
     <t>增加{0}%道术伤害</t>
   </si>
   <si>
-    <t>灭魔符</t>
+    <t>破魔符咒</t>
   </si>
   <si>
     <t>毒咒术</t>
@@ -539,28 +539,25 @@
     <t>·蚀甲</t>
   </si>
   <si>
-    <t>每次削减敌人1%护甲</t>
-  </si>
-  <si>
-    <t>疗伤术</t>
+    <t>圣疗术</t>
   </si>
   <si>
     <t>·御甲</t>
   </si>
   <si>
-    <t>增加100%护甲</t>
-  </si>
-  <si>
-    <t>护魂盾</t>
-  </si>
-  <si>
-    <t>圣心诀</t>
+    <t>增加100%护甲倍率</t>
+  </si>
+  <si>
+    <t>太虚麟盾</t>
+  </si>
+  <si>
+    <t>道法自然</t>
   </si>
   <si>
     <t>增加{0}%系数增幅</t>
   </si>
   <si>
-    <t>唤神咒</t>
+    <t>召唤英灵</t>
   </si>
   <si>
     <t>·御灵</t>
@@ -1567,7 +1564,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:AG68"/>
+  <dimension ref="C1:AG67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="6" width="9" style="1"/>
@@ -2103,10 +2100,10 @@
         <v>1</v>
       </c>
       <c r="AD8" s="4">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="4">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AF8" s="1">
         <v>1</v>
@@ -2186,10 +2183,10 @@
         <v>1</v>
       </c>
       <c r="AD9" s="4">
-        <v>-100</v>
+        <v>80</v>
       </c>
       <c r="AE9" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF9" s="1">
         <v>1</v>
@@ -2812,7 +2809,7 @@
         <v>0</v>
       </c>
       <c r="AC18" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD18" s="4">
         <v>50</v>
@@ -3368,10 +3365,10 @@
         <v>1</v>
       </c>
       <c r="AD29" s="1">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AE29" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AF29" s="1">
         <v>1</v>
@@ -3448,13 +3445,13 @@
         <v>0</v>
       </c>
       <c r="AC30" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD30" s="1">
-        <v>-50</v>
+        <v>20</v>
       </c>
       <c r="AE30" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AF30" s="1">
         <v>1</v>
@@ -4011,22 +4008,22 @@
     </row>
     <row r="40" customHeight="1" spans="3:33">
       <c r="C40" s="1">
-        <v>20023</v>
+        <v>20033</v>
       </c>
       <c r="D40" s="1">
         <v>2</v>
       </c>
       <c r="E40" s="1">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>110</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="I40" s="1">
         <v>0</v>
@@ -4077,10 +4074,10 @@
         <v>0</v>
       </c>
       <c r="AC40" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD40" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE40" s="1">
         <v>3</v>
@@ -4094,23 +4091,23 @@
     </row>
     <row r="41" customHeight="1" spans="3:33">
       <c r="C41" s="1">
-        <v>20033</v>
+        <v>20043</v>
       </c>
       <c r="D41" s="1">
         <v>2</v>
       </c>
       <c r="E41" s="1">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G41" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H41" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="I41" s="1">
         <v>0</v>
       </c>
@@ -4160,10 +4157,10 @@
         <v>0</v>
       </c>
       <c r="AC41" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD41" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE41" s="1">
         <v>3</v>
@@ -4177,7 +4174,7 @@
     </row>
     <row r="42" customHeight="1" spans="3:33">
       <c r="C42" s="1">
-        <v>20043</v>
+        <v>20073</v>
       </c>
       <c r="D42" s="1">
         <v>2</v>
@@ -4246,7 +4243,7 @@
         <v>4</v>
       </c>
       <c r="AD42" s="4">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="AE42" s="4">
         <v>1</v>
@@ -4255,21 +4252,98 @@
         <v>1</v>
       </c>
       <c r="AG42" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:33">
+      <c r="C44" s="1">
+        <v>20024</v>
+      </c>
+      <c r="D44" s="1">
+        <v>2</v>
+      </c>
+      <c r="E44" s="1">
+        <v>2002</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I44" s="1">
+        <v>0</v>
+      </c>
+      <c r="J44" s="1">
+        <v>0</v>
+      </c>
+      <c r="K44" s="1">
+        <v>1</v>
+      </c>
+      <c r="L44" s="1">
+        <v>0</v>
+      </c>
+      <c r="M44" s="1">
+        <v>0</v>
+      </c>
+      <c r="N44" s="1">
+        <v>0</v>
+      </c>
+      <c r="O44" s="1">
+        <v>0</v>
+      </c>
+      <c r="P44" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>0</v>
+      </c>
+      <c r="R44" s="1">
+        <v>0</v>
+      </c>
+      <c r="S44" s="1">
+        <v>0</v>
+      </c>
+      <c r="T44" s="1">
+        <v>0</v>
+      </c>
+      <c r="U44" s="1">
+        <v>0</v>
+      </c>
+      <c r="V44" s="1">
+        <v>0</v>
+      </c>
+      <c r="W44" s="4">
+        <v>0</v>
+      </c>
+      <c r="X44" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="1">
+        <v>100</v>
+      </c>
+      <c r="AF44" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG44" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:33">
       <c r="C45" s="1">
-        <v>20024</v>
+        <v>20034</v>
       </c>
       <c r="D45" s="1">
         <v>2</v>
       </c>
       <c r="E45" s="1">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>88</v>
@@ -4284,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="K45" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" s="1">
         <v>0</v>
@@ -4335,109 +4409,112 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" customHeight="1" spans="3:33">
-      <c r="C46" s="1">
-        <v>20034</v>
-      </c>
-      <c r="D46" s="1">
-        <v>2</v>
-      </c>
-      <c r="E46" s="1">
-        <v>2003</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="I46" s="1">
-        <v>0</v>
-      </c>
-      <c r="J46" s="1">
-        <v>0</v>
-      </c>
-      <c r="K46" s="1">
-        <v>0</v>
-      </c>
-      <c r="L46" s="1">
-        <v>0</v>
-      </c>
-      <c r="M46" s="1">
-        <v>0</v>
-      </c>
-      <c r="N46" s="1">
-        <v>0</v>
-      </c>
-      <c r="O46" s="1">
-        <v>0</v>
-      </c>
-      <c r="P46" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="1">
-        <v>0</v>
-      </c>
-      <c r="R46" s="1">
-        <v>0</v>
-      </c>
-      <c r="S46" s="1">
-        <v>0</v>
-      </c>
-      <c r="T46" s="1">
-        <v>0</v>
-      </c>
-      <c r="U46" s="1">
-        <v>0</v>
-      </c>
-      <c r="V46" s="1">
-        <v>0</v>
-      </c>
-      <c r="W46" s="4">
-        <v>0</v>
-      </c>
-      <c r="X46" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z46" s="1">
-        <v>100</v>
-      </c>
-      <c r="AF46" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG46" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" customFormat="1" customHeight="1" spans="3:33">
-      <c r="T49" s="1"/>
-      <c r="U49" s="1"/>
-    </row>
-    <row r="50" s="2" customFormat="1" customHeight="1"/>
+    <row r="48" customFormat="1" customHeight="1" spans="3:33">
+      <c r="T48" s="1"/>
+      <c r="U48" s="1"/>
+    </row>
+    <row r="49" s="2" customFormat="1" customHeight="1"/>
+    <row r="50" customHeight="1" spans="3:33">
+      <c r="C50" s="1">
+        <v>30011</v>
+      </c>
+      <c r="D50" s="1">
+        <v>3</v>
+      </c>
+      <c r="E50" s="4">
+        <v>3001</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I50" s="1">
+        <v>0</v>
+      </c>
+      <c r="J50" s="1">
+        <v>0</v>
+      </c>
+      <c r="K50" s="1">
+        <v>0</v>
+      </c>
+      <c r="L50" s="1">
+        <v>0</v>
+      </c>
+      <c r="M50" s="1">
+        <v>0</v>
+      </c>
+      <c r="N50" s="1">
+        <v>0</v>
+      </c>
+      <c r="O50" s="1">
+        <v>5</v>
+      </c>
+      <c r="P50" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="1">
+        <v>0</v>
+      </c>
+      <c r="R50" s="1">
+        <v>0</v>
+      </c>
+      <c r="S50" s="1">
+        <v>0</v>
+      </c>
+      <c r="T50" s="1">
+        <v>0</v>
+      </c>
+      <c r="U50" s="1">
+        <v>0</v>
+      </c>
+      <c r="V50" s="1">
+        <v>0</v>
+      </c>
+      <c r="W50" s="4">
+        <v>0</v>
+      </c>
+      <c r="X50" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="1">
+        <v>33</v>
+      </c>
+      <c r="AB50" s="1">
+        <v>20</v>
+      </c>
+      <c r="AF50" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG50" s="1">
+        <v>5</v>
+      </c>
+    </row>
     <row r="51" customHeight="1" spans="3:33">
       <c r="C51" s="1">
-        <v>30011</v>
+        <v>30021</v>
       </c>
       <c r="D51" s="1">
         <v>3</v>
       </c>
       <c r="E51" s="4">
-        <v>3001</v>
+        <v>3002</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>116</v>
+        <v>61</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>117</v>
+        <v>62</v>
       </c>
       <c r="I51" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J51" s="1">
         <v>0</v>
@@ -4455,7 +4532,7 @@
         <v>0</v>
       </c>
       <c r="O51" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P51" s="1">
         <v>0</v>
@@ -4483,12 +4560,6 @@
       </c>
       <c r="X51" s="1">
         <v>0</v>
-      </c>
-      <c r="AA51" s="1">
-        <v>33</v>
-      </c>
-      <c r="AB51" s="1">
-        <v>20</v>
       </c>
       <c r="AF51" s="1">
         <v>1</v>
@@ -4499,25 +4570,25 @@
     </row>
     <row r="52" customHeight="1" spans="3:33">
       <c r="C52" s="1">
-        <v>30021</v>
+        <v>30031</v>
       </c>
       <c r="D52" s="1">
         <v>3</v>
       </c>
       <c r="E52" s="4">
-        <v>3002</v>
+        <v>3003</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>61</v>
+        <v>120</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I52" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J52" s="1">
         <v>0</v>
@@ -4563,6 +4634,15 @@
       </c>
       <c r="X52" s="1">
         <v>0</v>
+      </c>
+      <c r="AC52" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD52" s="4">
+        <v>1</v>
+      </c>
+      <c r="AE52" s="4">
+        <v>90</v>
       </c>
       <c r="AF52" s="1">
         <v>1</v>
@@ -4573,22 +4653,22 @@
     </row>
     <row r="53" customHeight="1" spans="3:33">
       <c r="C53" s="1">
-        <v>30031</v>
+        <v>30041</v>
       </c>
       <c r="D53" s="1">
         <v>3</v>
       </c>
       <c r="E53" s="4">
-        <v>3003</v>
+        <v>3004</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I53" s="1">
         <v>0</v>
@@ -4639,13 +4719,13 @@
         <v>0</v>
       </c>
       <c r="AC53" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD53" s="4">
-        <v>-1</v>
-      </c>
-      <c r="AE53" s="4">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="AD53" s="1">
+        <v>100</v>
+      </c>
+      <c r="AE53" s="1">
+        <v>1</v>
       </c>
       <c r="AF53" s="1">
         <v>1</v>
@@ -4656,22 +4736,22 @@
     </row>
     <row r="54" customHeight="1" spans="3:33">
       <c r="C54" s="1">
-        <v>30041</v>
+        <v>30051</v>
       </c>
       <c r="D54" s="1">
         <v>3</v>
       </c>
       <c r="E54" s="4">
-        <v>3004</v>
+        <v>3005</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="I54" s="1">
         <v>0</v>
@@ -4720,15 +4800,6 @@
       </c>
       <c r="X54" s="1">
         <v>0</v>
-      </c>
-      <c r="AC54" s="1">
-        <v>8</v>
-      </c>
-      <c r="AD54" s="1">
-        <v>100</v>
-      </c>
-      <c r="AE54" s="1">
-        <v>1</v>
       </c>
       <c r="AF54" s="1">
         <v>1</v>
@@ -4739,22 +4810,22 @@
     </row>
     <row r="55" customHeight="1" spans="3:33">
       <c r="C55" s="1">
-        <v>30051</v>
+        <v>30061</v>
       </c>
       <c r="D55" s="1">
         <v>3</v>
       </c>
       <c r="E55" s="4">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>125</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="I55" s="1">
         <v>0</v>
@@ -4775,7 +4846,7 @@
         <v>0</v>
       </c>
       <c r="O55" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P55" s="1">
         <v>0</v>
@@ -4813,23 +4884,23 @@
     </row>
     <row r="56" customHeight="1" spans="3:33">
       <c r="C56" s="1">
-        <v>30061</v>
+        <v>30071</v>
       </c>
       <c r="D56" s="1">
         <v>3</v>
       </c>
       <c r="E56" s="4">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="F56" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H56" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G56" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="I56" s="1">
         <v>0</v>
       </c>
@@ -4840,7 +4911,7 @@
         <v>0</v>
       </c>
       <c r="L56" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="1">
         <v>0</v>
@@ -4849,7 +4920,7 @@
         <v>0</v>
       </c>
       <c r="O56" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P56" s="1">
         <v>0</v>
@@ -4885,98 +4956,104 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" customHeight="1" spans="3:33">
-      <c r="C57" s="1">
-        <v>30071</v>
-      </c>
-      <c r="D57" s="1">
+    <row r="58" customHeight="1" spans="3:33">
+      <c r="C58" s="1">
+        <v>30012</v>
+      </c>
+      <c r="D58" s="1">
         <v>3</v>
       </c>
-      <c r="E57" s="4">
-        <v>3007</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="G57" s="1" t="s">
+      <c r="E58" s="4">
+        <v>3001</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G58" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="H57" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="I57" s="1">
-        <v>0</v>
-      </c>
-      <c r="J57" s="1">
-        <v>0</v>
-      </c>
-      <c r="K57" s="1">
-        <v>0</v>
-      </c>
-      <c r="L57" s="1">
-        <v>1</v>
-      </c>
-      <c r="M57" s="1">
-        <v>0</v>
-      </c>
-      <c r="N57" s="1">
-        <v>0</v>
-      </c>
-      <c r="O57" s="1">
-        <v>0</v>
-      </c>
-      <c r="P57" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="1">
-        <v>0</v>
-      </c>
-      <c r="R57" s="1">
-        <v>0</v>
-      </c>
-      <c r="S57" s="1">
-        <v>0</v>
-      </c>
-      <c r="T57" s="1">
-        <v>0</v>
-      </c>
-      <c r="U57" s="1">
-        <v>0</v>
-      </c>
-      <c r="V57" s="1">
-        <v>0</v>
-      </c>
-      <c r="W57" s="4">
-        <v>0</v>
-      </c>
-      <c r="X57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF57" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG57" s="1">
+      <c r="H58" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I58" s="1">
+        <v>0</v>
+      </c>
+      <c r="J58" s="1">
+        <v>0</v>
+      </c>
+      <c r="K58" s="1">
+        <v>0</v>
+      </c>
+      <c r="L58" s="1">
+        <v>0</v>
+      </c>
+      <c r="M58" s="1">
+        <v>0</v>
+      </c>
+      <c r="N58" s="1">
+        <v>0</v>
+      </c>
+      <c r="O58" s="1">
+        <v>5</v>
+      </c>
+      <c r="P58" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="1">
+        <v>0</v>
+      </c>
+      <c r="R58" s="1">
+        <v>0</v>
+      </c>
+      <c r="S58" s="1">
+        <v>0</v>
+      </c>
+      <c r="T58" s="1">
+        <v>0</v>
+      </c>
+      <c r="U58" s="1">
+        <v>0</v>
+      </c>
+      <c r="V58" s="1">
+        <v>0</v>
+      </c>
+      <c r="W58" s="4">
+        <v>0</v>
+      </c>
+      <c r="X58" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="1">
+        <v>2006</v>
+      </c>
+      <c r="AB58" s="1">
+        <v>5</v>
+      </c>
+      <c r="AF58" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG58" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:33">
       <c r="C59" s="1">
-        <v>30012</v>
+        <v>30022</v>
       </c>
       <c r="D59" s="1">
         <v>3</v>
       </c>
       <c r="E59" s="4">
-        <v>3001</v>
+        <v>3002</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="I59" s="1">
         <v>0</v>
@@ -4988,7 +5065,7 @@
         <v>0</v>
       </c>
       <c r="L59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="1">
         <v>0</v>
@@ -4997,7 +5074,7 @@
         <v>0</v>
       </c>
       <c r="O59" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P59" s="1">
         <v>0</v>
@@ -5025,12 +5102,6 @@
       </c>
       <c r="X59" s="1">
         <v>0</v>
-      </c>
-      <c r="AA59" s="1">
-        <v>2006</v>
-      </c>
-      <c r="AB59" s="1">
-        <v>5</v>
       </c>
       <c r="AF59" s="1">
         <v>1</v>
@@ -5041,179 +5112,179 @@
     </row>
     <row r="60" customHeight="1" spans="3:33">
       <c r="C60" s="1">
-        <v>30022</v>
+        <v>30032</v>
       </c>
       <c r="D60" s="1">
         <v>3</v>
       </c>
       <c r="E60" s="4">
-        <v>3002</v>
+        <v>3003</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G60" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="I60" s="1">
+        <v>0</v>
+      </c>
+      <c r="J60" s="1">
+        <v>0</v>
+      </c>
+      <c r="K60" s="1">
+        <v>0</v>
+      </c>
+      <c r="L60" s="1">
+        <v>0</v>
+      </c>
+      <c r="M60" s="1">
+        <v>0</v>
+      </c>
+      <c r="N60" s="1">
+        <v>0</v>
+      </c>
+      <c r="O60" s="1">
+        <v>0</v>
+      </c>
+      <c r="P60" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="1">
+        <v>0</v>
+      </c>
+      <c r="R60" s="1">
+        <v>0</v>
+      </c>
+      <c r="S60" s="1">
+        <v>0</v>
+      </c>
+      <c r="T60" s="1">
+        <v>0</v>
+      </c>
+      <c r="U60" s="1">
+        <v>0</v>
+      </c>
+      <c r="V60" s="1">
+        <v>0</v>
+      </c>
+      <c r="W60" s="4">
+        <v>0</v>
+      </c>
+      <c r="X60" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="1">
+        <v>6</v>
+      </c>
+      <c r="AD60" s="1">
+        <v>10</v>
+      </c>
+      <c r="AE60" s="1">
+        <v>3</v>
+      </c>
+      <c r="AF60" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG60" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:33">
+      <c r="C62" s="1">
+        <v>30033</v>
+      </c>
+      <c r="D62" s="1">
+        <v>3</v>
+      </c>
+      <c r="E62" s="4">
+        <v>3003</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="G62" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="H60" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="I60" s="1">
-        <v>0</v>
-      </c>
-      <c r="J60" s="1">
-        <v>0</v>
-      </c>
-      <c r="K60" s="1">
-        <v>0</v>
-      </c>
-      <c r="L60" s="1">
-        <v>1</v>
-      </c>
-      <c r="M60" s="1">
-        <v>0</v>
-      </c>
-      <c r="N60" s="1">
-        <v>0</v>
-      </c>
-      <c r="O60" s="1">
-        <v>0</v>
-      </c>
-      <c r="P60" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="1">
-        <v>0</v>
-      </c>
-      <c r="R60" s="1">
-        <v>0</v>
-      </c>
-      <c r="S60" s="1">
-        <v>0</v>
-      </c>
-      <c r="T60" s="1">
-        <v>0</v>
-      </c>
-      <c r="U60" s="1">
-        <v>0</v>
-      </c>
-      <c r="V60" s="1">
-        <v>0</v>
-      </c>
-      <c r="W60" s="4">
-        <v>0</v>
-      </c>
-      <c r="X60" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF60" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG60" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="3:33">
-      <c r="C61" s="1">
-        <v>30032</v>
-      </c>
-      <c r="D61" s="1">
+      <c r="H62" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I62" s="1">
+        <v>0</v>
+      </c>
+      <c r="J62" s="1">
+        <v>0</v>
+      </c>
+      <c r="K62" s="1">
+        <v>0</v>
+      </c>
+      <c r="L62" s="1">
         <v>3</v>
       </c>
-      <c r="E61" s="4">
-        <v>3003</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="I61" s="1">
-        <v>0</v>
-      </c>
-      <c r="J61" s="1">
-        <v>0</v>
-      </c>
-      <c r="K61" s="1">
-        <v>0</v>
-      </c>
-      <c r="L61" s="1">
-        <v>0</v>
-      </c>
-      <c r="M61" s="1">
-        <v>0</v>
-      </c>
-      <c r="N61" s="1">
-        <v>0</v>
-      </c>
-      <c r="O61" s="1">
-        <v>0</v>
-      </c>
-      <c r="P61" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="1">
-        <v>0</v>
-      </c>
-      <c r="R61" s="1">
-        <v>0</v>
-      </c>
-      <c r="S61" s="1">
-        <v>0</v>
-      </c>
-      <c r="T61" s="1">
-        <v>0</v>
-      </c>
-      <c r="U61" s="1">
-        <v>0</v>
-      </c>
-      <c r="V61" s="1">
-        <v>0</v>
-      </c>
-      <c r="W61" s="4">
-        <v>0</v>
-      </c>
-      <c r="X61" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC61" s="1">
-        <v>6</v>
-      </c>
-      <c r="AD61" s="1">
-        <v>10</v>
-      </c>
-      <c r="AE61" s="1">
-        <v>3</v>
-      </c>
-      <c r="AF61" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG61" s="1">
+      <c r="M62" s="1">
+        <v>0</v>
+      </c>
+      <c r="N62" s="1">
+        <v>0</v>
+      </c>
+      <c r="O62" s="1">
+        <v>0</v>
+      </c>
+      <c r="P62" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="1">
+        <v>0</v>
+      </c>
+      <c r="R62" s="1">
+        <v>0</v>
+      </c>
+      <c r="S62" s="1">
+        <v>0</v>
+      </c>
+      <c r="T62" s="1">
+        <v>0</v>
+      </c>
+      <c r="U62" s="1">
+        <v>0</v>
+      </c>
+      <c r="V62" s="1">
+        <v>0</v>
+      </c>
+      <c r="W62" s="4">
+        <v>0</v>
+      </c>
+      <c r="X62" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF62" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG62" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:33">
       <c r="C63" s="1">
-        <v>30033</v>
+        <v>30043</v>
       </c>
       <c r="D63" s="1">
         <v>3</v>
       </c>
       <c r="E63" s="4">
-        <v>3003</v>
+        <v>3004</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I63" s="1">
         <v>0</v>
@@ -5225,43 +5296,52 @@
         <v>0</v>
       </c>
       <c r="L63" s="1">
+        <v>0</v>
+      </c>
+      <c r="M63" s="1">
+        <v>0</v>
+      </c>
+      <c r="N63" s="1">
+        <v>0</v>
+      </c>
+      <c r="O63" s="1">
+        <v>0</v>
+      </c>
+      <c r="P63" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="1">
+        <v>0</v>
+      </c>
+      <c r="R63" s="1">
+        <v>0</v>
+      </c>
+      <c r="S63" s="1">
+        <v>0</v>
+      </c>
+      <c r="T63" s="1">
+        <v>0</v>
+      </c>
+      <c r="U63" s="1">
+        <v>0</v>
+      </c>
+      <c r="V63" s="1">
+        <v>0</v>
+      </c>
+      <c r="W63" s="4">
+        <v>0</v>
+      </c>
+      <c r="X63" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="1">
+        <v>9</v>
+      </c>
+      <c r="AD63" s="1">
+        <v>10</v>
+      </c>
+      <c r="AE63" s="1">
         <v>3</v>
-      </c>
-      <c r="M63" s="1">
-        <v>0</v>
-      </c>
-      <c r="N63" s="1">
-        <v>0</v>
-      </c>
-      <c r="O63" s="1">
-        <v>0</v>
-      </c>
-      <c r="P63" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q63" s="1">
-        <v>0</v>
-      </c>
-      <c r="R63" s="1">
-        <v>0</v>
-      </c>
-      <c r="S63" s="1">
-        <v>0</v>
-      </c>
-      <c r="T63" s="1">
-        <v>0</v>
-      </c>
-      <c r="U63" s="1">
-        <v>0</v>
-      </c>
-      <c r="V63" s="1">
-        <v>0</v>
-      </c>
-      <c r="W63" s="4">
-        <v>0</v>
-      </c>
-      <c r="X63" s="1">
-        <v>0</v>
       </c>
       <c r="AF63" s="1">
         <v>1</v>
@@ -5272,22 +5352,22 @@
     </row>
     <row r="64" customHeight="1" spans="3:33">
       <c r="C64" s="1">
-        <v>30043</v>
+        <v>30073</v>
       </c>
       <c r="D64" s="1">
         <v>3</v>
       </c>
       <c r="E64" s="4">
-        <v>3004</v>
+        <v>3007</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I64" s="1">
         <v>0</v>
@@ -5337,111 +5417,105 @@
       <c r="X64" s="1">
         <v>0</v>
       </c>
-      <c r="AC64" s="1">
-        <v>9</v>
-      </c>
-      <c r="AD64" s="1">
-        <v>10</v>
-      </c>
-      <c r="AE64" s="1">
+      <c r="AC64" s="4">
+        <v>1001</v>
+      </c>
+      <c r="AF64" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG64" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:33">
+      <c r="C66" s="1">
+        <v>30024</v>
+      </c>
+      <c r="D66" s="1">
         <v>3</v>
       </c>
-      <c r="AF64" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG64" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="3:33">
-      <c r="C65" s="1">
-        <v>30073</v>
-      </c>
-      <c r="D65" s="1">
-        <v>3</v>
-      </c>
-      <c r="E65" s="4">
-        <v>3007</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="I65" s="1">
-        <v>0</v>
-      </c>
-      <c r="J65" s="1">
-        <v>0</v>
-      </c>
-      <c r="K65" s="1">
-        <v>0</v>
-      </c>
-      <c r="L65" s="1">
-        <v>0</v>
-      </c>
-      <c r="M65" s="1">
-        <v>0</v>
-      </c>
-      <c r="N65" s="1">
-        <v>0</v>
-      </c>
-      <c r="O65" s="1">
-        <v>0</v>
-      </c>
-      <c r="P65" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="1">
-        <v>0</v>
-      </c>
-      <c r="R65" s="1">
-        <v>0</v>
-      </c>
-      <c r="S65" s="1">
-        <v>0</v>
-      </c>
-      <c r="T65" s="1">
-        <v>0</v>
-      </c>
-      <c r="U65" s="1">
-        <v>0</v>
-      </c>
-      <c r="V65" s="1">
-        <v>0</v>
-      </c>
-      <c r="W65" s="4">
-        <v>0</v>
-      </c>
-      <c r="X65" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC65" s="4">
-        <v>1001</v>
-      </c>
-      <c r="AF65" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG65" s="1">
+      <c r="E66" s="4">
+        <v>3002</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I66" s="1">
+        <v>0</v>
+      </c>
+      <c r="J66" s="1">
+        <v>0</v>
+      </c>
+      <c r="K66" s="1">
+        <v>0</v>
+      </c>
+      <c r="L66" s="1">
+        <v>1</v>
+      </c>
+      <c r="M66" s="1">
+        <v>0</v>
+      </c>
+      <c r="N66" s="1">
+        <v>0</v>
+      </c>
+      <c r="O66" s="1">
+        <v>0</v>
+      </c>
+      <c r="P66" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="1">
+        <v>0</v>
+      </c>
+      <c r="R66" s="1">
+        <v>0</v>
+      </c>
+      <c r="S66" s="1">
+        <v>0</v>
+      </c>
+      <c r="T66" s="1">
+        <v>0</v>
+      </c>
+      <c r="U66" s="1">
+        <v>0</v>
+      </c>
+      <c r="V66" s="1">
+        <v>0</v>
+      </c>
+      <c r="W66" s="4">
+        <v>0</v>
+      </c>
+      <c r="X66" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z66" s="1">
+        <v>100</v>
+      </c>
+      <c r="AF66" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG66" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:33">
       <c r="C67" s="1">
-        <v>30024</v>
+        <v>30034</v>
       </c>
       <c r="D67" s="1">
         <v>3</v>
       </c>
       <c r="E67" s="4">
-        <v>3002</v>
+        <v>3003</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>88</v>
@@ -5459,7 +5533,7 @@
         <v>0</v>
       </c>
       <c r="L67" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" s="1">
         <v>0</v>
@@ -5504,83 +5578,6 @@
         <v>1</v>
       </c>
       <c r="AG67" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="68" customHeight="1" spans="3:33">
-      <c r="C68" s="1">
-        <v>30034</v>
-      </c>
-      <c r="D68" s="1">
-        <v>3</v>
-      </c>
-      <c r="E68" s="4">
-        <v>3003</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="I68" s="1">
-        <v>0</v>
-      </c>
-      <c r="J68" s="1">
-        <v>0</v>
-      </c>
-      <c r="K68" s="1">
-        <v>0</v>
-      </c>
-      <c r="L68" s="1">
-        <v>0</v>
-      </c>
-      <c r="M68" s="1">
-        <v>0</v>
-      </c>
-      <c r="N68" s="1">
-        <v>0</v>
-      </c>
-      <c r="O68" s="1">
-        <v>0</v>
-      </c>
-      <c r="P68" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="1">
-        <v>0</v>
-      </c>
-      <c r="R68" s="1">
-        <v>0</v>
-      </c>
-      <c r="S68" s="1">
-        <v>0</v>
-      </c>
-      <c r="T68" s="1">
-        <v>0</v>
-      </c>
-      <c r="U68" s="1">
-        <v>0</v>
-      </c>
-      <c r="V68" s="1">
-        <v>0</v>
-      </c>
-      <c r="W68" s="4">
-        <v>0</v>
-      </c>
-      <c r="X68" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z68" s="1">
-        <v>100</v>
-      </c>
-      <c r="AF68" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG68" s="1">
         <v>5</v>
       </c>
     </row>

--- a/Excel/SkillTalentConfig.xlsx
+++ b/Excel/SkillTalentConfig.xlsx
@@ -101,6 +101,52 @@
         </r>
       </text>
     </comment>
+    <comment ref="AD3" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+特效值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AF3" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+特效最大叠加层数
+0 无限次
+1 单次</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="AC4" authorId="1">
       <text>
         <r>
@@ -145,7 +191,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE4" authorId="1">
+    <comment ref="AF4" authorId="1">
       <text>
         <r>
           <rPr>
@@ -174,7 +220,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="139">
   <si>
     <t>#</t>
   </si>
@@ -257,6 +303,15 @@
     <t>附带效果</t>
   </si>
   <si>
+    <t>EffectVue</t>
+  </si>
+  <si>
+    <t>EffectDuration</t>
+  </si>
+  <si>
+    <t>EffectMax</t>
+  </si>
+  <si>
     <t>StartQuality</t>
   </si>
   <si>
@@ -330,12 +385,6 @@
   </si>
   <si>
     <t>EffectId</t>
-  </si>
-  <si>
-    <t>EffectValue</t>
-  </si>
-  <si>
-    <t>EffectMax</t>
   </si>
   <si>
     <t>int</t>
@@ -1564,7 +1613,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:AG67"/>
+  <dimension ref="C1:AH67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="6" width="9" style="1"/>
@@ -1583,24 +1632,26 @@
     <col min="21" max="21" width="10.625" style="1" customWidth="1"/>
     <col min="22" max="23" width="9.83333333333333" style="1" customWidth="1"/>
     <col min="24" max="28" width="10.0833333333333" style="1" customWidth="1"/>
-    <col min="29" max="30" width="9" style="1" customWidth="1"/>
-    <col min="31" max="31" width="7.58333333333333" style="1" customWidth="1"/>
-    <col min="32" max="32" width="11" style="1" customWidth="1"/>
-    <col min="33" max="33" width="11.9166666666667" style="1" customWidth="1"/>
-    <col min="34" max="16384" width="9" style="1"/>
+    <col min="29" max="29" width="7.41666666666667" style="1" customWidth="1"/>
+    <col min="30" max="30" width="9.16666666666667" style="1" customWidth="1"/>
+    <col min="31" max="31" width="9.83333333333333" style="1" customWidth="1"/>
+    <col min="32" max="32" width="7.41666666666667" style="1" customWidth="1"/>
+    <col min="33" max="33" width="11" style="1" customWidth="1"/>
+    <col min="34" max="34" width="11.9166666666667" style="1" customWidth="1"/>
+    <col min="35" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:33">
+    <row r="1" customHeight="1" spans="3:34">
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="3:33">
+    <row r="2" customHeight="1" spans="3:34">
       <c r="F2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1680,79 +1731,86 @@
       <c r="AC3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AD3" s="3"/>
-      <c r="AE3" s="3"/>
+      <c r="AD3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="AF3" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AG3" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
+      </c>
+      <c r="AH3" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C4" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="Y4" s="3" t="s">
         <v>22</v>
@@ -1761,121 +1819,127 @@
         <v>23</v>
       </c>
       <c r="AA4" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AC4" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AD4" s="3" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="AE4" s="3" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="AF4" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AG4" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
+      </c>
+      <c r="AH4" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="K5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Y5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Z5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AA5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AB5" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AC5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AD5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AE5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AF5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AG5" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="AH5" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="3:33">
+    <row r="6" customHeight="1" spans="3:34">
       <c r="C6" s="1">
         <v>10011</v>
       </c>
@@ -1886,13 +1950,13 @@
         <v>1001</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
@@ -1948,14 +2012,14 @@
       <c r="AB6" s="1">
         <v>20</v>
       </c>
-      <c r="AF6" s="1">
-        <v>1</v>
-      </c>
       <c r="AG6" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="3:33">
+    <row r="7" customHeight="1" spans="3:34">
       <c r="C7" s="1">
         <v>10021</v>
       </c>
@@ -1966,13 +2030,13 @@
         <v>1002</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I7" s="1">
         <v>50</v>
@@ -2022,14 +2086,14 @@
       <c r="X7" s="1">
         <v>0</v>
       </c>
-      <c r="AF7" s="1">
-        <v>1</v>
-      </c>
       <c r="AG7" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="3:33">
+    <row r="8" customHeight="1" spans="3:34">
       <c r="C8" s="1">
         <v>10031</v>
       </c>
@@ -2040,13 +2104,13 @@
         <v>1003</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
@@ -2103,16 +2167,19 @@
         <v>1</v>
       </c>
       <c r="AE8" s="4">
+        <v>999</v>
+      </c>
+      <c r="AF8" s="4">
         <v>90</v>
       </c>
-      <c r="AF8" s="1">
-        <v>1</v>
-      </c>
       <c r="AG8" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH8" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="3:33">
+    <row r="9" customHeight="1" spans="3:34">
       <c r="C9" s="1">
         <v>10041</v>
       </c>
@@ -2123,13 +2190,13 @@
         <v>1004</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I9" s="1">
         <v>0</v>
@@ -2186,16 +2253,19 @@
         <v>80</v>
       </c>
       <c r="AE9" s="4">
-        <v>1</v>
-      </c>
-      <c r="AF9" s="1">
+        <v>5</v>
+      </c>
+      <c r="AF9" s="4">
         <v>1</v>
       </c>
       <c r="AG9" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH9" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="3:33">
+    <row r="10" customHeight="1" spans="3:34">
       <c r="C10" s="1">
         <v>10051</v>
       </c>
@@ -2206,13 +2276,13 @@
         <v>1005</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I10" s="1">
         <v>0</v>
@@ -2262,14 +2332,14 @@
       <c r="X10" s="1">
         <v>0</v>
       </c>
-      <c r="AF10" s="1">
-        <v>1</v>
-      </c>
       <c r="AG10" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH10" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="3:33">
+    <row r="11" customHeight="1" spans="3:34">
       <c r="C11" s="1">
         <v>10061</v>
       </c>
@@ -2280,13 +2350,13 @@
         <v>1006</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
@@ -2336,14 +2406,14 @@
       <c r="X11" s="1">
         <v>0</v>
       </c>
-      <c r="AF11" s="1">
-        <v>1</v>
-      </c>
       <c r="AG11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH11" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="3:33">
+    <row r="12" customHeight="1" spans="3:34">
       <c r="C12" s="1">
         <v>10071</v>
       </c>
@@ -2354,13 +2424,13 @@
         <v>1007</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I12" s="1">
         <v>20</v>
@@ -2410,18 +2480,18 @@
       <c r="X12" s="1">
         <v>0</v>
       </c>
-      <c r="AF12" s="1">
-        <v>1</v>
-      </c>
       <c r="AG12" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH12" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="3:33">
+    <row r="13" customHeight="1" spans="3:34">
       <c r="F13" s="4"/>
       <c r="W13" s="4"/>
     </row>
-    <row r="14" customHeight="1" spans="3:33">
+    <row r="14" customHeight="1" spans="3:34">
       <c r="C14" s="1">
         <v>10012</v>
       </c>
@@ -2432,13 +2502,13 @@
         <v>1001</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
@@ -2494,14 +2564,14 @@
       <c r="AB14" s="1">
         <v>5</v>
       </c>
-      <c r="AF14" s="1">
-        <v>1</v>
-      </c>
       <c r="AG14" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH14" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="3:33">
+    <row r="15" customHeight="1" spans="3:34">
       <c r="C15" s="1">
         <v>10022</v>
       </c>
@@ -2512,13 +2582,13 @@
         <v>1002</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I15" s="1">
         <v>0</v>
@@ -2577,14 +2647,17 @@
       <c r="AE15" s="4">
         <v>0</v>
       </c>
-      <c r="AF15" s="1">
-        <v>1</v>
+      <c r="AF15" s="4">
+        <v>0</v>
       </c>
       <c r="AG15" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH15" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="3:33">
+    <row r="16" customHeight="1" spans="3:34">
       <c r="C16" s="1">
         <v>10032</v>
       </c>
@@ -2595,13 +2668,13 @@
         <v>1003</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
@@ -2651,14 +2724,14 @@
       <c r="X16" s="1">
         <v>0</v>
       </c>
-      <c r="AF16" s="1">
-        <v>1</v>
-      </c>
       <c r="AG16" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH16" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="3:33">
+    <row r="17" customHeight="1" spans="3:34">
       <c r="C17" s="1">
         <v>10042</v>
       </c>
@@ -2669,13 +2742,13 @@
         <v>1004</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
@@ -2732,16 +2805,19 @@
         <v>-50</v>
       </c>
       <c r="AE17" s="4">
-        <v>1</v>
-      </c>
-      <c r="AF17" s="1">
+        <v>999</v>
+      </c>
+      <c r="AF17" s="4">
         <v>1</v>
       </c>
       <c r="AG17" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH17" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="3:33">
+    <row r="18" customHeight="1" spans="3:34">
       <c r="C18" s="1">
         <v>10072</v>
       </c>
@@ -2752,13 +2828,13 @@
         <v>1007</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I18" s="1">
         <v>0</v>
@@ -2814,15 +2890,20 @@
       <c r="AD18" s="4">
         <v>50</v>
       </c>
-      <c r="AE18" s="4"/>
-      <c r="AF18" s="1">
+      <c r="AE18" s="4">
+        <v>999</v>
+      </c>
+      <c r="AF18" s="4">
         <v>1</v>
       </c>
       <c r="AG18" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH18" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="3:33">
+    <row r="20" customHeight="1" spans="3:34">
       <c r="C20" s="1">
         <v>10023</v>
       </c>
@@ -2833,13 +2914,13 @@
         <v>1002</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I20" s="1">
         <v>0</v>
@@ -2889,14 +2970,14 @@
       <c r="X20" s="1">
         <v>0</v>
       </c>
-      <c r="AF20" s="1">
-        <v>1</v>
-      </c>
       <c r="AG20" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH20" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="3:33">
+    <row r="21" customHeight="1" spans="3:34">
       <c r="C21" s="1">
         <v>10073</v>
       </c>
@@ -2907,13 +2988,13 @@
         <v>1007</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I21" s="1">
         <v>0</v>
@@ -2963,26 +3044,29 @@
       <c r="X21" s="1">
         <v>0</v>
       </c>
+      <c r="AC21" s="1">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="1">
+        <v>20</v>
+      </c>
+      <c r="AE21" s="4">
+        <v>999</v>
+      </c>
       <c r="AF21" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG21" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH21" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="3:33">
+    <row r="22" customHeight="1" spans="3:34">
       <c r="W22" s="4"/>
-      <c r="AC22" s="1">
-        <v>5</v>
-      </c>
-      <c r="AD22" s="1">
-        <v>20</v>
-      </c>
-      <c r="AE22" s="1">
-        <v>3</v>
-      </c>
     </row>
-    <row r="23" customHeight="1" spans="3:33">
+    <row r="23" customHeight="1" spans="3:34">
       <c r="C23" s="1">
         <v>10024</v>
       </c>
@@ -2993,13 +3077,13 @@
         <v>1002</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I23" s="1">
         <v>0</v>
@@ -3052,14 +3136,14 @@
       <c r="Z23" s="1">
         <v>100</v>
       </c>
-      <c r="AF23" s="1">
-        <v>1</v>
-      </c>
       <c r="AG23" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH23" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="3:33">
+    <row r="24" customHeight="1" spans="3:34">
       <c r="C24" s="1">
         <v>10034</v>
       </c>
@@ -3070,13 +3154,13 @@
         <v>1003</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I24" s="1">
         <v>0</v>
@@ -3129,18 +3213,18 @@
       <c r="Z24" s="1">
         <v>100</v>
       </c>
-      <c r="AF24" s="1">
-        <v>1</v>
-      </c>
       <c r="AG24" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH24" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="3:33">
+    <row r="25" customHeight="1" spans="3:34">
       <c r="W25" s="4"/>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1"/>
-    <row r="27" customHeight="1" spans="3:33">
+    <row r="27" customHeight="1" spans="3:34">
       <c r="C27" s="1">
         <v>20011</v>
       </c>
@@ -3151,13 +3235,13 @@
         <v>2001</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I27" s="1">
         <v>0</v>
@@ -3213,14 +3297,14 @@
       <c r="AB27" s="1">
         <v>20</v>
       </c>
-      <c r="AF27" s="1">
-        <v>1</v>
-      </c>
       <c r="AG27" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH27" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="3:33">
+    <row r="28" customHeight="1" spans="3:34">
       <c r="C28" s="1">
         <v>20021</v>
       </c>
@@ -3231,13 +3315,13 @@
         <v>2002</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I28" s="1">
         <v>50</v>
@@ -3287,14 +3371,14 @@
       <c r="X28" s="1">
         <v>0</v>
       </c>
-      <c r="AF28" s="1">
-        <v>1</v>
-      </c>
       <c r="AG28" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH28" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="3:33">
+    <row r="29" customHeight="1" spans="3:34">
       <c r="C29" s="1">
         <v>20031</v>
       </c>
@@ -3305,13 +3389,13 @@
         <v>2003</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I29" s="1">
         <v>0</v>
@@ -3367,17 +3451,20 @@
       <c r="AD29" s="1">
         <v>1</v>
       </c>
-      <c r="AE29" s="1">
+      <c r="AE29" s="4">
+        <v>999</v>
+      </c>
+      <c r="AF29" s="1">
         <v>90</v>
       </c>
-      <c r="AF29" s="1">
-        <v>1</v>
-      </c>
       <c r="AG29" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH29" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="3:33">
+    <row r="30" customHeight="1" spans="3:34">
       <c r="C30" s="1">
         <v>20041</v>
       </c>
@@ -3388,13 +3475,13 @@
         <v>2004</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I30" s="1">
         <v>0</v>
@@ -3450,17 +3537,20 @@
       <c r="AD30" s="1">
         <v>20</v>
       </c>
-      <c r="AE30" s="1">
+      <c r="AE30" s="4">
+        <v>999</v>
+      </c>
+      <c r="AF30" s="1">
         <v>3</v>
       </c>
-      <c r="AF30" s="1">
-        <v>1</v>
-      </c>
       <c r="AG30" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH30" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="3:33">
+    <row r="31" customHeight="1" spans="3:34">
       <c r="C31" s="1">
         <v>20051</v>
       </c>
@@ -3471,13 +3561,13 @@
         <v>2005</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I31" s="1">
         <v>0</v>
@@ -3527,14 +3617,14 @@
       <c r="X31" s="1">
         <v>0</v>
       </c>
-      <c r="AF31" s="1">
-        <v>1</v>
-      </c>
       <c r="AG31" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH31" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="3:33">
+    <row r="32" customHeight="1" spans="3:34">
       <c r="C32" s="1">
         <v>20061</v>
       </c>
@@ -3545,13 +3635,13 @@
         <v>2006</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I32" s="1">
         <v>0</v>
@@ -3601,14 +3691,14 @@
       <c r="X32" s="1">
         <v>0</v>
       </c>
-      <c r="AF32" s="1">
-        <v>1</v>
-      </c>
       <c r="AG32" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH32" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="3:33">
+    <row r="33" customHeight="1" spans="3:34">
       <c r="C33" s="1">
         <v>20071</v>
       </c>
@@ -3619,13 +3709,13 @@
         <v>2007</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I33" s="1">
         <v>0</v>
@@ -3682,20 +3772,23 @@
         <v>10</v>
       </c>
       <c r="AE33" s="4">
+        <v>999</v>
+      </c>
+      <c r="AF33" s="4">
         <v>3</v>
       </c>
-      <c r="AF33" s="1">
-        <v>1</v>
-      </c>
       <c r="AG33" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH33" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="34" customHeight="1" spans="3:33">
+    <row r="34" customHeight="1" spans="3:34">
       <c r="F34" s="4"/>
       <c r="W34" s="4"/>
     </row>
-    <row r="35" customHeight="1" spans="3:33">
+    <row r="35" customHeight="1" spans="3:34">
       <c r="C35" s="1">
         <v>20012</v>
       </c>
@@ -3706,13 +3799,13 @@
         <v>2001</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I35" s="1">
         <v>0</v>
@@ -3768,14 +3861,14 @@
       <c r="AB35" s="1">
         <v>5</v>
       </c>
-      <c r="AF35" s="1">
-        <v>1</v>
-      </c>
       <c r="AG35" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH35" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="3:33">
+    <row r="36" customHeight="1" spans="3:34">
       <c r="C36" s="1">
         <v>20022</v>
       </c>
@@ -3786,13 +3879,13 @@
         <v>2002</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I36" s="1">
         <v>0</v>
@@ -3842,14 +3935,14 @@
       <c r="X36" s="1">
         <v>0</v>
       </c>
-      <c r="AF36" s="1">
-        <v>1</v>
-      </c>
       <c r="AG36" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH36" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="3:33">
+    <row r="37" customHeight="1" spans="3:34">
       <c r="C37" s="1">
         <v>20032</v>
       </c>
@@ -3860,13 +3953,13 @@
         <v>2003</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I37" s="1">
         <v>0</v>
@@ -3916,14 +4009,14 @@
       <c r="X37" s="1">
         <v>0</v>
       </c>
-      <c r="AF37" s="1">
-        <v>1</v>
-      </c>
       <c r="AG37" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH37" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="38" customHeight="1" spans="3:33">
+    <row r="38" customHeight="1" spans="3:34">
       <c r="C38" s="1">
         <v>20072</v>
       </c>
@@ -3934,13 +4027,13 @@
         <v>2007</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I38" s="1">
         <v>0</v>
@@ -3991,8 +4084,9 @@
         <v>0</v>
       </c>
       <c r="AD38" s="4"/>
+      <c r="AE38" s="4"/>
     </row>
-    <row r="39" customHeight="1" spans="3:33">
+    <row r="39" customHeight="1" spans="3:34">
       <c r="R39" s="1">
         <v>0</v>
       </c>
@@ -4006,7 +4100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="3:33">
+    <row r="40" customHeight="1" spans="3:34">
       <c r="C40" s="1">
         <v>20033</v>
       </c>
@@ -4017,13 +4111,13 @@
         <v>2003</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I40" s="1">
         <v>0</v>
@@ -4079,17 +4173,20 @@
       <c r="AD40" s="1">
         <v>10</v>
       </c>
-      <c r="AE40" s="1">
+      <c r="AE40" s="4">
+        <v>999</v>
+      </c>
+      <c r="AF40" s="1">
         <v>3</v>
       </c>
-      <c r="AF40" s="1">
-        <v>1</v>
-      </c>
       <c r="AG40" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH40" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="3:33">
+    <row r="41" customHeight="1" spans="3:34">
       <c r="C41" s="1">
         <v>20043</v>
       </c>
@@ -4100,13 +4197,13 @@
         <v>2004</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I41" s="1">
         <v>0</v>
@@ -4162,17 +4259,20 @@
       <c r="AD41" s="1">
         <v>5</v>
       </c>
-      <c r="AE41" s="1">
+      <c r="AE41" s="4">
+        <v>999</v>
+      </c>
+      <c r="AF41" s="1">
         <v>3</v>
       </c>
-      <c r="AF41" s="1">
-        <v>1</v>
-      </c>
       <c r="AG41" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH41" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="42" customHeight="1" spans="3:33">
+    <row r="42" customHeight="1" spans="3:34">
       <c r="C42" s="1">
         <v>20073</v>
       </c>
@@ -4183,13 +4283,13 @@
         <v>2007</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I42" s="1">
         <v>0</v>
@@ -4246,16 +4346,19 @@
         <v>-30</v>
       </c>
       <c r="AE42" s="4">
-        <v>1</v>
-      </c>
-      <c r="AF42" s="1">
+        <v>999</v>
+      </c>
+      <c r="AF42" s="4">
         <v>1</v>
       </c>
       <c r="AG42" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH42" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="44" customHeight="1" spans="3:33">
+    <row r="44" customHeight="1" spans="3:34">
       <c r="C44" s="1">
         <v>20024</v>
       </c>
@@ -4266,13 +4369,13 @@
         <v>2002</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I44" s="1">
         <v>0</v>
@@ -4325,14 +4428,14 @@
       <c r="Z44" s="1">
         <v>100</v>
       </c>
-      <c r="AF44" s="1">
-        <v>1</v>
-      </c>
       <c r="AG44" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH44" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="45" customHeight="1" spans="3:33">
+    <row r="45" customHeight="1" spans="3:34">
       <c r="C45" s="1">
         <v>20034</v>
       </c>
@@ -4343,13 +4446,13 @@
         <v>2003</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I45" s="1">
         <v>0</v>
@@ -4402,19 +4505,19 @@
       <c r="Z45" s="1">
         <v>100</v>
       </c>
-      <c r="AF45" s="1">
-        <v>1</v>
-      </c>
       <c r="AG45" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH45" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="48" customFormat="1" customHeight="1" spans="3:33">
+    <row r="48" customFormat="1" customHeight="1" spans="3:34">
       <c r="T48" s="1"/>
       <c r="U48" s="1"/>
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1"/>
-    <row r="50" customHeight="1" spans="3:33">
+    <row r="50" customHeight="1" spans="3:34">
       <c r="C50" s="1">
         <v>30011</v>
       </c>
@@ -4425,13 +4528,13 @@
         <v>3001</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I50" s="1">
         <v>0</v>
@@ -4487,14 +4590,14 @@
       <c r="AB50" s="1">
         <v>20</v>
       </c>
-      <c r="AF50" s="1">
-        <v>1</v>
-      </c>
       <c r="AG50" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH50" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="51" customHeight="1" spans="3:33">
+    <row r="51" customHeight="1" spans="3:34">
       <c r="C51" s="1">
         <v>30021</v>
       </c>
@@ -4505,13 +4608,13 @@
         <v>3002</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I51" s="1">
         <v>50</v>
@@ -4561,14 +4664,14 @@
       <c r="X51" s="1">
         <v>0</v>
       </c>
-      <c r="AF51" s="1">
-        <v>1</v>
-      </c>
       <c r="AG51" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH51" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="52" customHeight="1" spans="3:33">
+    <row r="52" customHeight="1" spans="3:34">
       <c r="C52" s="1">
         <v>30031</v>
       </c>
@@ -4579,13 +4682,13 @@
         <v>3003</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I52" s="1">
         <v>0</v>
@@ -4642,16 +4745,19 @@
         <v>1</v>
       </c>
       <c r="AE52" s="4">
+        <v>999</v>
+      </c>
+      <c r="AF52" s="4">
         <v>90</v>
       </c>
-      <c r="AF52" s="1">
-        <v>1</v>
-      </c>
       <c r="AG52" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH52" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="53" customHeight="1" spans="3:33">
+    <row r="53" customHeight="1" spans="3:34">
       <c r="C53" s="1">
         <v>30041</v>
       </c>
@@ -4662,13 +4768,13 @@
         <v>3004</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I53" s="1">
         <v>0</v>
@@ -4724,17 +4830,20 @@
       <c r="AD53" s="1">
         <v>100</v>
       </c>
-      <c r="AE53" s="1">
-        <v>1</v>
+      <c r="AE53" s="4">
+        <v>999</v>
       </c>
       <c r="AF53" s="1">
         <v>1</v>
       </c>
       <c r="AG53" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH53" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="54" customHeight="1" spans="3:33">
+    <row r="54" customHeight="1" spans="3:34">
       <c r="C54" s="1">
         <v>30051</v>
       </c>
@@ -4745,13 +4854,13 @@
         <v>3005</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I54" s="1">
         <v>0</v>
@@ -4801,14 +4910,14 @@
       <c r="X54" s="1">
         <v>0</v>
       </c>
-      <c r="AF54" s="1">
-        <v>1</v>
-      </c>
       <c r="AG54" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH54" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="55" customHeight="1" spans="3:33">
+    <row r="55" customHeight="1" spans="3:34">
       <c r="C55" s="1">
         <v>30061</v>
       </c>
@@ -4819,13 +4928,13 @@
         <v>3006</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I55" s="1">
         <v>0</v>
@@ -4875,14 +4984,14 @@
       <c r="X55" s="1">
         <v>0</v>
       </c>
-      <c r="AF55" s="1">
-        <v>1</v>
-      </c>
       <c r="AG55" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH55" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="56" customHeight="1" spans="3:33">
+    <row r="56" customHeight="1" spans="3:34">
       <c r="C56" s="1">
         <v>30071</v>
       </c>
@@ -4893,14 +5002,14 @@
         <v>3007</v>
       </c>
       <c r="F56" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H56" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="G56" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="I56" s="1">
         <v>0</v>
       </c>
@@ -4949,14 +5058,14 @@
       <c r="X56" s="1">
         <v>0</v>
       </c>
-      <c r="AF56" s="1">
-        <v>1</v>
-      </c>
       <c r="AG56" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH56" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="58" customHeight="1" spans="3:33">
+    <row r="58" customHeight="1" spans="3:34">
       <c r="C58" s="1">
         <v>30012</v>
       </c>
@@ -4967,13 +5076,13 @@
         <v>3001</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I58" s="1">
         <v>0</v>
@@ -5029,14 +5138,14 @@
       <c r="AB58" s="1">
         <v>5</v>
       </c>
-      <c r="AF58" s="1">
-        <v>1</v>
-      </c>
       <c r="AG58" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH58" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="59" customHeight="1" spans="3:33">
+    <row r="59" customHeight="1" spans="3:34">
       <c r="C59" s="1">
         <v>30022</v>
       </c>
@@ -5047,13 +5156,13 @@
         <v>3002</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I59" s="1">
         <v>0</v>
@@ -5103,14 +5212,14 @@
       <c r="X59" s="1">
         <v>0</v>
       </c>
-      <c r="AF59" s="1">
-        <v>1</v>
-      </c>
       <c r="AG59" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH59" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="60" customHeight="1" spans="3:33">
+    <row r="60" customHeight="1" spans="3:34">
       <c r="C60" s="1">
         <v>30032</v>
       </c>
@@ -5121,13 +5230,13 @@
         <v>3003</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I60" s="1">
         <v>0</v>
@@ -5183,17 +5292,20 @@
       <c r="AD60" s="1">
         <v>10</v>
       </c>
-      <c r="AE60" s="1">
+      <c r="AE60" s="4">
+        <v>999</v>
+      </c>
+      <c r="AF60" s="1">
         <v>3</v>
       </c>
-      <c r="AF60" s="1">
-        <v>1</v>
-      </c>
       <c r="AG60" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH60" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="62" customHeight="1" spans="3:33">
+    <row r="62" customHeight="1" spans="3:34">
       <c r="C62" s="1">
         <v>30033</v>
       </c>
@@ -5204,13 +5316,13 @@
         <v>3003</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I62" s="1">
         <v>0</v>
@@ -5260,14 +5372,14 @@
       <c r="X62" s="1">
         <v>0</v>
       </c>
-      <c r="AF62" s="1">
-        <v>1</v>
-      </c>
       <c r="AG62" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH62" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="63" customHeight="1" spans="3:33">
+    <row r="63" customHeight="1" spans="3:34">
       <c r="C63" s="1">
         <v>30043</v>
       </c>
@@ -5278,13 +5390,13 @@
         <v>3004</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I63" s="1">
         <v>0</v>
@@ -5340,17 +5452,20 @@
       <c r="AD63" s="1">
         <v>10</v>
       </c>
-      <c r="AE63" s="1">
+      <c r="AE63" s="4">
+        <v>999</v>
+      </c>
+      <c r="AF63" s="1">
         <v>3</v>
       </c>
-      <c r="AF63" s="1">
-        <v>1</v>
-      </c>
       <c r="AG63" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH63" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="64" customHeight="1" spans="3:33">
+    <row r="64" customHeight="1" spans="3:34">
       <c r="C64" s="1">
         <v>30073</v>
       </c>
@@ -5361,13 +5476,13 @@
         <v>3007</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I64" s="1">
         <v>0</v>
@@ -5420,14 +5535,14 @@
       <c r="AC64" s="4">
         <v>1001</v>
       </c>
-      <c r="AF64" s="1">
-        <v>1</v>
-      </c>
       <c r="AG64" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH64" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="66" customHeight="1" spans="3:33">
+    <row r="66" customHeight="1" spans="3:34">
       <c r="C66" s="1">
         <v>30024</v>
       </c>
@@ -5438,13 +5553,13 @@
         <v>3002</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I66" s="1">
         <v>0</v>
@@ -5497,14 +5612,14 @@
       <c r="Z66" s="1">
         <v>100</v>
       </c>
-      <c r="AF66" s="1">
-        <v>1</v>
-      </c>
       <c r="AG66" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH66" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="67" customHeight="1" spans="3:33">
+    <row r="67" customHeight="1" spans="3:34">
       <c r="C67" s="1">
         <v>30034</v>
       </c>
@@ -5515,13 +5630,13 @@
         <v>3003</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I67" s="1">
         <v>0</v>
@@ -5574,10 +5689,10 @@
       <c r="Z67" s="1">
         <v>100</v>
       </c>
-      <c r="AF67" s="1">
-        <v>1</v>
-      </c>
       <c r="AG67" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH67" s="1">
         <v>5</v>
       </c>
     </row>

--- a/Excel/SkillTalentConfig.xlsx
+++ b/Excel/SkillTalentConfig.xlsx
@@ -220,7 +220,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="145">
   <si>
     <t>#</t>
   </si>
@@ -459,7 +459,7 @@
     <t>·吸血</t>
   </si>
   <si>
-    <t>回复1%伤害的生命</t>
+    <t>回复30%物攻的生命</t>
   </si>
   <si>
     <t>·断河</t>
@@ -486,7 +486,7 @@
     <t>·焚魂</t>
   </si>
   <si>
-    <t>额外灼烧敌人20%的伤害，最高3层</t>
+    <t>额外灼烧敌人20%的伤害，持续5秒，最高3层</t>
   </si>
   <si>
     <t>·疾风</t>
@@ -510,6 +510,12 @@
     <t>火狱阵法</t>
   </si>
   <si>
+    <t>·蚀骨</t>
+  </si>
+  <si>
+    <t>敌人额外承受1%伤害，最高50层</t>
+  </si>
+  <si>
     <t>烈焰焚天</t>
   </si>
   <si>
@@ -537,31 +543,34 @@
     <t>增加{0}%魔法增幅</t>
   </si>
   <si>
+    <t>·汲取</t>
+  </si>
+  <si>
+    <t>回复20%魔攻的生命</t>
+  </si>
+  <si>
+    <t>·火狱</t>
+  </si>
+  <si>
+    <t>火海的攻击范围增加一行一列</t>
+  </si>
+  <si>
+    <t>·冰狱</t>
+  </si>
+  <si>
+    <t>冰封的攻击范围增加一行一列</t>
+  </si>
+  <si>
     <t>·狂潮</t>
   </si>
   <si>
     <t>额外攻击一个敌人</t>
   </si>
   <si>
-    <t>·火狱</t>
-  </si>
-  <si>
-    <t>火海的攻击范围增加一行一列</t>
-  </si>
-  <si>
-    <t>·冰狱</t>
-  </si>
-  <si>
-    <t>冰封的攻击范围增加一行一列</t>
-  </si>
-  <si>
-    <t>·蚀骨</t>
-  </si>
-  <si>
     <t>·燃魂</t>
   </si>
   <si>
-    <t>自己个额外增加5%伤害，最高3层</t>
+    <t>额外增加5%伤害，最高3层</t>
   </si>
   <si>
     <t>·冻结</t>
@@ -585,7 +594,10 @@
     <t>毒咒术</t>
   </si>
   <si>
-    <t>·蚀甲</t>
+    <t>·禁疗</t>
+  </si>
+  <si>
+    <t>降低敌人80%的回复效果</t>
   </si>
   <si>
     <t>圣疗术</t>
@@ -616,6 +628,12 @@
   </si>
   <si>
     <t>增加{0}%道术增幅</t>
+  </si>
+  <si>
+    <t>·回复</t>
+  </si>
+  <si>
+    <t>回复25%道术的生命</t>
   </si>
   <si>
     <t>·双生</t>
@@ -815,12 +833,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1613,7 +1631,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:AH67"/>
+  <dimension ref="C1:AH68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="6" width="9" style="1"/>
@@ -2639,16 +2657,16 @@
         <v>0</v>
       </c>
       <c r="AC15" s="1">
-        <v>3</v>
+        <v>101</v>
       </c>
       <c r="AD15" s="4">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="AE15" s="4">
         <v>0</v>
       </c>
       <c r="AF15" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG15" s="1">
         <v>1</v>
@@ -3044,14 +3062,14 @@
       <c r="X21" s="1">
         <v>0</v>
       </c>
-      <c r="AC21" s="1">
-        <v>5</v>
+      <c r="AC21" s="4">
+        <v>206</v>
       </c>
       <c r="AD21" s="1">
         <v>20</v>
       </c>
       <c r="AE21" s="4">
-        <v>999</v>
+        <v>5</v>
       </c>
       <c r="AF21" s="1">
         <v>3</v>
@@ -3385,17 +3403,17 @@
       <c r="D29" s="1">
         <v>2</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="1">
         <v>2003</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>95</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="I29" s="1">
         <v>0</v>
@@ -3446,7 +3464,7 @@
         <v>0</v>
       </c>
       <c r="AC29" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AD29" s="1">
         <v>1</v>
@@ -3455,7 +3473,7 @@
         <v>999</v>
       </c>
       <c r="AF29" s="1">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="AG29" s="1">
         <v>1</v>
@@ -3475,13 +3493,13 @@
         <v>2004</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>65</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I30" s="1">
         <v>0</v>
@@ -3561,7 +3579,7 @@
         <v>2005</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>70</v>
@@ -3635,7 +3653,7 @@
         <v>2006</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>73</v>
@@ -3709,13 +3727,13 @@
         <v>2007</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I33" s="1">
         <v>0</v>
@@ -3802,10 +3820,10 @@
         <v>91</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I35" s="1">
         <v>0</v>
@@ -3854,12 +3872,6 @@
       </c>
       <c r="X35" s="1">
         <v>0</v>
-      </c>
-      <c r="AA35" s="1">
-        <v>2005</v>
-      </c>
-      <c r="AB35" s="1">
-        <v>5</v>
       </c>
       <c r="AG35" s="1">
         <v>1</v>
@@ -3882,10 +3894,10 @@
         <v>94</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I36" s="1">
         <v>0</v>
@@ -3897,7 +3909,7 @@
         <v>0</v>
       </c>
       <c r="L36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="1">
         <v>0</v>
@@ -3934,6 +3946,18 @@
       </c>
       <c r="X36" s="1">
         <v>0</v>
+      </c>
+      <c r="AC36" s="1">
+        <v>102</v>
+      </c>
+      <c r="AD36" s="4">
+        <v>20</v>
+      </c>
+      <c r="AE36" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="4">
+        <v>1</v>
       </c>
       <c r="AG36" s="1">
         <v>1</v>
@@ -3956,10 +3980,10 @@
         <v>95</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I37" s="1">
         <v>0</v>
@@ -4027,13 +4051,13 @@
         <v>2007</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I38" s="1">
         <v>0</v>
@@ -4102,22 +4126,22 @@
     </row>
     <row r="40" customHeight="1" spans="3:34">
       <c r="C40" s="1">
-        <v>20033</v>
+        <v>20023</v>
       </c>
       <c r="D40" s="1">
         <v>2</v>
       </c>
       <c r="E40" s="1">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="I40" s="1">
         <v>0</v>
@@ -4129,7 +4153,7 @@
         <v>0</v>
       </c>
       <c r="L40" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="1">
         <v>0</v>
@@ -4166,18 +4190,6 @@
       </c>
       <c r="X40" s="1">
         <v>0</v>
-      </c>
-      <c r="AC40" s="1">
-        <v>6</v>
-      </c>
-      <c r="AD40" s="1">
-        <v>10</v>
-      </c>
-      <c r="AE40" s="4">
-        <v>999</v>
-      </c>
-      <c r="AF40" s="1">
-        <v>3</v>
       </c>
       <c r="AG40" s="1">
         <v>1</v>
@@ -4197,13 +4209,13 @@
         <v>2004</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I41" s="1">
         <v>0</v>
@@ -4283,13 +4295,13 @@
         <v>2007</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="I42" s="1">
         <v>0</v>
@@ -4528,13 +4540,13 @@
         <v>3001</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="I50" s="1">
         <v>0</v>
@@ -4608,7 +4620,7 @@
         <v>3002</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>62</v>
@@ -4682,13 +4694,13 @@
         <v>3003</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>66</v>
+        <v>125</v>
       </c>
       <c r="I52" s="1">
         <v>0</v>
@@ -4739,16 +4751,16 @@
         <v>0</v>
       </c>
       <c r="AC52" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD52" s="4">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="AE52" s="4">
         <v>999</v>
       </c>
       <c r="AF52" s="4">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="AG52" s="1">
         <v>1</v>
@@ -4768,13 +4780,13 @@
         <v>3004</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I53" s="1">
         <v>0</v>
@@ -4854,7 +4866,7 @@
         <v>3005</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>70</v>
@@ -4928,13 +4940,13 @@
         <v>3006</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="I55" s="1">
         <v>0</v>
@@ -5002,13 +5014,13 @@
         <v>3007</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="I56" s="1">
         <v>0</v>
@@ -5076,13 +5088,13 @@
         <v>3001</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="I58" s="1">
         <v>0</v>
@@ -5156,13 +5168,13 @@
         <v>3002</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="I59" s="1">
         <v>0</v>
@@ -5174,7 +5186,7 @@
         <v>0</v>
       </c>
       <c r="L59" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59" s="1">
         <v>0</v>
@@ -5211,6 +5223,18 @@
       </c>
       <c r="X59" s="1">
         <v>0</v>
+      </c>
+      <c r="AC59" s="1">
+        <v>103</v>
+      </c>
+      <c r="AD59" s="1">
+        <v>25</v>
+      </c>
+      <c r="AE59" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF59" s="1">
+        <v>1</v>
       </c>
       <c r="AG59" s="1">
         <v>1</v>
@@ -5230,13 +5254,13 @@
         <v>3003</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I60" s="1">
         <v>0</v>
@@ -5307,22 +5331,22 @@
     </row>
     <row r="62" customHeight="1" spans="3:34">
       <c r="C62" s="1">
-        <v>30033</v>
+        <v>30023</v>
       </c>
       <c r="D62" s="1">
         <v>3</v>
       </c>
       <c r="E62" s="4">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="I62" s="1">
         <v>0</v>
@@ -5334,7 +5358,7 @@
         <v>0</v>
       </c>
       <c r="L62" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M62" s="1">
         <v>0</v>
@@ -5381,22 +5405,22 @@
     </row>
     <row r="63" customHeight="1" spans="3:34">
       <c r="C63" s="1">
-        <v>30043</v>
+        <v>30033</v>
       </c>
       <c r="D63" s="1">
         <v>3</v>
       </c>
       <c r="E63" s="4">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="I63" s="1">
         <v>0</v>
@@ -5408,7 +5432,7 @@
         <v>0</v>
       </c>
       <c r="L63" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M63" s="1">
         <v>0</v>
@@ -5445,18 +5469,6 @@
       </c>
       <c r="X63" s="1">
         <v>0</v>
-      </c>
-      <c r="AC63" s="1">
-        <v>9</v>
-      </c>
-      <c r="AD63" s="1">
-        <v>10</v>
-      </c>
-      <c r="AE63" s="4">
-        <v>999</v>
-      </c>
-      <c r="AF63" s="1">
-        <v>3</v>
       </c>
       <c r="AG63" s="1">
         <v>1</v>
@@ -5467,170 +5479,179 @@
     </row>
     <row r="64" customHeight="1" spans="3:34">
       <c r="C64" s="1">
-        <v>30073</v>
+        <v>30043</v>
       </c>
       <c r="D64" s="1">
         <v>3</v>
       </c>
       <c r="E64" s="4">
+        <v>3004</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I64" s="1">
+        <v>0</v>
+      </c>
+      <c r="J64" s="1">
+        <v>0</v>
+      </c>
+      <c r="K64" s="1">
+        <v>0</v>
+      </c>
+      <c r="L64" s="1">
+        <v>0</v>
+      </c>
+      <c r="M64" s="1">
+        <v>0</v>
+      </c>
+      <c r="N64" s="1">
+        <v>0</v>
+      </c>
+      <c r="O64" s="1">
+        <v>0</v>
+      </c>
+      <c r="P64" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="1">
+        <v>0</v>
+      </c>
+      <c r="R64" s="1">
+        <v>0</v>
+      </c>
+      <c r="S64" s="1">
+        <v>0</v>
+      </c>
+      <c r="T64" s="1">
+        <v>0</v>
+      </c>
+      <c r="U64" s="1">
+        <v>0</v>
+      </c>
+      <c r="V64" s="1">
+        <v>0</v>
+      </c>
+      <c r="W64" s="4">
+        <v>0</v>
+      </c>
+      <c r="X64" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="1">
+        <v>9</v>
+      </c>
+      <c r="AD64" s="1">
+        <v>10</v>
+      </c>
+      <c r="AE64" s="4">
+        <v>999</v>
+      </c>
+      <c r="AF64" s="1">
+        <v>3</v>
+      </c>
+      <c r="AG64" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH64" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:34">
+      <c r="C65" s="1">
+        <v>30073</v>
+      </c>
+      <c r="D65" s="1">
+        <v>3</v>
+      </c>
+      <c r="E65" s="4">
         <v>3007</v>
       </c>
-      <c r="F64" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="I64" s="1">
-        <v>0</v>
-      </c>
-      <c r="J64" s="1">
-        <v>0</v>
-      </c>
-      <c r="K64" s="1">
-        <v>0</v>
-      </c>
-      <c r="L64" s="1">
-        <v>0</v>
-      </c>
-      <c r="M64" s="1">
-        <v>0</v>
-      </c>
-      <c r="N64" s="1">
-        <v>0</v>
-      </c>
-      <c r="O64" s="1">
-        <v>0</v>
-      </c>
-      <c r="P64" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="1">
-        <v>0</v>
-      </c>
-      <c r="R64" s="1">
-        <v>0</v>
-      </c>
-      <c r="S64" s="1">
-        <v>0</v>
-      </c>
-      <c r="T64" s="1">
-        <v>0</v>
-      </c>
-      <c r="U64" s="1">
-        <v>0</v>
-      </c>
-      <c r="V64" s="1">
-        <v>0</v>
-      </c>
-      <c r="W64" s="4">
-        <v>0</v>
-      </c>
-      <c r="X64" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC64" s="4">
+      <c r="F65" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="I65" s="1">
+        <v>0</v>
+      </c>
+      <c r="J65" s="1">
+        <v>0</v>
+      </c>
+      <c r="K65" s="1">
+        <v>0</v>
+      </c>
+      <c r="L65" s="1">
+        <v>0</v>
+      </c>
+      <c r="M65" s="1">
+        <v>0</v>
+      </c>
+      <c r="N65" s="1">
+        <v>0</v>
+      </c>
+      <c r="O65" s="1">
+        <v>0</v>
+      </c>
+      <c r="P65" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="1">
+        <v>0</v>
+      </c>
+      <c r="R65" s="1">
+        <v>0</v>
+      </c>
+      <c r="S65" s="1">
+        <v>0</v>
+      </c>
+      <c r="T65" s="1">
+        <v>0</v>
+      </c>
+      <c r="U65" s="1">
+        <v>0</v>
+      </c>
+      <c r="V65" s="1">
+        <v>0</v>
+      </c>
+      <c r="W65" s="4">
+        <v>0</v>
+      </c>
+      <c r="X65" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="4">
         <v>1001</v>
       </c>
-      <c r="AG64" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH64" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66" customHeight="1" spans="3:34">
-      <c r="C66" s="1">
-        <v>30024</v>
-      </c>
-      <c r="D66" s="1">
-        <v>3</v>
-      </c>
-      <c r="E66" s="4">
-        <v>3002</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I66" s="1">
-        <v>0</v>
-      </c>
-      <c r="J66" s="1">
-        <v>0</v>
-      </c>
-      <c r="K66" s="1">
-        <v>0</v>
-      </c>
-      <c r="L66" s="1">
-        <v>1</v>
-      </c>
-      <c r="M66" s="1">
-        <v>0</v>
-      </c>
-      <c r="N66" s="1">
-        <v>0</v>
-      </c>
-      <c r="O66" s="1">
-        <v>0</v>
-      </c>
-      <c r="P66" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="1">
-        <v>0</v>
-      </c>
-      <c r="R66" s="1">
-        <v>0</v>
-      </c>
-      <c r="S66" s="1">
-        <v>0</v>
-      </c>
-      <c r="T66" s="1">
-        <v>0</v>
-      </c>
-      <c r="U66" s="1">
-        <v>0</v>
-      </c>
-      <c r="V66" s="1">
-        <v>0</v>
-      </c>
-      <c r="W66" s="4">
-        <v>0</v>
-      </c>
-      <c r="X66" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z66" s="1">
-        <v>100</v>
-      </c>
-      <c r="AG66" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH66" s="1">
+      <c r="AG65" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH65" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:34">
       <c r="C67" s="1">
-        <v>30034</v>
+        <v>30024</v>
       </c>
       <c r="D67" s="1">
         <v>3</v>
       </c>
       <c r="E67" s="4">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>89</v>
@@ -5648,7 +5669,7 @@
         <v>0</v>
       </c>
       <c r="L67" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="1">
         <v>0</v>
@@ -5693,6 +5714,83 @@
         <v>1</v>
       </c>
       <c r="AH67" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:34">
+      <c r="C68" s="1">
+        <v>30034</v>
+      </c>
+      <c r="D68" s="1">
+        <v>3</v>
+      </c>
+      <c r="E68" s="4">
+        <v>3003</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I68" s="1">
+        <v>0</v>
+      </c>
+      <c r="J68" s="1">
+        <v>0</v>
+      </c>
+      <c r="K68" s="1">
+        <v>0</v>
+      </c>
+      <c r="L68" s="1">
+        <v>0</v>
+      </c>
+      <c r="M68" s="1">
+        <v>0</v>
+      </c>
+      <c r="N68" s="1">
+        <v>0</v>
+      </c>
+      <c r="O68" s="1">
+        <v>0</v>
+      </c>
+      <c r="P68" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="1">
+        <v>0</v>
+      </c>
+      <c r="R68" s="1">
+        <v>0</v>
+      </c>
+      <c r="S68" s="1">
+        <v>0</v>
+      </c>
+      <c r="T68" s="1">
+        <v>0</v>
+      </c>
+      <c r="U68" s="1">
+        <v>0</v>
+      </c>
+      <c r="V68" s="1">
+        <v>0</v>
+      </c>
+      <c r="W68" s="4">
+        <v>0</v>
+      </c>
+      <c r="X68" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="1">
+        <v>100</v>
+      </c>
+      <c r="AG68" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH68" s="1">
         <v>5</v>
       </c>
     </row>

--- a/Excel/SkillTalentConfig.xlsx
+++ b/Excel/SkillTalentConfig.xlsx
@@ -220,7 +220,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="148">
   <si>
     <t>#</t>
   </si>
@@ -432,46 +432,49 @@
     <t>龙魂护体</t>
   </si>
   <si>
+    <t>减少技能30%冷却时间</t>
+  </si>
+  <si>
+    <t>无求易决</t>
+  </si>
+  <si>
+    <t>·圣体</t>
+  </si>
+  <si>
+    <t>增加5%系数增幅</t>
+  </si>
+  <si>
+    <t>火麟剑诀</t>
+  </si>
+  <si>
+    <t>减少技能20%冷却时间</t>
+  </si>
+  <si>
+    <t>增加5%物攻增幅</t>
+  </si>
+  <si>
+    <t>·吸血</t>
+  </si>
+  <si>
+    <t>回复30%物攻的生命</t>
+  </si>
+  <si>
+    <t>·断河</t>
+  </si>
+  <si>
+    <t>剑阵的攻击范围增加一行一列</t>
+  </si>
+  <si>
+    <t>·致残</t>
+  </si>
+  <si>
+    <t>降低敌人50%的攻击速度</t>
+  </si>
+  <si>
     <t>·无断</t>
   </si>
   <si>
-    <t>增加30秒持续时间</t>
-  </si>
-  <si>
-    <t>无求易决</t>
-  </si>
-  <si>
-    <t>·圣体</t>
-  </si>
-  <si>
-    <t>增加5%系数增幅</t>
-  </si>
-  <si>
-    <t>火麟剑诀</t>
-  </si>
-  <si>
-    <t>减少技能20%冷却时间</t>
-  </si>
-  <si>
-    <t>增加5%物攻增幅</t>
-  </si>
-  <si>
-    <t>·吸血</t>
-  </si>
-  <si>
-    <t>回复30%物攻的生命</t>
-  </si>
-  <si>
-    <t>·断河</t>
-  </si>
-  <si>
-    <t>剑阵的攻击范围增加一行一列</t>
-  </si>
-  <si>
-    <t>·致残</t>
-  </si>
-  <si>
-    <t>降低敌人50%的攻击速度</t>
+    <t>增加护盾加防效果30秒</t>
   </si>
   <si>
     <t>削减敌人50%护甲倍率</t>
@@ -555,6 +558,9 @@
     <t>火海的攻击范围增加一行一列</t>
   </si>
   <si>
+    <t>增加护盾加攻效果30秒</t>
+  </si>
+  <si>
     <t>·冰狱</t>
   </si>
   <si>
@@ -634,6 +640,9 @@
   </si>
   <si>
     <t>回复25%道术的生命</t>
+  </si>
+  <si>
+    <t>增加护盾加生命效果30秒</t>
   </si>
   <si>
     <t>·双生</t>
@@ -833,12 +842,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1631,7 +1640,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:AH68"/>
+  <dimension ref="C1:AH71"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="6" width="9" style="1"/>
@@ -2297,16 +2306,16 @@
         <v>69</v>
       </c>
       <c r="G10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="I10" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J10" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
         <v>0</v>
@@ -2368,13 +2377,13 @@
         <v>1006</v>
       </c>
       <c r="F11" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
@@ -2442,13 +2451,13 @@
         <v>1007</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I12" s="1">
         <v>20</v>
@@ -2523,10 +2532,10 @@
         <v>58</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
@@ -2603,10 +2612,10 @@
         <v>61</v>
       </c>
       <c r="G15" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="I15" s="1">
         <v>0</v>
@@ -2689,10 +2698,10 @@
         <v>64</v>
       </c>
       <c r="G16" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
@@ -2763,10 +2772,10 @@
         <v>67</v>
       </c>
       <c r="G17" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
@@ -2837,19 +2846,19 @@
     </row>
     <row r="18" customHeight="1" spans="3:34">
       <c r="C18" s="1">
-        <v>10072</v>
+        <v>10052</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
       </c>
       <c r="E18" s="1">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>84</v>
@@ -2903,282 +2912,291 @@
         <v>0</v>
       </c>
       <c r="AC18" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD18" s="4">
+        <v>12</v>
+      </c>
+      <c r="AD18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="1">
+        <v>30</v>
+      </c>
+      <c r="AF18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH18" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:34">
+      <c r="C19" s="1">
+        <v>10072</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1007</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0</v>
+      </c>
+      <c r="N19" s="1">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1">
+        <v>0</v>
+      </c>
+      <c r="P19" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>0</v>
+      </c>
+      <c r="R19" s="1">
+        <v>0</v>
+      </c>
+      <c r="S19" s="1">
+        <v>0</v>
+      </c>
+      <c r="T19" s="1">
+        <v>0</v>
+      </c>
+      <c r="U19" s="1">
+        <v>0</v>
+      </c>
+      <c r="V19" s="1">
+        <v>0</v>
+      </c>
+      <c r="W19" s="4">
+        <v>0</v>
+      </c>
+      <c r="X19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD19" s="4">
         <v>50</v>
       </c>
-      <c r="AE18" s="4">
+      <c r="AE19" s="4">
         <v>999</v>
       </c>
-      <c r="AF18" s="4">
-        <v>1</v>
-      </c>
-      <c r="AG18" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH18" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:34">
-      <c r="C20" s="1">
-        <v>10023</v>
-      </c>
-      <c r="D20" s="1">
-        <v>1</v>
-      </c>
-      <c r="E20" s="1">
-        <v>1002</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="I20" s="1">
-        <v>0</v>
-      </c>
-      <c r="J20" s="1">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
-        <v>2</v>
-      </c>
-      <c r="L20" s="1">
-        <v>0</v>
-      </c>
-      <c r="M20" s="1">
-        <v>0</v>
-      </c>
-      <c r="N20" s="1">
-        <v>0</v>
-      </c>
-      <c r="O20" s="1">
-        <v>0</v>
-      </c>
-      <c r="P20" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="1">
-        <v>0</v>
-      </c>
-      <c r="R20" s="1">
-        <v>0</v>
-      </c>
-      <c r="S20" s="1">
-        <v>0</v>
-      </c>
-      <c r="T20" s="1">
-        <v>0</v>
-      </c>
-      <c r="U20" s="1">
-        <v>0</v>
-      </c>
-      <c r="V20" s="1">
-        <v>0</v>
-      </c>
-      <c r="W20" s="4">
-        <v>0</v>
-      </c>
-      <c r="X20" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG20" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH20" s="1">
+      <c r="AF19" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG19" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH19" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:34">
       <c r="C21" s="1">
+        <v>10023</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1002</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
+        <v>2</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
+        <v>0</v>
+      </c>
+      <c r="N21" s="1">
+        <v>0</v>
+      </c>
+      <c r="O21" s="1">
+        <v>0</v>
+      </c>
+      <c r="P21" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>0</v>
+      </c>
+      <c r="R21" s="1">
+        <v>0</v>
+      </c>
+      <c r="S21" s="1">
+        <v>0</v>
+      </c>
+      <c r="T21" s="1">
+        <v>0</v>
+      </c>
+      <c r="U21" s="1">
+        <v>0</v>
+      </c>
+      <c r="V21" s="1">
+        <v>0</v>
+      </c>
+      <c r="W21" s="4">
+        <v>0</v>
+      </c>
+      <c r="X21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH21" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:34">
+      <c r="C22" s="1">
         <v>10073</v>
       </c>
-      <c r="D21" s="1">
-        <v>1</v>
-      </c>
-      <c r="E21" s="1">
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1">
         <v>1007</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="H21" s="1" t="s">
+      <c r="F22" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I21" s="1">
-        <v>0</v>
-      </c>
-      <c r="J21" s="1">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
-        <v>0</v>
-      </c>
-      <c r="L21" s="1">
-        <v>0</v>
-      </c>
-      <c r="M21" s="1">
-        <v>0</v>
-      </c>
-      <c r="N21" s="1">
-        <v>0</v>
-      </c>
-      <c r="O21" s="1">
-        <v>0</v>
-      </c>
-      <c r="P21" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="1">
-        <v>0</v>
-      </c>
-      <c r="R21" s="1">
-        <v>0</v>
-      </c>
-      <c r="S21" s="1">
-        <v>0</v>
-      </c>
-      <c r="T21" s="1">
-        <v>0</v>
-      </c>
-      <c r="U21" s="1">
-        <v>0</v>
-      </c>
-      <c r="V21" s="1">
-        <v>0</v>
-      </c>
-      <c r="W21" s="4">
-        <v>0</v>
-      </c>
-      <c r="X21" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="4">
+      <c r="H22" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I22" s="1">
+        <v>0</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1">
+        <v>0</v>
+      </c>
+      <c r="N22" s="1">
+        <v>0</v>
+      </c>
+      <c r="O22" s="1">
+        <v>0</v>
+      </c>
+      <c r="P22" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>0</v>
+      </c>
+      <c r="R22" s="1">
+        <v>0</v>
+      </c>
+      <c r="S22" s="1">
+        <v>0</v>
+      </c>
+      <c r="T22" s="1">
+        <v>0</v>
+      </c>
+      <c r="U22" s="1">
+        <v>0</v>
+      </c>
+      <c r="V22" s="1">
+        <v>0</v>
+      </c>
+      <c r="W22" s="4">
+        <v>0</v>
+      </c>
+      <c r="X22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="4">
         <v>206</v>
       </c>
-      <c r="AD21" s="1">
+      <c r="AD22" s="1">
         <v>20</v>
       </c>
-      <c r="AE21" s="4">
-        <v>5</v>
-      </c>
-      <c r="AF21" s="1">
+      <c r="AE22" s="4">
+        <v>5</v>
+      </c>
+      <c r="AF22" s="1">
         <v>3</v>
       </c>
-      <c r="AG21" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH21" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:34">
-      <c r="W22" s="4"/>
+      <c r="AG22" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH22" s="1">
+        <v>5</v>
+      </c>
     </row>
     <row r="23" customHeight="1" spans="3:34">
-      <c r="C23" s="1">
-        <v>10024</v>
-      </c>
-      <c r="D23" s="1">
-        <v>1</v>
-      </c>
-      <c r="E23" s="1">
-        <v>1002</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I23" s="1">
-        <v>0</v>
-      </c>
-      <c r="J23" s="1">
-        <v>0</v>
-      </c>
-      <c r="K23" s="1">
-        <v>0</v>
-      </c>
-      <c r="L23" s="1">
-        <v>0</v>
-      </c>
-      <c r="M23" s="1">
-        <v>0</v>
-      </c>
-      <c r="N23" s="1">
-        <v>0</v>
-      </c>
-      <c r="O23" s="1">
-        <v>0</v>
-      </c>
-      <c r="P23" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="1">
-        <v>0</v>
-      </c>
-      <c r="R23" s="1">
-        <v>0</v>
-      </c>
-      <c r="S23" s="1">
-        <v>0</v>
-      </c>
-      <c r="T23" s="1">
-        <v>0</v>
-      </c>
-      <c r="U23" s="1">
-        <v>0</v>
-      </c>
-      <c r="V23" s="1">
-        <v>0</v>
-      </c>
-      <c r="W23" s="4">
-        <v>0</v>
-      </c>
-      <c r="X23" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="1">
-        <v>100</v>
-      </c>
-      <c r="AG23" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH23" s="1">
-        <v>5</v>
-      </c>
+      <c r="W23" s="4"/>
     </row>
     <row r="24" customHeight="1" spans="3:34">
       <c r="C24" s="1">
-        <v>10034</v>
+        <v>10024</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
       </c>
       <c r="E24" s="1">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I24" s="1">
         <v>0</v>
@@ -3193,10 +3211,10 @@
         <v>0</v>
       </c>
       <c r="M24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" s="1">
         <v>0</v>
@@ -3239,110 +3257,107 @@
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:34">
-      <c r="W25" s="4"/>
-    </row>
-    <row r="26" s="2" customFormat="1" customHeight="1"/>
-    <row r="27" customHeight="1" spans="3:34">
-      <c r="C27" s="1">
-        <v>20011</v>
-      </c>
-      <c r="D27" s="1">
-        <v>2</v>
-      </c>
-      <c r="E27" s="4">
-        <v>2001</v>
-      </c>
-      <c r="F27" s="4" t="s">
+      <c r="C25" s="1">
+        <v>10034</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1003</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="I27" s="1">
-        <v>0</v>
-      </c>
-      <c r="J27" s="1">
-        <v>0</v>
-      </c>
-      <c r="K27" s="1">
-        <v>0</v>
-      </c>
-      <c r="L27" s="1">
-        <v>0</v>
-      </c>
-      <c r="M27" s="1">
-        <v>0</v>
-      </c>
-      <c r="N27" s="1">
-        <v>0</v>
-      </c>
-      <c r="O27" s="1">
-        <v>5</v>
-      </c>
-      <c r="P27" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="1">
-        <v>0</v>
-      </c>
-      <c r="R27" s="1">
-        <v>0</v>
-      </c>
-      <c r="S27" s="1">
-        <v>0</v>
-      </c>
-      <c r="T27" s="1">
-        <v>0</v>
-      </c>
-      <c r="U27" s="1">
-        <v>0</v>
-      </c>
-      <c r="V27" s="1">
-        <v>0</v>
-      </c>
-      <c r="W27" s="4">
-        <v>0</v>
-      </c>
-      <c r="X27" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="1">
-        <v>32</v>
-      </c>
-      <c r="AB27" s="1">
-        <v>20</v>
-      </c>
-      <c r="AG27" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH27" s="1">
-        <v>5</v>
-      </c>
-    </row>
+      <c r="I25" s="1">
+        <v>0</v>
+      </c>
+      <c r="J25" s="1">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1">
+        <v>0</v>
+      </c>
+      <c r="M25" s="1">
+        <v>1</v>
+      </c>
+      <c r="N25" s="1">
+        <v>1</v>
+      </c>
+      <c r="O25" s="1">
+        <v>0</v>
+      </c>
+      <c r="P25" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>0</v>
+      </c>
+      <c r="R25" s="1">
+        <v>0</v>
+      </c>
+      <c r="S25" s="1">
+        <v>0</v>
+      </c>
+      <c r="T25" s="1">
+        <v>0</v>
+      </c>
+      <c r="U25" s="1">
+        <v>0</v>
+      </c>
+      <c r="V25" s="1">
+        <v>0</v>
+      </c>
+      <c r="W25" s="4">
+        <v>0</v>
+      </c>
+      <c r="X25" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="1">
+        <v>100</v>
+      </c>
+      <c r="AG25" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH25" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:34">
+      <c r="W26" s="4"/>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1"/>
     <row r="28" customHeight="1" spans="3:34">
       <c r="C28" s="1">
-        <v>20021</v>
+        <v>20011</v>
       </c>
       <c r="D28" s="1">
         <v>2</v>
       </c>
       <c r="E28" s="4">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="F28" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H28" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G28" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="I28" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J28" s="1">
         <v>0</v>
@@ -3360,7 +3375,7 @@
         <v>0</v>
       </c>
       <c r="O28" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P28" s="1">
         <v>0</v>
@@ -3388,6 +3403,12 @@
       </c>
       <c r="X28" s="1">
         <v>0</v>
+      </c>
+      <c r="AA28" s="1">
+        <v>32</v>
+      </c>
+      <c r="AB28" s="1">
+        <v>20</v>
       </c>
       <c r="AG28" s="1">
         <v>1</v>
@@ -3398,25 +3419,25 @@
     </row>
     <row r="29" customHeight="1" spans="3:34">
       <c r="C29" s="1">
-        <v>20031</v>
+        <v>20021</v>
       </c>
       <c r="D29" s="1">
         <v>2</v>
       </c>
-      <c r="E29" s="1">
-        <v>2003</v>
+      <c r="E29" s="4">
+        <v>2002</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>95</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="I29" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J29" s="1">
         <v>0</v>
@@ -3462,18 +3483,6 @@
       </c>
       <c r="X29" s="1">
         <v>0</v>
-      </c>
-      <c r="AC29" s="1">
-        <v>6</v>
-      </c>
-      <c r="AD29" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE29" s="4">
-        <v>999</v>
-      </c>
-      <c r="AF29" s="1">
-        <v>50</v>
       </c>
       <c r="AG29" s="1">
         <v>1</v>
@@ -3484,23 +3493,23 @@
     </row>
     <row r="30" customHeight="1" spans="3:34">
       <c r="C30" s="1">
-        <v>20041</v>
+        <v>20031</v>
       </c>
       <c r="D30" s="1">
         <v>2</v>
       </c>
-      <c r="E30" s="4">
-        <v>2004</v>
+      <c r="E30" s="1">
+        <v>2003</v>
       </c>
       <c r="F30" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G30" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="I30" s="1">
         <v>0</v>
       </c>
@@ -3550,16 +3559,16 @@
         <v>0</v>
       </c>
       <c r="AC30" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AD30" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="AE30" s="4">
         <v>999</v>
       </c>
       <c r="AF30" s="1">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="AG30" s="1">
         <v>1</v>
@@ -3570,28 +3579,28 @@
     </row>
     <row r="31" customHeight="1" spans="3:34">
       <c r="C31" s="1">
-        <v>20051</v>
+        <v>20041</v>
       </c>
       <c r="D31" s="1">
         <v>2</v>
       </c>
       <c r="E31" s="4">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="F31" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="I31" s="1">
         <v>0</v>
       </c>
       <c r="J31" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
         <v>0</v>
@@ -3634,6 +3643,18 @@
       </c>
       <c r="X31" s="1">
         <v>0</v>
+      </c>
+      <c r="AC31" s="1">
+        <v>1</v>
+      </c>
+      <c r="AD31" s="1">
+        <v>20</v>
+      </c>
+      <c r="AE31" s="4">
+        <v>999</v>
+      </c>
+      <c r="AF31" s="1">
+        <v>3</v>
       </c>
       <c r="AG31" s="1">
         <v>1</v>
@@ -3644,25 +3665,25 @@
     </row>
     <row r="32" customHeight="1" spans="3:34">
       <c r="C32" s="1">
-        <v>20061</v>
+        <v>20051</v>
       </c>
       <c r="D32" s="1">
         <v>2</v>
       </c>
       <c r="E32" s="4">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>101</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I32" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J32" s="1">
         <v>0</v>
@@ -3680,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="O32" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P32" s="1">
         <v>0</v>
@@ -3718,187 +3739,187 @@
     </row>
     <row r="33" customHeight="1" spans="3:34">
       <c r="C33" s="1">
-        <v>20071</v>
+        <v>20061</v>
       </c>
       <c r="D33" s="1">
         <v>2</v>
       </c>
       <c r="E33" s="4">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>102</v>
       </c>
       <c r="G33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I33" s="1">
+        <v>0</v>
+      </c>
+      <c r="J33" s="1">
+        <v>0</v>
+      </c>
+      <c r="K33" s="1">
+        <v>0</v>
+      </c>
+      <c r="L33" s="1">
+        <v>0</v>
+      </c>
+      <c r="M33" s="1">
+        <v>0</v>
+      </c>
+      <c r="N33" s="1">
+        <v>0</v>
+      </c>
+      <c r="O33" s="1">
+        <v>5</v>
+      </c>
+      <c r="P33" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>0</v>
+      </c>
+      <c r="R33" s="1">
+        <v>0</v>
+      </c>
+      <c r="S33" s="1">
+        <v>0</v>
+      </c>
+      <c r="T33" s="1">
+        <v>0</v>
+      </c>
+      <c r="U33" s="1">
+        <v>0</v>
+      </c>
+      <c r="V33" s="1">
+        <v>0</v>
+      </c>
+      <c r="W33" s="4">
+        <v>0</v>
+      </c>
+      <c r="X33" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH33" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:34">
+      <c r="C34" s="1">
+        <v>20071</v>
+      </c>
+      <c r="D34" s="1">
+        <v>2</v>
+      </c>
+      <c r="E34" s="4">
+        <v>2007</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="G34" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="I33" s="1">
-        <v>0</v>
-      </c>
-      <c r="J33" s="1">
-        <v>0</v>
-      </c>
-      <c r="K33" s="1">
-        <v>0</v>
-      </c>
-      <c r="L33" s="1">
-        <v>0</v>
-      </c>
-      <c r="M33" s="1">
-        <v>0</v>
-      </c>
-      <c r="N33" s="1">
-        <v>0</v>
-      </c>
-      <c r="O33" s="1">
-        <v>0</v>
-      </c>
-      <c r="P33" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="1">
-        <v>0</v>
-      </c>
-      <c r="R33" s="1">
-        <v>0</v>
-      </c>
-      <c r="S33" s="1">
-        <v>0</v>
-      </c>
-      <c r="T33" s="1">
-        <v>0</v>
-      </c>
-      <c r="U33" s="1">
-        <v>0</v>
-      </c>
-      <c r="V33" s="1">
-        <v>0</v>
-      </c>
-      <c r="W33" s="4">
-        <v>0</v>
-      </c>
-      <c r="X33" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC33" s="1">
+      <c r="H34" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I34" s="1">
+        <v>0</v>
+      </c>
+      <c r="J34" s="1">
+        <v>0</v>
+      </c>
+      <c r="K34" s="1">
+        <v>0</v>
+      </c>
+      <c r="L34" s="1">
+        <v>0</v>
+      </c>
+      <c r="M34" s="1">
+        <v>0</v>
+      </c>
+      <c r="N34" s="1">
+        <v>0</v>
+      </c>
+      <c r="O34" s="1">
+        <v>0</v>
+      </c>
+      <c r="P34" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="1">
+        <v>0</v>
+      </c>
+      <c r="R34" s="1">
+        <v>0</v>
+      </c>
+      <c r="S34" s="1">
+        <v>0</v>
+      </c>
+      <c r="T34" s="1">
+        <v>0</v>
+      </c>
+      <c r="U34" s="1">
+        <v>0</v>
+      </c>
+      <c r="V34" s="1">
+        <v>0</v>
+      </c>
+      <c r="W34" s="4">
+        <v>0</v>
+      </c>
+      <c r="X34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="1">
         <v>6</v>
       </c>
-      <c r="AD33" s="4">
+      <c r="AD34" s="4">
         <v>10</v>
       </c>
-      <c r="AE33" s="4">
+      <c r="AE34" s="4">
         <v>999</v>
       </c>
-      <c r="AF33" s="4">
+      <c r="AF34" s="4">
         <v>3</v>
       </c>
-      <c r="AG33" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH33" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:34">
-      <c r="F34" s="4"/>
-      <c r="W34" s="4"/>
+      <c r="AG34" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH34" s="1">
+        <v>5</v>
+      </c>
     </row>
     <row r="35" customHeight="1" spans="3:34">
-      <c r="C35" s="1">
-        <v>20012</v>
-      </c>
-      <c r="D35" s="1">
-        <v>2</v>
-      </c>
-      <c r="E35" s="4">
-        <v>2001</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I35" s="1">
-        <v>0</v>
-      </c>
-      <c r="J35" s="1">
-        <v>0</v>
-      </c>
-      <c r="K35" s="1">
-        <v>0</v>
-      </c>
-      <c r="L35" s="1">
-        <v>0</v>
-      </c>
-      <c r="M35" s="1">
-        <v>0</v>
-      </c>
-      <c r="N35" s="1">
-        <v>0</v>
-      </c>
-      <c r="O35" s="1">
-        <v>5</v>
-      </c>
-      <c r="P35" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="1">
-        <v>0</v>
-      </c>
-      <c r="R35" s="1">
-        <v>0</v>
-      </c>
-      <c r="S35" s="1">
-        <v>0</v>
-      </c>
-      <c r="T35" s="1">
-        <v>0</v>
-      </c>
-      <c r="U35" s="1">
-        <v>0</v>
-      </c>
-      <c r="V35" s="1">
-        <v>0</v>
-      </c>
-      <c r="W35" s="4">
-        <v>0</v>
-      </c>
-      <c r="X35" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG35" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH35" s="1">
-        <v>5</v>
-      </c>
+      <c r="F35" s="4"/>
+      <c r="W35" s="4"/>
     </row>
     <row r="36" customHeight="1" spans="3:34">
       <c r="C36" s="1">
-        <v>20022</v>
+        <v>20012</v>
       </c>
       <c r="D36" s="1">
         <v>2</v>
       </c>
-      <c r="E36" s="1">
-        <v>2002</v>
+      <c r="E36" s="4">
+        <v>2001</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G36" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="H36" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="I36" s="1">
         <v>0</v>
       </c>
@@ -3918,7 +3939,7 @@
         <v>0</v>
       </c>
       <c r="O36" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P36" s="1">
         <v>0</v>
@@ -3946,18 +3967,6 @@
       </c>
       <c r="X36" s="1">
         <v>0</v>
-      </c>
-      <c r="AC36" s="1">
-        <v>102</v>
-      </c>
-      <c r="AD36" s="4">
-        <v>20</v>
-      </c>
-      <c r="AE36" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF36" s="4">
-        <v>1</v>
       </c>
       <c r="AG36" s="1">
         <v>1</v>
@@ -3968,23 +3977,23 @@
     </row>
     <row r="37" customHeight="1" spans="3:34">
       <c r="C37" s="1">
-        <v>20032</v>
+        <v>20022</v>
       </c>
       <c r="D37" s="1">
         <v>2</v>
       </c>
-      <c r="E37" s="4">
-        <v>2003</v>
+      <c r="E37" s="1">
+        <v>2002</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>95</v>
       </c>
       <c r="G37" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H37" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="I37" s="1">
         <v>0</v>
       </c>
@@ -3998,10 +4007,10 @@
         <v>0</v>
       </c>
       <c r="M37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37" s="1">
         <v>0</v>
@@ -4032,6 +4041,18 @@
       </c>
       <c r="X37" s="1">
         <v>0</v>
+      </c>
+      <c r="AC37" s="1">
+        <v>102</v>
+      </c>
+      <c r="AD37" s="4">
+        <v>20</v>
+      </c>
+      <c r="AE37" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF37" s="4">
+        <v>1</v>
       </c>
       <c r="AG37" s="1">
         <v>1</v>
@@ -4042,75 +4063,124 @@
     </row>
     <row r="38" customHeight="1" spans="3:34">
       <c r="C38" s="1">
-        <v>20072</v>
+        <v>20032</v>
       </c>
       <c r="D38" s="1">
         <v>2</v>
       </c>
-      <c r="E38" s="1">
-        <v>2007</v>
+      <c r="E38" s="4">
+        <v>2003</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G38" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="I38" s="1">
+        <v>0</v>
+      </c>
+      <c r="J38" s="1">
+        <v>0</v>
+      </c>
+      <c r="K38" s="1">
+        <v>0</v>
+      </c>
+      <c r="L38" s="1">
+        <v>0</v>
+      </c>
+      <c r="M38" s="1">
+        <v>1</v>
+      </c>
+      <c r="N38" s="1">
+        <v>1</v>
+      </c>
+      <c r="O38" s="1">
+        <v>0</v>
+      </c>
+      <c r="P38" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>0</v>
+      </c>
+      <c r="R38" s="1">
+        <v>0</v>
+      </c>
+      <c r="S38" s="1">
+        <v>0</v>
+      </c>
+      <c r="T38" s="1">
+        <v>0</v>
+      </c>
+      <c r="U38" s="1">
+        <v>0</v>
+      </c>
+      <c r="V38" s="1">
+        <v>0</v>
+      </c>
+      <c r="W38" s="4">
+        <v>0</v>
+      </c>
+      <c r="X38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG38" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH38" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:34">
+      <c r="C39" s="1">
+        <v>20052</v>
+      </c>
+      <c r="D39" s="1">
+        <v>2</v>
+      </c>
+      <c r="E39" s="4">
+        <v>2005</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H39" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="I38" s="1">
-        <v>0</v>
-      </c>
-      <c r="J38" s="1">
-        <v>0</v>
-      </c>
-      <c r="K38" s="1">
-        <v>0</v>
-      </c>
-      <c r="L38" s="1">
-        <v>0</v>
-      </c>
-      <c r="M38" s="1">
-        <v>1</v>
-      </c>
-      <c r="N38" s="1">
-        <v>1</v>
-      </c>
-      <c r="O38" s="1">
-        <v>0</v>
-      </c>
-      <c r="P38" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="1">
-        <v>0</v>
-      </c>
-      <c r="R38" s="1">
-        <v>0</v>
-      </c>
-      <c r="S38" s="1">
-        <v>0</v>
-      </c>
-      <c r="T38" s="1">
-        <v>0</v>
-      </c>
-      <c r="U38" s="1">
-        <v>0</v>
-      </c>
-      <c r="V38" s="1">
-        <v>0</v>
-      </c>
-      <c r="W38" s="4">
-        <v>0</v>
-      </c>
-      <c r="X38" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD38" s="4"/>
-      <c r="AE38" s="4"/>
-    </row>
-    <row r="39" customHeight="1" spans="3:34">
+      <c r="I39" s="1">
+        <v>0</v>
+      </c>
+      <c r="J39" s="1">
+        <v>0</v>
+      </c>
+      <c r="K39" s="1">
+        <v>0</v>
+      </c>
+      <c r="L39" s="1">
+        <v>0</v>
+      </c>
+      <c r="M39" s="1">
+        <v>0</v>
+      </c>
+      <c r="N39" s="1">
+        <v>0</v>
+      </c>
+      <c r="O39" s="1">
+        <v>0</v>
+      </c>
+      <c r="P39" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="1">
+        <v>0</v>
+      </c>
       <c r="R39" s="1">
         <v>0</v>
       </c>
@@ -4122,20 +4192,47 @@
       </c>
       <c r="U39" s="1">
         <v>0</v>
+      </c>
+      <c r="V39" s="1">
+        <v>0</v>
+      </c>
+      <c r="W39" s="4">
+        <v>0</v>
+      </c>
+      <c r="X39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="1">
+        <v>13</v>
+      </c>
+      <c r="AD39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="1">
+        <v>30</v>
+      </c>
+      <c r="AF39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG39" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH39" s="1">
+        <v>5</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:34">
       <c r="C40" s="1">
-        <v>20023</v>
+        <v>20072</v>
       </c>
       <c r="D40" s="1">
         <v>2</v>
       </c>
       <c r="E40" s="1">
-        <v>2002</v>
+        <v>2007</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>113</v>
@@ -4153,13 +4250,13 @@
         <v>0</v>
       </c>
       <c r="L40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O40" s="1">
         <v>0</v>
@@ -4191,59 +4288,10 @@
       <c r="X40" s="1">
         <v>0</v>
       </c>
-      <c r="AG40" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH40" s="1">
-        <v>5</v>
-      </c>
+      <c r="AD40" s="4"/>
+      <c r="AE40" s="4"/>
     </row>
     <row r="41" customHeight="1" spans="3:34">
-      <c r="C41" s="1">
-        <v>20043</v>
-      </c>
-      <c r="D41" s="1">
-        <v>2</v>
-      </c>
-      <c r="E41" s="1">
-        <v>2004</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="I41" s="1">
-        <v>0</v>
-      </c>
-      <c r="J41" s="1">
-        <v>0</v>
-      </c>
-      <c r="K41" s="1">
-        <v>0</v>
-      </c>
-      <c r="L41" s="1">
-        <v>0</v>
-      </c>
-      <c r="M41" s="1">
-        <v>0</v>
-      </c>
-      <c r="N41" s="1">
-        <v>0</v>
-      </c>
-      <c r="O41" s="1">
-        <v>0</v>
-      </c>
-      <c r="P41" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="1">
-        <v>0</v>
-      </c>
       <c r="R41" s="1">
         <v>0</v>
       </c>
@@ -4255,453 +4303,432 @@
       </c>
       <c r="U41" s="1">
         <v>0</v>
-      </c>
-      <c r="V41" s="1">
-        <v>0</v>
-      </c>
-      <c r="W41" s="4">
-        <v>0</v>
-      </c>
-      <c r="X41" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC41" s="1">
-        <v>7</v>
-      </c>
-      <c r="AD41" s="1">
-        <v>5</v>
-      </c>
-      <c r="AE41" s="4">
-        <v>999</v>
-      </c>
-      <c r="AF41" s="1">
-        <v>3</v>
-      </c>
-      <c r="AG41" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH41" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:34">
       <c r="C42" s="1">
-        <v>20073</v>
+        <v>20023</v>
       </c>
       <c r="D42" s="1">
         <v>2</v>
       </c>
       <c r="E42" s="1">
-        <v>2007</v>
+        <v>2002</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="G42" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="I42" s="1">
+        <v>0</v>
+      </c>
+      <c r="J42" s="1">
+        <v>0</v>
+      </c>
+      <c r="K42" s="1">
+        <v>0</v>
+      </c>
+      <c r="L42" s="1">
+        <v>1</v>
+      </c>
+      <c r="M42" s="1">
+        <v>0</v>
+      </c>
+      <c r="N42" s="1">
+        <v>0</v>
+      </c>
+      <c r="O42" s="1">
+        <v>0</v>
+      </c>
+      <c r="P42" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="1">
+        <v>0</v>
+      </c>
+      <c r="R42" s="1">
+        <v>0</v>
+      </c>
+      <c r="S42" s="1">
+        <v>0</v>
+      </c>
+      <c r="T42" s="1">
+        <v>0</v>
+      </c>
+      <c r="U42" s="1">
+        <v>0</v>
+      </c>
+      <c r="V42" s="1">
+        <v>0</v>
+      </c>
+      <c r="W42" s="4">
+        <v>0</v>
+      </c>
+      <c r="X42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH42" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:34">
+      <c r="C43" s="1">
+        <v>20043</v>
+      </c>
+      <c r="D43" s="1">
+        <v>2</v>
+      </c>
+      <c r="E43" s="1">
+        <v>2004</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="H43" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="I42" s="1">
-        <v>0</v>
-      </c>
-      <c r="J42" s="1">
-        <v>0</v>
-      </c>
-      <c r="K42" s="1">
-        <v>0</v>
-      </c>
-      <c r="L42" s="1">
-        <v>0</v>
-      </c>
-      <c r="M42" s="1">
-        <v>0</v>
-      </c>
-      <c r="N42" s="1">
-        <v>0</v>
-      </c>
-      <c r="O42" s="1">
-        <v>0</v>
-      </c>
-      <c r="P42" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="1">
-        <v>0</v>
-      </c>
-      <c r="R42" s="1">
-        <v>0</v>
-      </c>
-      <c r="S42" s="1">
-        <v>0</v>
-      </c>
-      <c r="T42" s="1">
-        <v>0</v>
-      </c>
-      <c r="U42" s="1">
-        <v>0</v>
-      </c>
-      <c r="V42" s="1">
-        <v>0</v>
-      </c>
-      <c r="W42" s="4">
-        <v>0</v>
-      </c>
-      <c r="X42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC42" s="1">
-        <v>4</v>
-      </c>
-      <c r="AD42" s="4">
-        <v>-30</v>
-      </c>
-      <c r="AE42" s="4">
+      <c r="I43" s="1">
+        <v>0</v>
+      </c>
+      <c r="J43" s="1">
+        <v>0</v>
+      </c>
+      <c r="K43" s="1">
+        <v>0</v>
+      </c>
+      <c r="L43" s="1">
+        <v>0</v>
+      </c>
+      <c r="M43" s="1">
+        <v>0</v>
+      </c>
+      <c r="N43" s="1">
+        <v>0</v>
+      </c>
+      <c r="O43" s="1">
+        <v>0</v>
+      </c>
+      <c r="P43" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="1">
+        <v>0</v>
+      </c>
+      <c r="R43" s="1">
+        <v>0</v>
+      </c>
+      <c r="S43" s="1">
+        <v>0</v>
+      </c>
+      <c r="T43" s="1">
+        <v>0</v>
+      </c>
+      <c r="U43" s="1">
+        <v>0</v>
+      </c>
+      <c r="V43" s="1">
+        <v>0</v>
+      </c>
+      <c r="W43" s="4">
+        <v>0</v>
+      </c>
+      <c r="X43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="1">
+        <v>7</v>
+      </c>
+      <c r="AD43" s="1">
+        <v>5</v>
+      </c>
+      <c r="AE43" s="4">
         <v>999</v>
       </c>
-      <c r="AF42" s="4">
-        <v>1</v>
-      </c>
-      <c r="AG42" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH42" s="1">
+      <c r="AF43" s="1">
+        <v>3</v>
+      </c>
+      <c r="AG43" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH43" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:34">
       <c r="C44" s="1">
-        <v>20024</v>
+        <v>20073</v>
       </c>
       <c r="D44" s="1">
         <v>2</v>
       </c>
       <c r="E44" s="1">
+        <v>2007</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I44" s="1">
+        <v>0</v>
+      </c>
+      <c r="J44" s="1">
+        <v>0</v>
+      </c>
+      <c r="K44" s="1">
+        <v>0</v>
+      </c>
+      <c r="L44" s="1">
+        <v>0</v>
+      </c>
+      <c r="M44" s="1">
+        <v>0</v>
+      </c>
+      <c r="N44" s="1">
+        <v>0</v>
+      </c>
+      <c r="O44" s="1">
+        <v>0</v>
+      </c>
+      <c r="P44" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>0</v>
+      </c>
+      <c r="R44" s="1">
+        <v>0</v>
+      </c>
+      <c r="S44" s="1">
+        <v>0</v>
+      </c>
+      <c r="T44" s="1">
+        <v>0</v>
+      </c>
+      <c r="U44" s="1">
+        <v>0</v>
+      </c>
+      <c r="V44" s="1">
+        <v>0</v>
+      </c>
+      <c r="W44" s="4">
+        <v>0</v>
+      </c>
+      <c r="X44" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="1">
+        <v>4</v>
+      </c>
+      <c r="AD44" s="4">
+        <v>-30</v>
+      </c>
+      <c r="AE44" s="4">
+        <v>999</v>
+      </c>
+      <c r="AF44" s="4">
+        <v>1</v>
+      </c>
+      <c r="AG44" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH44" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:34">
+      <c r="C46" s="1">
+        <v>20024</v>
+      </c>
+      <c r="D46" s="1">
+        <v>2</v>
+      </c>
+      <c r="E46" s="1">
         <v>2002</v>
       </c>
-      <c r="F44" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H44" s="1" t="s">
+      <c r="F46" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G46" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="I44" s="1">
-        <v>0</v>
-      </c>
-      <c r="J44" s="1">
-        <v>0</v>
-      </c>
-      <c r="K44" s="1">
-        <v>1</v>
-      </c>
-      <c r="L44" s="1">
-        <v>0</v>
-      </c>
-      <c r="M44" s="1">
-        <v>0</v>
-      </c>
-      <c r="N44" s="1">
-        <v>0</v>
-      </c>
-      <c r="O44" s="1">
-        <v>0</v>
-      </c>
-      <c r="P44" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="1">
-        <v>0</v>
-      </c>
-      <c r="R44" s="1">
-        <v>0</v>
-      </c>
-      <c r="S44" s="1">
-        <v>0</v>
-      </c>
-      <c r="T44" s="1">
-        <v>0</v>
-      </c>
-      <c r="U44" s="1">
-        <v>0</v>
-      </c>
-      <c r="V44" s="1">
-        <v>0</v>
-      </c>
-      <c r="W44" s="4">
-        <v>0</v>
-      </c>
-      <c r="X44" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z44" s="1">
+      <c r="H46" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I46" s="1">
+        <v>0</v>
+      </c>
+      <c r="J46" s="1">
+        <v>0</v>
+      </c>
+      <c r="K46" s="1">
+        <v>1</v>
+      </c>
+      <c r="L46" s="1">
+        <v>0</v>
+      </c>
+      <c r="M46" s="1">
+        <v>0</v>
+      </c>
+      <c r="N46" s="1">
+        <v>0</v>
+      </c>
+      <c r="O46" s="1">
+        <v>0</v>
+      </c>
+      <c r="P46" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="1">
+        <v>0</v>
+      </c>
+      <c r="R46" s="1">
+        <v>0</v>
+      </c>
+      <c r="S46" s="1">
+        <v>0</v>
+      </c>
+      <c r="T46" s="1">
+        <v>0</v>
+      </c>
+      <c r="U46" s="1">
+        <v>0</v>
+      </c>
+      <c r="V46" s="1">
+        <v>0</v>
+      </c>
+      <c r="W46" s="4">
+        <v>0</v>
+      </c>
+      <c r="X46" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="1">
         <v>100</v>
       </c>
-      <c r="AG44" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH44" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="3:34">
-      <c r="C45" s="1">
+      <c r="AG46" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH46" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:34">
+      <c r="C47" s="1">
         <v>20034</v>
       </c>
-      <c r="D45" s="1">
+      <c r="D47" s="1">
         <v>2</v>
       </c>
-      <c r="E45" s="1">
+      <c r="E47" s="1">
         <v>2003</v>
       </c>
-      <c r="F45" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H45" s="1" t="s">
+      <c r="F47" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G47" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="I45" s="1">
-        <v>0</v>
-      </c>
-      <c r="J45" s="1">
-        <v>0</v>
-      </c>
-      <c r="K45" s="1">
-        <v>0</v>
-      </c>
-      <c r="L45" s="1">
-        <v>0</v>
-      </c>
-      <c r="M45" s="1">
-        <v>0</v>
-      </c>
-      <c r="N45" s="1">
-        <v>0</v>
-      </c>
-      <c r="O45" s="1">
-        <v>0</v>
-      </c>
-      <c r="P45" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="1">
-        <v>0</v>
-      </c>
-      <c r="R45" s="1">
-        <v>0</v>
-      </c>
-      <c r="S45" s="1">
-        <v>0</v>
-      </c>
-      <c r="T45" s="1">
-        <v>0</v>
-      </c>
-      <c r="U45" s="1">
-        <v>0</v>
-      </c>
-      <c r="V45" s="1">
-        <v>0</v>
-      </c>
-      <c r="W45" s="4">
-        <v>0</v>
-      </c>
-      <c r="X45" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z45" s="1">
+      <c r="H47" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I47" s="1">
+        <v>0</v>
+      </c>
+      <c r="J47" s="1">
+        <v>0</v>
+      </c>
+      <c r="K47" s="1">
+        <v>0</v>
+      </c>
+      <c r="L47" s="1">
+        <v>0</v>
+      </c>
+      <c r="M47" s="1">
+        <v>0</v>
+      </c>
+      <c r="N47" s="1">
+        <v>0</v>
+      </c>
+      <c r="O47" s="1">
+        <v>0</v>
+      </c>
+      <c r="P47" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="1">
+        <v>0</v>
+      </c>
+      <c r="R47" s="1">
+        <v>0</v>
+      </c>
+      <c r="S47" s="1">
+        <v>0</v>
+      </c>
+      <c r="T47" s="1">
+        <v>0</v>
+      </c>
+      <c r="U47" s="1">
+        <v>0</v>
+      </c>
+      <c r="V47" s="1">
+        <v>0</v>
+      </c>
+      <c r="W47" s="4">
+        <v>0</v>
+      </c>
+      <c r="X47" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="1">
         <v>100</v>
       </c>
-      <c r="AG45" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH45" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" customFormat="1" customHeight="1" spans="3:34">
-      <c r="T48" s="1"/>
-      <c r="U48" s="1"/>
-    </row>
-    <row r="49" s="2" customFormat="1" customHeight="1"/>
-    <row r="50" customHeight="1" spans="3:34">
-      <c r="C50" s="1">
-        <v>30011</v>
-      </c>
-      <c r="D50" s="1">
-        <v>3</v>
-      </c>
-      <c r="E50" s="4">
-        <v>3001</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="I50" s="1">
-        <v>0</v>
-      </c>
-      <c r="J50" s="1">
-        <v>0</v>
-      </c>
-      <c r="K50" s="1">
-        <v>0</v>
-      </c>
-      <c r="L50" s="1">
-        <v>0</v>
-      </c>
-      <c r="M50" s="1">
-        <v>0</v>
-      </c>
-      <c r="N50" s="1">
-        <v>0</v>
-      </c>
-      <c r="O50" s="1">
-        <v>5</v>
-      </c>
-      <c r="P50" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="1">
-        <v>0</v>
-      </c>
-      <c r="R50" s="1">
-        <v>0</v>
-      </c>
-      <c r="S50" s="1">
-        <v>0</v>
-      </c>
-      <c r="T50" s="1">
-        <v>0</v>
-      </c>
-      <c r="U50" s="1">
-        <v>0</v>
-      </c>
-      <c r="V50" s="1">
-        <v>0</v>
-      </c>
-      <c r="W50" s="4">
-        <v>0</v>
-      </c>
-      <c r="X50" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA50" s="1">
-        <v>33</v>
-      </c>
-      <c r="AB50" s="1">
-        <v>20</v>
-      </c>
-      <c r="AG50" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH50" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:34">
-      <c r="C51" s="1">
-        <v>30021</v>
-      </c>
-      <c r="D51" s="1">
-        <v>3</v>
-      </c>
-      <c r="E51" s="4">
-        <v>3002</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I51" s="1">
-        <v>50</v>
-      </c>
-      <c r="J51" s="1">
-        <v>0</v>
-      </c>
-      <c r="K51" s="1">
-        <v>0</v>
-      </c>
-      <c r="L51" s="1">
-        <v>0</v>
-      </c>
-      <c r="M51" s="1">
-        <v>0</v>
-      </c>
-      <c r="N51" s="1">
-        <v>0</v>
-      </c>
-      <c r="O51" s="1">
-        <v>0</v>
-      </c>
-      <c r="P51" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="1">
-        <v>0</v>
-      </c>
-      <c r="R51" s="1">
-        <v>0</v>
-      </c>
-      <c r="S51" s="1">
-        <v>0</v>
-      </c>
-      <c r="T51" s="1">
-        <v>0</v>
-      </c>
-      <c r="U51" s="1">
-        <v>0</v>
-      </c>
-      <c r="V51" s="1">
-        <v>0</v>
-      </c>
-      <c r="W51" s="4">
-        <v>0</v>
-      </c>
-      <c r="X51" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG51" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH51" s="1">
-        <v>5</v>
-      </c>
-    </row>
+      <c r="AG47" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH47" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" customHeight="1" spans="3:34">
+      <c r="T50" s="1"/>
+      <c r="U50" s="1"/>
+    </row>
+    <row r="51" s="2" customFormat="1" customHeight="1"/>
     <row r="52" customHeight="1" spans="3:34">
       <c r="C52" s="1">
-        <v>30031</v>
+        <v>30011</v>
       </c>
       <c r="D52" s="1">
         <v>3</v>
       </c>
       <c r="E52" s="4">
-        <v>3003</v>
+        <v>3001</v>
       </c>
       <c r="F52" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H52" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="I52" s="1">
         <v>0</v>
       </c>
@@ -4721,7 +4748,7 @@
         <v>0</v>
       </c>
       <c r="O52" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P52" s="1">
         <v>0</v>
@@ -4750,17 +4777,11 @@
       <c r="X52" s="1">
         <v>0</v>
       </c>
-      <c r="AC52" s="1">
-        <v>2</v>
-      </c>
-      <c r="AD52" s="4">
-        <v>80</v>
-      </c>
-      <c r="AE52" s="4">
-        <v>999</v>
-      </c>
-      <c r="AF52" s="4">
-        <v>1</v>
+      <c r="AA52" s="1">
+        <v>33</v>
+      </c>
+      <c r="AB52" s="1">
+        <v>20</v>
       </c>
       <c r="AG52" s="1">
         <v>1</v>
@@ -4771,25 +4792,25 @@
     </row>
     <row r="53" customHeight="1" spans="3:34">
       <c r="C53" s="1">
-        <v>30041</v>
+        <v>30021</v>
       </c>
       <c r="D53" s="1">
         <v>3</v>
       </c>
       <c r="E53" s="4">
-        <v>3004</v>
+        <v>3002</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>127</v>
+        <v>62</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>128</v>
+        <v>63</v>
       </c>
       <c r="I53" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J53" s="1">
         <v>0</v>
@@ -4835,18 +4856,6 @@
       </c>
       <c r="X53" s="1">
         <v>0</v>
-      </c>
-      <c r="AC53" s="1">
-        <v>8</v>
-      </c>
-      <c r="AD53" s="1">
-        <v>100</v>
-      </c>
-      <c r="AE53" s="4">
-        <v>999</v>
-      </c>
-      <c r="AF53" s="1">
-        <v>1</v>
       </c>
       <c r="AG53" s="1">
         <v>1</v>
@@ -4857,22 +4866,22 @@
     </row>
     <row r="54" customHeight="1" spans="3:34">
       <c r="C54" s="1">
-        <v>30051</v>
+        <v>30031</v>
       </c>
       <c r="D54" s="1">
         <v>3</v>
       </c>
       <c r="E54" s="4">
-        <v>3005</v>
+        <v>3003</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="I54" s="1">
         <v>0</v>
@@ -4921,6 +4930,18 @@
       </c>
       <c r="X54" s="1">
         <v>0</v>
+      </c>
+      <c r="AC54" s="1">
+        <v>2</v>
+      </c>
+      <c r="AD54" s="4">
+        <v>80</v>
+      </c>
+      <c r="AE54" s="4">
+        <v>999</v>
+      </c>
+      <c r="AF54" s="4">
+        <v>1</v>
       </c>
       <c r="AG54" s="1">
         <v>1</v>
@@ -4931,23 +4952,23 @@
     </row>
     <row r="55" customHeight="1" spans="3:34">
       <c r="C55" s="1">
-        <v>30061</v>
+        <v>30041</v>
       </c>
       <c r="D55" s="1">
         <v>3</v>
       </c>
       <c r="E55" s="4">
-        <v>3006</v>
+        <v>3004</v>
       </c>
       <c r="F55" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H55" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="G55" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="I55" s="1">
         <v>0</v>
       </c>
@@ -4967,7 +4988,7 @@
         <v>0</v>
       </c>
       <c r="O55" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P55" s="1">
         <v>0</v>
@@ -4995,6 +5016,18 @@
       </c>
       <c r="X55" s="1">
         <v>0</v>
+      </c>
+      <c r="AC55" s="1">
+        <v>8</v>
+      </c>
+      <c r="AD55" s="1">
+        <v>100</v>
+      </c>
+      <c r="AE55" s="4">
+        <v>999</v>
+      </c>
+      <c r="AF55" s="1">
+        <v>1</v>
       </c>
       <c r="AG55" s="1">
         <v>1</v>
@@ -5005,96 +5038,170 @@
     </row>
     <row r="56" customHeight="1" spans="3:34">
       <c r="C56" s="1">
-        <v>30071</v>
+        <v>30051</v>
       </c>
       <c r="D56" s="1">
         <v>3</v>
       </c>
       <c r="E56" s="4">
-        <v>3007</v>
+        <v>3005</v>
       </c>
       <c r="F56" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I56" s="1">
+        <v>30</v>
+      </c>
+      <c r="J56" s="1">
+        <v>0</v>
+      </c>
+      <c r="K56" s="1">
+        <v>0</v>
+      </c>
+      <c r="L56" s="1">
+        <v>0</v>
+      </c>
+      <c r="M56" s="1">
+        <v>0</v>
+      </c>
+      <c r="N56" s="1">
+        <v>0</v>
+      </c>
+      <c r="O56" s="1">
+        <v>0</v>
+      </c>
+      <c r="P56" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="1">
+        <v>0</v>
+      </c>
+      <c r="R56" s="1">
+        <v>0</v>
+      </c>
+      <c r="S56" s="1">
+        <v>0</v>
+      </c>
+      <c r="T56" s="1">
+        <v>0</v>
+      </c>
+      <c r="U56" s="1">
+        <v>0</v>
+      </c>
+      <c r="V56" s="1">
+        <v>0</v>
+      </c>
+      <c r="W56" s="4">
+        <v>0</v>
+      </c>
+      <c r="X56" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG56" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH56" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:34">
+      <c r="C57" s="1">
+        <v>30061</v>
+      </c>
+      <c r="D57" s="1">
+        <v>3</v>
+      </c>
+      <c r="E57" s="4">
+        <v>3006</v>
+      </c>
+      <c r="F57" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="G56" s="1" t="s">
+      <c r="G57" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H57" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="H56" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I56" s="1">
-        <v>0</v>
-      </c>
-      <c r="J56" s="1">
-        <v>0</v>
-      </c>
-      <c r="K56" s="1">
-        <v>0</v>
-      </c>
-      <c r="L56" s="1">
-        <v>1</v>
-      </c>
-      <c r="M56" s="1">
-        <v>0</v>
-      </c>
-      <c r="N56" s="1">
-        <v>0</v>
-      </c>
-      <c r="O56" s="1">
-        <v>0</v>
-      </c>
-      <c r="P56" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="1">
-        <v>0</v>
-      </c>
-      <c r="R56" s="1">
-        <v>0</v>
-      </c>
-      <c r="S56" s="1">
-        <v>0</v>
-      </c>
-      <c r="T56" s="1">
-        <v>0</v>
-      </c>
-      <c r="U56" s="1">
-        <v>0</v>
-      </c>
-      <c r="V56" s="1">
-        <v>0</v>
-      </c>
-      <c r="W56" s="4">
-        <v>0</v>
-      </c>
-      <c r="X56" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG56" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH56" s="1">
+      <c r="I57" s="1">
+        <v>0</v>
+      </c>
+      <c r="J57" s="1">
+        <v>0</v>
+      </c>
+      <c r="K57" s="1">
+        <v>0</v>
+      </c>
+      <c r="L57" s="1">
+        <v>0</v>
+      </c>
+      <c r="M57" s="1">
+        <v>0</v>
+      </c>
+      <c r="N57" s="1">
+        <v>0</v>
+      </c>
+      <c r="O57" s="1">
+        <v>5</v>
+      </c>
+      <c r="P57" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="1">
+        <v>0</v>
+      </c>
+      <c r="R57" s="1">
+        <v>0</v>
+      </c>
+      <c r="S57" s="1">
+        <v>0</v>
+      </c>
+      <c r="T57" s="1">
+        <v>0</v>
+      </c>
+      <c r="U57" s="1">
+        <v>0</v>
+      </c>
+      <c r="V57" s="1">
+        <v>0</v>
+      </c>
+      <c r="W57" s="4">
+        <v>0</v>
+      </c>
+      <c r="X57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH57" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:34">
       <c r="C58" s="1">
-        <v>30012</v>
+        <v>30071</v>
       </c>
       <c r="D58" s="1">
         <v>3</v>
       </c>
       <c r="E58" s="4">
-        <v>3001</v>
+        <v>3007</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I58" s="1">
         <v>0</v>
@@ -5106,7 +5213,7 @@
         <v>0</v>
       </c>
       <c r="L58" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="1">
         <v>0</v>
@@ -5115,7 +5222,7 @@
         <v>0</v>
       </c>
       <c r="O58" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P58" s="1">
         <v>0</v>
@@ -5144,123 +5251,31 @@
       <c r="X58" s="1">
         <v>0</v>
       </c>
-      <c r="AA58" s="1">
-        <v>2006</v>
-      </c>
-      <c r="AB58" s="1">
-        <v>5</v>
-      </c>
       <c r="AG58" s="1">
         <v>1</v>
       </c>
       <c r="AH58" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" customHeight="1" spans="3:34">
-      <c r="C59" s="1">
-        <v>30022</v>
-      </c>
-      <c r="D59" s="1">
-        <v>3</v>
-      </c>
-      <c r="E59" s="4">
-        <v>3002</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I59" s="1">
-        <v>0</v>
-      </c>
-      <c r="J59" s="1">
-        <v>0</v>
-      </c>
-      <c r="K59" s="1">
-        <v>0</v>
-      </c>
-      <c r="L59" s="1">
-        <v>0</v>
-      </c>
-      <c r="M59" s="1">
-        <v>0</v>
-      </c>
-      <c r="N59" s="1">
-        <v>0</v>
-      </c>
-      <c r="O59" s="1">
-        <v>0</v>
-      </c>
-      <c r="P59" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="1">
-        <v>0</v>
-      </c>
-      <c r="R59" s="1">
-        <v>0</v>
-      </c>
-      <c r="S59" s="1">
-        <v>0</v>
-      </c>
-      <c r="T59" s="1">
-        <v>0</v>
-      </c>
-      <c r="U59" s="1">
-        <v>0</v>
-      </c>
-      <c r="V59" s="1">
-        <v>0</v>
-      </c>
-      <c r="W59" s="4">
-        <v>0</v>
-      </c>
-      <c r="X59" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC59" s="1">
-        <v>103</v>
-      </c>
-      <c r="AD59" s="1">
-        <v>25</v>
-      </c>
-      <c r="AE59" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF59" s="1">
-        <v>1</v>
-      </c>
-      <c r="AG59" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH59" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:34">
       <c r="C60" s="1">
-        <v>30032</v>
+        <v>30012</v>
       </c>
       <c r="D60" s="1">
         <v>3</v>
       </c>
       <c r="E60" s="4">
-        <v>3003</v>
+        <v>3001</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="I60" s="1">
         <v>0</v>
@@ -5281,7 +5296,7 @@
         <v>0</v>
       </c>
       <c r="O60" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P60" s="1">
         <v>0</v>
@@ -5310,43 +5325,123 @@
       <c r="X60" s="1">
         <v>0</v>
       </c>
-      <c r="AC60" s="1">
-        <v>6</v>
-      </c>
-      <c r="AD60" s="1">
-        <v>10</v>
-      </c>
-      <c r="AE60" s="4">
-        <v>999</v>
-      </c>
-      <c r="AF60" s="1">
+      <c r="AA60" s="1">
+        <v>2006</v>
+      </c>
+      <c r="AB60" s="1">
+        <v>5</v>
+      </c>
+      <c r="AG60" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH60" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:34">
+      <c r="C61" s="1">
+        <v>30022</v>
+      </c>
+      <c r="D61" s="1">
         <v>3</v>
       </c>
-      <c r="AG60" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH60" s="1">
+      <c r="E61" s="4">
+        <v>3002</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I61" s="1">
+        <v>0</v>
+      </c>
+      <c r="J61" s="1">
+        <v>0</v>
+      </c>
+      <c r="K61" s="1">
+        <v>0</v>
+      </c>
+      <c r="L61" s="1">
+        <v>0</v>
+      </c>
+      <c r="M61" s="1">
+        <v>0</v>
+      </c>
+      <c r="N61" s="1">
+        <v>0</v>
+      </c>
+      <c r="O61" s="1">
+        <v>0</v>
+      </c>
+      <c r="P61" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="1">
+        <v>0</v>
+      </c>
+      <c r="R61" s="1">
+        <v>0</v>
+      </c>
+      <c r="S61" s="1">
+        <v>0</v>
+      </c>
+      <c r="T61" s="1">
+        <v>0</v>
+      </c>
+      <c r="U61" s="1">
+        <v>0</v>
+      </c>
+      <c r="V61" s="1">
+        <v>0</v>
+      </c>
+      <c r="W61" s="4">
+        <v>0</v>
+      </c>
+      <c r="X61" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="1">
+        <v>103</v>
+      </c>
+      <c r="AD61" s="1">
+        <v>25</v>
+      </c>
+      <c r="AE61" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="1">
+        <v>1</v>
+      </c>
+      <c r="AG61" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH61" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:34">
       <c r="C62" s="1">
-        <v>30023</v>
+        <v>30032</v>
       </c>
       <c r="D62" s="1">
         <v>3</v>
       </c>
       <c r="E62" s="4">
-        <v>3002</v>
+        <v>3003</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="I62" s="1">
         <v>0</v>
@@ -5358,7 +5453,7 @@
         <v>0</v>
       </c>
       <c r="L62" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="1">
         <v>0</v>
@@ -5395,6 +5490,18 @@
       </c>
       <c r="X62" s="1">
         <v>0</v>
+      </c>
+      <c r="AC62" s="1">
+        <v>6</v>
+      </c>
+      <c r="AD62" s="1">
+        <v>10</v>
+      </c>
+      <c r="AE62" s="4">
+        <v>999</v>
+      </c>
+      <c r="AF62" s="1">
+        <v>3</v>
       </c>
       <c r="AG62" s="1">
         <v>1</v>
@@ -5405,19 +5512,19 @@
     </row>
     <row r="63" customHeight="1" spans="3:34">
       <c r="C63" s="1">
-        <v>30033</v>
+        <v>30052</v>
       </c>
       <c r="D63" s="1">
         <v>3</v>
       </c>
       <c r="E63" s="4">
-        <v>3003</v>
+        <v>3005</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>140</v>
@@ -5432,7 +5539,7 @@
         <v>0</v>
       </c>
       <c r="L63" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M63" s="1">
         <v>0</v>
@@ -5470,194 +5577,191 @@
       <c r="X63" s="1">
         <v>0</v>
       </c>
+      <c r="AC63" s="1">
+        <v>11</v>
+      </c>
+      <c r="AD63" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="1">
+        <v>30</v>
+      </c>
+      <c r="AF63" s="1">
+        <v>0</v>
+      </c>
       <c r="AG63" s="1">
         <v>1</v>
       </c>
       <c r="AH63" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" spans="3:34">
-      <c r="C64" s="1">
-        <v>30043</v>
-      </c>
-      <c r="D64" s="1">
-        <v>3</v>
-      </c>
-      <c r="E64" s="4">
-        <v>3004</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="I64" s="1">
-        <v>0</v>
-      </c>
-      <c r="J64" s="1">
-        <v>0</v>
-      </c>
-      <c r="K64" s="1">
-        <v>0</v>
-      </c>
-      <c r="L64" s="1">
-        <v>0</v>
-      </c>
-      <c r="M64" s="1">
-        <v>0</v>
-      </c>
-      <c r="N64" s="1">
-        <v>0</v>
-      </c>
-      <c r="O64" s="1">
-        <v>0</v>
-      </c>
-      <c r="P64" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="1">
-        <v>0</v>
-      </c>
-      <c r="R64" s="1">
-        <v>0</v>
-      </c>
-      <c r="S64" s="1">
-        <v>0</v>
-      </c>
-      <c r="T64" s="1">
-        <v>0</v>
-      </c>
-      <c r="U64" s="1">
-        <v>0</v>
-      </c>
-      <c r="V64" s="1">
-        <v>0</v>
-      </c>
-      <c r="W64" s="4">
-        <v>0</v>
-      </c>
-      <c r="X64" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC64" s="1">
-        <v>9</v>
-      </c>
-      <c r="AD64" s="1">
-        <v>10</v>
-      </c>
-      <c r="AE64" s="4">
-        <v>999</v>
-      </c>
-      <c r="AF64" s="1">
-        <v>3</v>
-      </c>
-      <c r="AG64" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH64" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:34">
       <c r="C65" s="1">
-        <v>30073</v>
+        <v>30023</v>
       </c>
       <c r="D65" s="1">
         <v>3</v>
       </c>
       <c r="E65" s="4">
-        <v>3007</v>
+        <v>3002</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="G65" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="I65" s="1">
+        <v>0</v>
+      </c>
+      <c r="J65" s="1">
+        <v>0</v>
+      </c>
+      <c r="K65" s="1">
+        <v>0</v>
+      </c>
+      <c r="L65" s="1">
+        <v>1</v>
+      </c>
+      <c r="M65" s="1">
+        <v>0</v>
+      </c>
+      <c r="N65" s="1">
+        <v>0</v>
+      </c>
+      <c r="O65" s="1">
+        <v>0</v>
+      </c>
+      <c r="P65" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="1">
+        <v>0</v>
+      </c>
+      <c r="R65" s="1">
+        <v>0</v>
+      </c>
+      <c r="S65" s="1">
+        <v>0</v>
+      </c>
+      <c r="T65" s="1">
+        <v>0</v>
+      </c>
+      <c r="U65" s="1">
+        <v>0</v>
+      </c>
+      <c r="V65" s="1">
+        <v>0</v>
+      </c>
+      <c r="W65" s="4">
+        <v>0</v>
+      </c>
+      <c r="X65" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH65" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:34">
+      <c r="C66" s="1">
+        <v>30033</v>
+      </c>
+      <c r="D66" s="1">
+        <v>3</v>
+      </c>
+      <c r="E66" s="4">
+        <v>3003</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H66" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="H65" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="I65" s="1">
-        <v>0</v>
-      </c>
-      <c r="J65" s="1">
-        <v>0</v>
-      </c>
-      <c r="K65" s="1">
-        <v>0</v>
-      </c>
-      <c r="L65" s="1">
-        <v>0</v>
-      </c>
-      <c r="M65" s="1">
-        <v>0</v>
-      </c>
-      <c r="N65" s="1">
-        <v>0</v>
-      </c>
-      <c r="O65" s="1">
-        <v>0</v>
-      </c>
-      <c r="P65" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="1">
-        <v>0</v>
-      </c>
-      <c r="R65" s="1">
-        <v>0</v>
-      </c>
-      <c r="S65" s="1">
-        <v>0</v>
-      </c>
-      <c r="T65" s="1">
-        <v>0</v>
-      </c>
-      <c r="U65" s="1">
-        <v>0</v>
-      </c>
-      <c r="V65" s="1">
-        <v>0</v>
-      </c>
-      <c r="W65" s="4">
-        <v>0</v>
-      </c>
-      <c r="X65" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC65" s="4">
-        <v>1001</v>
-      </c>
-      <c r="AG65" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH65" s="1">
+      <c r="I66" s="1">
+        <v>0</v>
+      </c>
+      <c r="J66" s="1">
+        <v>0</v>
+      </c>
+      <c r="K66" s="1">
+        <v>0</v>
+      </c>
+      <c r="L66" s="1">
+        <v>3</v>
+      </c>
+      <c r="M66" s="1">
+        <v>0</v>
+      </c>
+      <c r="N66" s="1">
+        <v>0</v>
+      </c>
+      <c r="O66" s="1">
+        <v>0</v>
+      </c>
+      <c r="P66" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="1">
+        <v>0</v>
+      </c>
+      <c r="R66" s="1">
+        <v>0</v>
+      </c>
+      <c r="S66" s="1">
+        <v>0</v>
+      </c>
+      <c r="T66" s="1">
+        <v>0</v>
+      </c>
+      <c r="U66" s="1">
+        <v>0</v>
+      </c>
+      <c r="V66" s="1">
+        <v>0</v>
+      </c>
+      <c r="W66" s="4">
+        <v>0</v>
+      </c>
+      <c r="X66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG66" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH66" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:34">
       <c r="C67" s="1">
-        <v>30024</v>
+        <v>30043</v>
       </c>
       <c r="D67" s="1">
         <v>3</v>
       </c>
       <c r="E67" s="4">
-        <v>3002</v>
+        <v>3004</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>89</v>
+        <v>144</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="I67" s="1">
         <v>0</v>
@@ -5669,7 +5773,7 @@
         <v>0</v>
       </c>
       <c r="L67" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" s="1">
         <v>0</v>
@@ -5707,8 +5811,17 @@
       <c r="X67" s="1">
         <v>0</v>
       </c>
-      <c r="Z67" s="1">
-        <v>100</v>
+      <c r="AC67" s="1">
+        <v>9</v>
+      </c>
+      <c r="AD67" s="1">
+        <v>10</v>
+      </c>
+      <c r="AE67" s="4">
+        <v>999</v>
+      </c>
+      <c r="AF67" s="1">
+        <v>3</v>
       </c>
       <c r="AG67" s="1">
         <v>1</v>
@@ -5719,78 +5832,232 @@
     </row>
     <row r="68" customHeight="1" spans="3:34">
       <c r="C68" s="1">
-        <v>30034</v>
+        <v>30073</v>
       </c>
       <c r="D68" s="1">
         <v>3</v>
       </c>
       <c r="E68" s="4">
+        <v>3007</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I68" s="1">
+        <v>0</v>
+      </c>
+      <c r="J68" s="1">
+        <v>0</v>
+      </c>
+      <c r="K68" s="1">
+        <v>0</v>
+      </c>
+      <c r="L68" s="1">
+        <v>0</v>
+      </c>
+      <c r="M68" s="1">
+        <v>0</v>
+      </c>
+      <c r="N68" s="1">
+        <v>0</v>
+      </c>
+      <c r="O68" s="1">
+        <v>0</v>
+      </c>
+      <c r="P68" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="1">
+        <v>0</v>
+      </c>
+      <c r="R68" s="1">
+        <v>0</v>
+      </c>
+      <c r="S68" s="1">
+        <v>0</v>
+      </c>
+      <c r="T68" s="1">
+        <v>0</v>
+      </c>
+      <c r="U68" s="1">
+        <v>0</v>
+      </c>
+      <c r="V68" s="1">
+        <v>0</v>
+      </c>
+      <c r="W68" s="4">
+        <v>0</v>
+      </c>
+      <c r="X68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="4">
+        <v>1001</v>
+      </c>
+      <c r="AG68" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH68" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:34">
+      <c r="C70" s="1">
+        <v>30024</v>
+      </c>
+      <c r="D70" s="1">
+        <v>3</v>
+      </c>
+      <c r="E70" s="4">
+        <v>3002</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I70" s="1">
+        <v>0</v>
+      </c>
+      <c r="J70" s="1">
+        <v>0</v>
+      </c>
+      <c r="K70" s="1">
+        <v>0</v>
+      </c>
+      <c r="L70" s="1">
+        <v>1</v>
+      </c>
+      <c r="M70" s="1">
+        <v>0</v>
+      </c>
+      <c r="N70" s="1">
+        <v>0</v>
+      </c>
+      <c r="O70" s="1">
+        <v>0</v>
+      </c>
+      <c r="P70" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="1">
+        <v>0</v>
+      </c>
+      <c r="R70" s="1">
+        <v>0</v>
+      </c>
+      <c r="S70" s="1">
+        <v>0</v>
+      </c>
+      <c r="T70" s="1">
+        <v>0</v>
+      </c>
+      <c r="U70" s="1">
+        <v>0</v>
+      </c>
+      <c r="V70" s="1">
+        <v>0</v>
+      </c>
+      <c r="W70" s="4">
+        <v>0</v>
+      </c>
+      <c r="X70" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="1">
+        <v>100</v>
+      </c>
+      <c r="AG70" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH70" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:34">
+      <c r="C71" s="1">
+        <v>30034</v>
+      </c>
+      <c r="D71" s="1">
+        <v>3</v>
+      </c>
+      <c r="E71" s="4">
         <v>3003</v>
       </c>
-      <c r="F68" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H68" s="1" t="s">
+      <c r="F71" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G71" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="I68" s="1">
-        <v>0</v>
-      </c>
-      <c r="J68" s="1">
-        <v>0</v>
-      </c>
-      <c r="K68" s="1">
-        <v>0</v>
-      </c>
-      <c r="L68" s="1">
-        <v>0</v>
-      </c>
-      <c r="M68" s="1">
-        <v>0</v>
-      </c>
-      <c r="N68" s="1">
-        <v>0</v>
-      </c>
-      <c r="O68" s="1">
-        <v>0</v>
-      </c>
-      <c r="P68" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="1">
-        <v>0</v>
-      </c>
-      <c r="R68" s="1">
-        <v>0</v>
-      </c>
-      <c r="S68" s="1">
-        <v>0</v>
-      </c>
-      <c r="T68" s="1">
-        <v>0</v>
-      </c>
-      <c r="U68" s="1">
-        <v>0</v>
-      </c>
-      <c r="V68" s="1">
-        <v>0</v>
-      </c>
-      <c r="W68" s="4">
-        <v>0</v>
-      </c>
-      <c r="X68" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z68" s="1">
+      <c r="H71" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I71" s="1">
+        <v>0</v>
+      </c>
+      <c r="J71" s="1">
+        <v>0</v>
+      </c>
+      <c r="K71" s="1">
+        <v>0</v>
+      </c>
+      <c r="L71" s="1">
+        <v>0</v>
+      </c>
+      <c r="M71" s="1">
+        <v>0</v>
+      </c>
+      <c r="N71" s="1">
+        <v>0</v>
+      </c>
+      <c r="O71" s="1">
+        <v>0</v>
+      </c>
+      <c r="P71" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="1">
+        <v>0</v>
+      </c>
+      <c r="R71" s="1">
+        <v>0</v>
+      </c>
+      <c r="S71" s="1">
+        <v>0</v>
+      </c>
+      <c r="T71" s="1">
+        <v>0</v>
+      </c>
+      <c r="U71" s="1">
+        <v>0</v>
+      </c>
+      <c r="V71" s="1">
+        <v>0</v>
+      </c>
+      <c r="W71" s="4">
+        <v>0</v>
+      </c>
+      <c r="X71" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="1">
         <v>100</v>
       </c>
-      <c r="AG68" s="1">
-        <v>1</v>
-      </c>
-      <c r="AH68" s="1">
+      <c r="AG71" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH71" s="1">
         <v>5</v>
       </c>
     </row>

--- a/Excel/SkillTalentConfig.xlsx
+++ b/Excel/SkillTalentConfig.xlsx
@@ -495,7 +495,7 @@
     <t>·疾风</t>
   </si>
   <si>
-    <t>此技能攻击速度增加100%</t>
+    <t>此技能攻击速度增加50%</t>
   </si>
   <si>
     <t>冥想心法</t>
@@ -842,12 +842,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3247,7 +3247,7 @@
         <v>0</v>
       </c>
       <c r="Z24" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AG24" s="1">
         <v>1</v>
@@ -3324,7 +3324,7 @@
         <v>0</v>
       </c>
       <c r="Z25" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AG25" s="1">
         <v>1</v>
@@ -4619,7 +4619,7 @@
         <v>0</v>
       </c>
       <c r="Z46" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AG46" s="1">
         <v>1</v>
@@ -4696,7 +4696,7 @@
         <v>0</v>
       </c>
       <c r="Z47" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AG47" s="1">
         <v>1</v>
@@ -5975,7 +5975,7 @@
         <v>0</v>
       </c>
       <c r="Z70" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AG70" s="1">
         <v>1</v>
@@ -6052,7 +6052,7 @@
         <v>0</v>
       </c>
       <c r="Z71" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AG71" s="1">
         <v>1</v>

--- a/Excel/SkillTalentConfig.xlsx
+++ b/Excel/SkillTalentConfig.xlsx
@@ -842,12 +842,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4447,7 +4447,7 @@
         <v>0</v>
       </c>
       <c r="AC43" s="1">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AD43" s="1">
         <v>5</v>
@@ -5812,7 +5812,7 @@
         <v>0</v>
       </c>
       <c r="AC67" s="1">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AD67" s="1">
         <v>10</v>

--- a/Excel/SkillTalentConfig.xlsx
+++ b/Excel/SkillTalentConfig.xlsx
@@ -842,12 +842,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="M25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" s="1">
         <v>0</v>
@@ -4577,7 +4577,7 @@
         <v>0</v>
       </c>
       <c r="K46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="1">
         <v>0</v>
@@ -5936,7 +5936,7 @@
         <v>0</v>
       </c>
       <c r="L70" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" s="1">
         <v>0</v>

--- a/Excel/SkillTalentConfig.xlsx
+++ b/Excel/SkillTalentConfig.xlsx
@@ -842,12 +842,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5018,7 +5018,7 @@
         <v>0</v>
       </c>
       <c r="AC55" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AD55" s="1">
         <v>100</v>

--- a/Excel/SkillTalentConfig.xlsx
+++ b/Excel/SkillTalentConfig.xlsx
@@ -612,7 +612,7 @@
     <t>·御甲</t>
   </si>
   <si>
-    <t>增加100%护甲倍率</t>
+    <t>增加75%护甲倍率</t>
   </si>
   <si>
     <t>太虚麟盾</t>
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="AA6" s="1">
-        <v>31</v>
+        <v>1007</v>
       </c>
       <c r="AB6" s="1">
         <v>20</v>
@@ -3405,7 +3405,7 @@
         <v>0</v>
       </c>
       <c r="AA28" s="1">
-        <v>32</v>
+        <v>1008</v>
       </c>
       <c r="AB28" s="1">
         <v>20</v>
@@ -4778,7 +4778,7 @@
         <v>0</v>
       </c>
       <c r="AA52" s="1">
-        <v>33</v>
+        <v>1009</v>
       </c>
       <c r="AB52" s="1">
         <v>20</v>
@@ -5021,7 +5021,7 @@
         <v>12</v>
       </c>
       <c r="AD55" s="1">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AE55" s="4">
         <v>999</v>

--- a/Excel/SkillTalentConfig.xlsx
+++ b/Excel/SkillTalentConfig.xlsx
@@ -220,7 +220,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="147">
   <si>
     <t>#</t>
   </si>
@@ -447,16 +447,13 @@
     <t>火麟剑诀</t>
   </si>
   <si>
-    <t>减少技能20%冷却时间</t>
-  </si>
-  <si>
     <t>增加5%物攻增幅</t>
   </si>
   <si>
     <t>·吸血</t>
   </si>
   <si>
-    <t>回复30%物攻的生命</t>
+    <t>回复15%物攻的生命</t>
   </si>
   <si>
     <t>·断河</t>
@@ -549,7 +546,7 @@
     <t>·汲取</t>
   </si>
   <si>
-    <t>回复20%魔攻的生命</t>
+    <t>回复15%魔攻的生命</t>
   </si>
   <si>
     <t>·火狱</t>
@@ -582,7 +579,7 @@
     <t>·冻结</t>
   </si>
   <si>
-    <t>敌人降低30%的攻击速度</t>
+    <t>敌人降低50%的攻击速度</t>
   </si>
   <si>
     <t>清心咒</t>
@@ -612,7 +609,7 @@
     <t>·御甲</t>
   </si>
   <si>
-    <t>增加75%护甲倍率</t>
+    <t>增加50%护甲倍率</t>
   </si>
   <si>
     <t>太虚麟盾</t>
@@ -639,7 +636,7 @@
     <t>·回复</t>
   </si>
   <si>
-    <t>回复25%道术的生命</t>
+    <t>回复15%道术的生命</t>
   </si>
   <si>
     <t>增加护盾加生命效果30秒</t>
@@ -2457,10 +2454,10 @@
         <v>62</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="I12" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J12" s="1">
         <v>0</v>
@@ -2535,7 +2532,7 @@
         <v>72</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
@@ -2612,10 +2609,10 @@
         <v>61</v>
       </c>
       <c r="G15" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="I15" s="1">
         <v>0</v>
@@ -2669,7 +2666,7 @@
         <v>101</v>
       </c>
       <c r="AD15" s="4">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AE15" s="4">
         <v>0</v>
@@ -2698,10 +2695,10 @@
         <v>64</v>
       </c>
       <c r="G16" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
@@ -2772,10 +2769,10 @@
         <v>67</v>
       </c>
       <c r="G17" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
@@ -2858,10 +2855,10 @@
         <v>69</v>
       </c>
       <c r="G18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="I18" s="1">
         <v>0</v>
@@ -2947,7 +2944,7 @@
         <v>65</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I19" s="1">
         <v>0</v>
@@ -3030,10 +3027,10 @@
         <v>61</v>
       </c>
       <c r="G21" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="I21" s="1">
         <v>0</v>
@@ -3104,10 +3101,10 @@
         <v>74</v>
       </c>
       <c r="G22" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="I22" s="1">
         <v>0</v>
@@ -3193,10 +3190,10 @@
         <v>61</v>
       </c>
       <c r="G24" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="I24" s="1">
         <v>0</v>
@@ -3270,10 +3267,10 @@
         <v>64</v>
       </c>
       <c r="G25" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="I25" s="1">
         <v>0</v>
@@ -3348,13 +3345,13 @@
         <v>2001</v>
       </c>
       <c r="F28" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="H28" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="I28" s="1">
         <v>0</v>
@@ -3428,7 +3425,7 @@
         <v>2002</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>62</v>
@@ -3502,13 +3499,13 @@
         <v>2003</v>
       </c>
       <c r="F30" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="H30" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="I30" s="1">
         <v>0</v>
@@ -3588,13 +3585,13 @@
         <v>2004</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>65</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I31" s="1">
         <v>0</v>
@@ -3674,7 +3671,7 @@
         <v>2005</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>62</v>
@@ -3748,7 +3745,7 @@
         <v>2006</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>72</v>
@@ -3822,13 +3819,13 @@
         <v>2007</v>
       </c>
       <c r="F34" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="H34" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="I34" s="1">
         <v>0</v>
@@ -3912,13 +3909,13 @@
         <v>2001</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G36" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="I36" s="1">
         <v>0</v>
@@ -3986,13 +3983,13 @@
         <v>2002</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G37" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="I37" s="1">
         <v>0</v>
@@ -4046,7 +4043,7 @@
         <v>102</v>
       </c>
       <c r="AD37" s="4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AE37" s="4">
         <v>0</v>
@@ -4072,13 +4069,13 @@
         <v>2003</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G38" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="I38" s="1">
         <v>0</v>
@@ -4146,13 +4143,13 @@
         <v>2005</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I39" s="1">
         <v>0</v>
@@ -4232,13 +4229,13 @@
         <v>2007</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G40" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H40" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="I40" s="1">
         <v>0</v>
@@ -4316,13 +4313,13 @@
         <v>2002</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G42" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H42" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="I42" s="1">
         <v>0</v>
@@ -4390,13 +4387,13 @@
         <v>2004</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G43" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H43" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="I43" s="1">
         <v>0</v>
@@ -4476,13 +4473,13 @@
         <v>2007</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G44" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H44" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="I44" s="1">
         <v>0</v>
@@ -4536,7 +4533,7 @@
         <v>4</v>
       </c>
       <c r="AD44" s="4">
-        <v>-30</v>
+        <v>-50</v>
       </c>
       <c r="AE44" s="4">
         <v>999</v>
@@ -4562,13 +4559,13 @@
         <v>2002</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G46" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H46" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="I46" s="1">
         <v>0</v>
@@ -4639,13 +4636,13 @@
         <v>2003</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G47" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H47" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="I47" s="1">
         <v>0</v>
@@ -4721,13 +4718,13 @@
         <v>3001</v>
       </c>
       <c r="F52" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G52" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="G52" s="1" t="s">
+      <c r="H52" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="I52" s="1">
         <v>0</v>
@@ -4801,7 +4798,7 @@
         <v>3002</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>62</v>
@@ -4875,13 +4872,13 @@
         <v>3003</v>
       </c>
       <c r="F54" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G54" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="G54" s="1" t="s">
+      <c r="H54" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>127</v>
       </c>
       <c r="I54" s="1">
         <v>0</v>
@@ -4961,13 +4958,13 @@
         <v>3004</v>
       </c>
       <c r="F55" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G55" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="G55" s="1" t="s">
+      <c r="H55" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="I55" s="1">
         <v>0</v>
@@ -5021,7 +5018,7 @@
         <v>12</v>
       </c>
       <c r="AD55" s="1">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AE55" s="4">
         <v>999</v>
@@ -5047,7 +5044,7 @@
         <v>3005</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>62</v>
@@ -5121,13 +5118,13 @@
         <v>3006</v>
       </c>
       <c r="F57" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H57" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>133</v>
       </c>
       <c r="I57" s="1">
         <v>0</v>
@@ -5195,13 +5192,13 @@
         <v>3007</v>
       </c>
       <c r="F58" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G58" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="G58" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="H58" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I58" s="1">
         <v>0</v>
@@ -5269,13 +5266,13 @@
         <v>3001</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G60" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H60" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="I60" s="1">
         <v>0</v>
@@ -5349,13 +5346,13 @@
         <v>3002</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G61" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H61" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>139</v>
       </c>
       <c r="I61" s="1">
         <v>0</v>
@@ -5409,7 +5406,7 @@
         <v>103</v>
       </c>
       <c r="AD61" s="1">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AE61" s="1">
         <v>0</v>
@@ -5435,13 +5432,13 @@
         <v>3003</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I62" s="1">
         <v>0</v>
@@ -5521,13 +5518,13 @@
         <v>3005</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I63" s="1">
         <v>0</v>
@@ -5607,13 +5604,13 @@
         <v>3002</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I65" s="1">
         <v>0</v>
@@ -5681,13 +5678,13 @@
         <v>3003</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G66" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H66" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="I66" s="1">
         <v>0</v>
@@ -5755,13 +5752,13 @@
         <v>3004</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G67" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="H67" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>145</v>
       </c>
       <c r="I67" s="1">
         <v>0</v>
@@ -5841,13 +5838,13 @@
         <v>3007</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G68" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H68" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>147</v>
       </c>
       <c r="I68" s="1">
         <v>0</v>
@@ -5918,13 +5915,13 @@
         <v>3002</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G70" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H70" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="I70" s="1">
         <v>0</v>
@@ -5995,13 +5992,13 @@
         <v>3003</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G71" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H71" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="I71" s="1">
         <v>0</v>

--- a/Excel/SkillTalentConfig.xlsx
+++ b/Excel/SkillTalentConfig.xlsx
@@ -1,13 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="手动配置" sheetId="2" r:id="rId1"/>
+    <sheet name="道具" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -219,8 +225,201 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>admin</author>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+ID* 10 + level
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+0 以自己为圆心
+1 距离1格</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+攻击力系数（百分比），额外附加固定伤害值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AD3" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+特效值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AF3" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+特效最大叠加层数
+0 无限次
+1 单次</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AC4" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+特效ID</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AD4" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+特效值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AF4" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+特效最大叠加层数
+0 无限次
+1 单次</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="149">
   <si>
     <t>#</t>
   </si>
@@ -661,6 +860,12 @@
   </si>
   <si>
     <t>神兽获得人物的灭魂符</t>
+  </si>
+  <si>
+    <t>·鹰眼</t>
+  </si>
+  <si>
+    <t>攻击距离加1格</t>
   </si>
 </sst>
 </file>
@@ -859,13 +1064,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1313,11 +1518,11 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1676,290 +1881,290 @@
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="3:34">
-      <c r="C3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3" t="s">
+      <c r="F3" s="2"/>
+      <c r="G3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="P3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="Q3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="R3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="S3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="T3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="3" t="s">
+      <c r="U3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="V3" s="3" t="s">
+      <c r="V3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="W3" s="3" t="s">
+      <c r="W3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="X3" s="3" t="s">
+      <c r="X3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="Y3" s="3" t="s">
+      <c r="Y3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Z3" s="3" t="s">
+      <c r="Z3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="AA3" s="3" t="s">
+      <c r="AA3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AB3" s="3" t="s">
+      <c r="AB3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AC3" s="3" t="s">
+      <c r="AC3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AD3" s="3" t="s">
+      <c r="AD3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AE3" s="3" t="s">
+      <c r="AE3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AF3" s="3" t="s">
+      <c r="AF3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AG3" s="3" t="s">
+      <c r="AG3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AH3" s="3" t="s">
+      <c r="AH3" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="3:34">
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3" t="s">
+      <c r="F4" s="2"/>
+      <c r="G4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="N4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="O4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="P4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="Q4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="R4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="S4" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="T4" s="3" t="s">
+      <c r="T4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="U4" s="3" t="s">
+      <c r="U4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="V4" s="3" t="s">
+      <c r="V4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="W4" s="3" t="s">
+      <c r="W4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="X4" s="3" t="s">
+      <c r="X4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Y4" s="3" t="s">
+      <c r="Y4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Z4" s="3" t="s">
+      <c r="Z4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="AA4" s="3" t="s">
+      <c r="AA4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="AB4" s="3" t="s">
+      <c r="AB4" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AC4" s="3" t="s">
+      <c r="AC4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AD4" s="3" t="s">
+      <c r="AD4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AE4" s="3" t="s">
+      <c r="AE4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AF4" s="3" t="s">
+      <c r="AF4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AG4" s="3" t="s">
+      <c r="AG4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AH4" s="3" t="s">
+      <c r="AH4" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="3:34">
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3" t="s">
+      <c r="F5" s="2"/>
+      <c r="G5" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="L5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="M5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="N5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="O5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="P5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Q5" s="3" t="s">
+      <c r="Q5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="R5" s="3" t="s">
+      <c r="R5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="S5" s="3" t="s">
+      <c r="S5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="T5" s="3" t="s">
+      <c r="T5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U5" s="3" t="s">
+      <c r="U5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="V5" s="3" t="s">
+      <c r="V5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="W5" s="3" t="s">
+      <c r="W5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="X5" s="3" t="s">
+      <c r="X5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Y5" s="3" t="s">
+      <c r="Y5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Z5" s="3" t="s">
+      <c r="Z5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="AA5" s="3" t="s">
+      <c r="AA5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="AB5" s="3" t="s">
+      <c r="AB5" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AC5" s="3" t="s">
+      <c r="AC5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="AD5" s="3" t="s">
+      <c r="AD5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="AE5" s="3" t="s">
+      <c r="AE5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="AF5" s="3" t="s">
+      <c r="AF5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="AG5" s="3" t="s">
+      <c r="AG5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="AH5" s="3" t="s">
+      <c r="AH5" s="2" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1973,7 +2178,7 @@
       <c r="E6" s="1">
         <v>1001</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>58</v>
       </c>
       <c r="G6" s="1" t="s">
@@ -2024,7 +2229,7 @@
       <c r="V6" s="1">
         <v>0</v>
       </c>
-      <c r="W6" s="4">
+      <c r="W6" s="3">
         <v>0</v>
       </c>
       <c r="X6" s="1">
@@ -2053,7 +2258,7 @@
       <c r="E7" s="1">
         <v>1002</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>61</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -2104,7 +2309,7 @@
       <c r="V7" s="1">
         <v>0</v>
       </c>
-      <c r="W7" s="4">
+      <c r="W7" s="3">
         <v>0</v>
       </c>
       <c r="X7" s="1">
@@ -2127,7 +2332,7 @@
       <c r="E8" s="1">
         <v>1003</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>64</v>
       </c>
       <c r="G8" s="1" t="s">
@@ -2178,7 +2383,7 @@
       <c r="V8" s="1">
         <v>0</v>
       </c>
-      <c r="W8" s="4">
+      <c r="W8" s="3">
         <v>0</v>
       </c>
       <c r="X8" s="1">
@@ -2187,13 +2392,13 @@
       <c r="AC8" s="1">
         <v>1</v>
       </c>
-      <c r="AD8" s="4">
-        <v>1</v>
-      </c>
-      <c r="AE8" s="4">
+      <c r="AD8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="3">
         <v>999</v>
       </c>
-      <c r="AF8" s="4">
+      <c r="AF8" s="3">
         <v>90</v>
       </c>
       <c r="AG8" s="1">
@@ -2213,7 +2418,7 @@
       <c r="E9" s="1">
         <v>1004</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G9" s="1" t="s">
@@ -2264,7 +2469,7 @@
       <c r="V9" s="1">
         <v>0</v>
       </c>
-      <c r="W9" s="4">
+      <c r="W9" s="3">
         <v>0</v>
       </c>
       <c r="X9" s="1">
@@ -2273,13 +2478,13 @@
       <c r="AC9" s="1">
         <v>1</v>
       </c>
-      <c r="AD9" s="4">
+      <c r="AD9" s="3">
         <v>80</v>
       </c>
-      <c r="AE9" s="4">
+      <c r="AE9" s="3">
         <v>5</v>
       </c>
-      <c r="AF9" s="4">
+      <c r="AF9" s="3">
         <v>1</v>
       </c>
       <c r="AG9" s="1">
@@ -2299,7 +2504,7 @@
       <c r="E10" s="1">
         <v>1005</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>69</v>
       </c>
       <c r="G10" s="1" t="s">
@@ -2350,7 +2555,7 @@
       <c r="V10" s="1">
         <v>0</v>
       </c>
-      <c r="W10" s="4">
+      <c r="W10" s="3">
         <v>0</v>
       </c>
       <c r="X10" s="1">
@@ -2373,7 +2578,7 @@
       <c r="E11" s="1">
         <v>1006</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>71</v>
       </c>
       <c r="G11" s="1" t="s">
@@ -2424,7 +2629,7 @@
       <c r="V11" s="1">
         <v>0</v>
       </c>
-      <c r="W11" s="4">
+      <c r="W11" s="3">
         <v>0</v>
       </c>
       <c r="X11" s="1">
@@ -2447,7 +2652,7 @@
       <c r="E12" s="1">
         <v>1007</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>74</v>
       </c>
       <c r="G12" s="1" t="s">
@@ -2498,7 +2703,7 @@
       <c r="V12" s="1">
         <v>0</v>
       </c>
-      <c r="W12" s="4">
+      <c r="W12" s="3">
         <v>0</v>
       </c>
       <c r="X12" s="1">
@@ -2512,8 +2717,8 @@
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:34">
-      <c r="F13" s="4"/>
-      <c r="W13" s="4"/>
+      <c r="F13" s="3"/>
+      <c r="W13" s="3"/>
     </row>
     <row r="14" customHeight="1" spans="3:34">
       <c r="C14" s="1">
@@ -2525,7 +2730,7 @@
       <c r="E14" s="1">
         <v>1001</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>58</v>
       </c>
       <c r="G14" s="1" t="s">
@@ -2576,7 +2781,7 @@
       <c r="V14" s="1">
         <v>0</v>
       </c>
-      <c r="W14" s="4">
+      <c r="W14" s="3">
         <v>0</v>
       </c>
       <c r="X14" s="1">
@@ -2605,7 +2810,7 @@
       <c r="E15" s="1">
         <v>1002</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="3" t="s">
         <v>61</v>
       </c>
       <c r="G15" s="1" t="s">
@@ -2656,7 +2861,7 @@
       <c r="V15" s="1">
         <v>0</v>
       </c>
-      <c r="W15" s="4">
+      <c r="W15" s="3">
         <v>0</v>
       </c>
       <c r="X15" s="1">
@@ -2665,13 +2870,13 @@
       <c r="AC15" s="1">
         <v>101</v>
       </c>
-      <c r="AD15" s="4">
+      <c r="AD15" s="3">
         <v>15</v>
       </c>
-      <c r="AE15" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="4">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="3">
         <v>1</v>
       </c>
       <c r="AG15" s="1">
@@ -2691,7 +2896,7 @@
       <c r="E16" s="1">
         <v>1003</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="3" t="s">
         <v>64</v>
       </c>
       <c r="G16" s="1" t="s">
@@ -2742,7 +2947,7 @@
       <c r="V16" s="1">
         <v>0</v>
       </c>
-      <c r="W16" s="4">
+      <c r="W16" s="3">
         <v>0</v>
       </c>
       <c r="X16" s="1">
@@ -2765,7 +2970,7 @@
       <c r="E17" s="1">
         <v>1004</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G17" s="1" t="s">
@@ -2816,7 +3021,7 @@
       <c r="V17" s="1">
         <v>0</v>
       </c>
-      <c r="W17" s="4">
+      <c r="W17" s="3">
         <v>0</v>
       </c>
       <c r="X17" s="1">
@@ -2825,13 +3030,13 @@
       <c r="AC17" s="1">
         <v>4</v>
       </c>
-      <c r="AD17" s="4">
+      <c r="AD17" s="3">
         <v>-50</v>
       </c>
-      <c r="AE17" s="4">
+      <c r="AE17" s="3">
         <v>999</v>
       </c>
-      <c r="AF17" s="4">
+      <c r="AF17" s="3">
         <v>1</v>
       </c>
       <c r="AG17" s="1">
@@ -2851,7 +3056,7 @@
       <c r="E18" s="1">
         <v>1005</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="3" t="s">
         <v>69</v>
       </c>
       <c r="G18" s="1" t="s">
@@ -2902,7 +3107,7 @@
       <c r="V18" s="1">
         <v>0</v>
       </c>
-      <c r="W18" s="4">
+      <c r="W18" s="3">
         <v>0</v>
       </c>
       <c r="X18" s="1">
@@ -2937,7 +3142,7 @@
       <c r="E19" s="1">
         <v>1007</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="3" t="s">
         <v>74</v>
       </c>
       <c r="G19" s="1" t="s">
@@ -2988,7 +3193,7 @@
       <c r="V19" s="1">
         <v>0</v>
       </c>
-      <c r="W19" s="4">
+      <c r="W19" s="3">
         <v>0</v>
       </c>
       <c r="X19" s="1">
@@ -2997,13 +3202,13 @@
       <c r="AC19" s="1">
         <v>1</v>
       </c>
-      <c r="AD19" s="4">
+      <c r="AD19" s="3">
         <v>50</v>
       </c>
-      <c r="AE19" s="4">
+      <c r="AE19" s="3">
         <v>999</v>
       </c>
-      <c r="AF19" s="4">
+      <c r="AF19" s="3">
         <v>1</v>
       </c>
       <c r="AG19" s="1">
@@ -3023,7 +3228,7 @@
       <c r="E21" s="1">
         <v>1002</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="3" t="s">
         <v>61</v>
       </c>
       <c r="G21" s="1" t="s">
@@ -3074,7 +3279,7 @@
       <c r="V21" s="1">
         <v>0</v>
       </c>
-      <c r="W21" s="4">
+      <c r="W21" s="3">
         <v>0</v>
       </c>
       <c r="X21" s="1">
@@ -3097,7 +3302,7 @@
       <c r="E22" s="1">
         <v>1007</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="3" t="s">
         <v>74</v>
       </c>
       <c r="G22" s="1" t="s">
@@ -3148,19 +3353,19 @@
       <c r="V22" s="1">
         <v>0</v>
       </c>
-      <c r="W22" s="4">
+      <c r="W22" s="3">
         <v>0</v>
       </c>
       <c r="X22" s="1">
         <v>0</v>
       </c>
-      <c r="AC22" s="4">
+      <c r="AC22" s="3">
         <v>206</v>
       </c>
       <c r="AD22" s="1">
         <v>20</v>
       </c>
-      <c r="AE22" s="4">
+      <c r="AE22" s="3">
         <v>5</v>
       </c>
       <c r="AF22" s="1">
@@ -3174,7 +3379,7 @@
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:34">
-      <c r="W23" s="4"/>
+      <c r="W23" s="3"/>
     </row>
     <row r="24" customHeight="1" spans="3:34">
       <c r="C24" s="1">
@@ -3186,7 +3391,7 @@
       <c r="E24" s="1">
         <v>1002</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="3" t="s">
         <v>61</v>
       </c>
       <c r="G24" s="1" t="s">
@@ -3237,7 +3442,7 @@
       <c r="V24" s="1">
         <v>0</v>
       </c>
-      <c r="W24" s="4">
+      <c r="W24" s="3">
         <v>0</v>
       </c>
       <c r="X24" s="1">
@@ -3263,7 +3468,7 @@
       <c r="E25" s="1">
         <v>1003</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="3" t="s">
         <v>64</v>
       </c>
       <c r="G25" s="1" t="s">
@@ -3314,7 +3519,7 @@
       <c r="V25" s="1">
         <v>0</v>
       </c>
-      <c r="W25" s="4">
+      <c r="W25" s="3">
         <v>0</v>
       </c>
       <c r="X25" s="1">
@@ -3331,9 +3536,9 @@
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:34">
-      <c r="W26" s="4"/>
-    </row>
-    <row r="27" s="2" customFormat="1" customHeight="1"/>
+      <c r="W26" s="3"/>
+    </row>
+    <row r="27" s="4" customFormat="1" customHeight="1"/>
     <row r="28" customHeight="1" spans="3:34">
       <c r="C28" s="1">
         <v>20011</v>
@@ -3341,10 +3546,10 @@
       <c r="D28" s="1">
         <v>2</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="3">
         <v>2001</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="3" t="s">
         <v>91</v>
       </c>
       <c r="G28" s="1" t="s">
@@ -3395,7 +3600,7 @@
       <c r="V28" s="1">
         <v>0</v>
       </c>
-      <c r="W28" s="4">
+      <c r="W28" s="3">
         <v>0</v>
       </c>
       <c r="X28" s="1">
@@ -3421,10 +3626,10 @@
       <c r="D29" s="1">
         <v>2</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="3">
         <v>2002</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="3" t="s">
         <v>94</v>
       </c>
       <c r="G29" s="1" t="s">
@@ -3475,7 +3680,7 @@
       <c r="V29" s="1">
         <v>0</v>
       </c>
-      <c r="W29" s="4">
+      <c r="W29" s="3">
         <v>0</v>
       </c>
       <c r="X29" s="1">
@@ -3498,7 +3703,7 @@
       <c r="E30" s="1">
         <v>2003</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="3" t="s">
         <v>95</v>
       </c>
       <c r="G30" s="1" t="s">
@@ -3549,7 +3754,7 @@
       <c r="V30" s="1">
         <v>0</v>
       </c>
-      <c r="W30" s="4">
+      <c r="W30" s="3">
         <v>0</v>
       </c>
       <c r="X30" s="1">
@@ -3561,7 +3766,7 @@
       <c r="AD30" s="1">
         <v>1</v>
       </c>
-      <c r="AE30" s="4">
+      <c r="AE30" s="3">
         <v>999</v>
       </c>
       <c r="AF30" s="1">
@@ -3581,10 +3786,10 @@
       <c r="D31" s="1">
         <v>2</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="3">
         <v>2004</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="F31" s="3" t="s">
         <v>98</v>
       </c>
       <c r="G31" s="1" t="s">
@@ -3635,7 +3840,7 @@
       <c r="V31" s="1">
         <v>0</v>
       </c>
-      <c r="W31" s="4">
+      <c r="W31" s="3">
         <v>0</v>
       </c>
       <c r="X31" s="1">
@@ -3647,7 +3852,7 @@
       <c r="AD31" s="1">
         <v>20</v>
       </c>
-      <c r="AE31" s="4">
+      <c r="AE31" s="3">
         <v>999</v>
       </c>
       <c r="AF31" s="1">
@@ -3667,10 +3872,10 @@
       <c r="D32" s="1">
         <v>2</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E32" s="3">
         <v>2005</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="3" t="s">
         <v>100</v>
       </c>
       <c r="G32" s="1" t="s">
@@ -3721,7 +3926,7 @@
       <c r="V32" s="1">
         <v>0</v>
       </c>
-      <c r="W32" s="4">
+      <c r="W32" s="3">
         <v>0</v>
       </c>
       <c r="X32" s="1">
@@ -3741,10 +3946,10 @@
       <c r="D33" s="1">
         <v>2</v>
       </c>
-      <c r="E33" s="4">
+      <c r="E33" s="3">
         <v>2006</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F33" s="3" t="s">
         <v>101</v>
       </c>
       <c r="G33" s="1" t="s">
@@ -3795,7 +4000,7 @@
       <c r="V33" s="1">
         <v>0</v>
       </c>
-      <c r="W33" s="4">
+      <c r="W33" s="3">
         <v>0</v>
       </c>
       <c r="X33" s="1">
@@ -3815,10 +4020,10 @@
       <c r="D34" s="1">
         <v>2</v>
       </c>
-      <c r="E34" s="4">
+      <c r="E34" s="3">
         <v>2007</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="3" t="s">
         <v>102</v>
       </c>
       <c r="G34" s="1" t="s">
@@ -3869,7 +4074,7 @@
       <c r="V34" s="1">
         <v>0</v>
       </c>
-      <c r="W34" s="4">
+      <c r="W34" s="3">
         <v>0</v>
       </c>
       <c r="X34" s="1">
@@ -3878,13 +4083,13 @@
       <c r="AC34" s="1">
         <v>6</v>
       </c>
-      <c r="AD34" s="4">
+      <c r="AD34" s="3">
         <v>10</v>
       </c>
-      <c r="AE34" s="4">
+      <c r="AE34" s="3">
         <v>999</v>
       </c>
-      <c r="AF34" s="4">
+      <c r="AF34" s="3">
         <v>3</v>
       </c>
       <c r="AG34" s="1">
@@ -3895,8 +4100,8 @@
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:34">
-      <c r="F35" s="4"/>
-      <c r="W35" s="4"/>
+      <c r="F35" s="3"/>
+      <c r="W35" s="3"/>
     </row>
     <row r="36" customHeight="1" spans="3:34">
       <c r="C36" s="1">
@@ -3905,10 +4110,10 @@
       <c r="D36" s="1">
         <v>2</v>
       </c>
-      <c r="E36" s="4">
+      <c r="E36" s="3">
         <v>2001</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="3" t="s">
         <v>91</v>
       </c>
       <c r="G36" s="1" t="s">
@@ -3959,7 +4164,7 @@
       <c r="V36" s="1">
         <v>0</v>
       </c>
-      <c r="W36" s="4">
+      <c r="W36" s="3">
         <v>0</v>
       </c>
       <c r="X36" s="1">
@@ -3982,7 +4187,7 @@
       <c r="E37" s="1">
         <v>2002</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F37" s="3" t="s">
         <v>94</v>
       </c>
       <c r="G37" s="1" t="s">
@@ -4033,7 +4238,7 @@
       <c r="V37" s="1">
         <v>0</v>
       </c>
-      <c r="W37" s="4">
+      <c r="W37" s="3">
         <v>0</v>
       </c>
       <c r="X37" s="1">
@@ -4042,13 +4247,13 @@
       <c r="AC37" s="1">
         <v>102</v>
       </c>
-      <c r="AD37" s="4">
+      <c r="AD37" s="3">
         <v>15</v>
       </c>
-      <c r="AE37" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF37" s="4">
+      <c r="AE37" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF37" s="3">
         <v>1</v>
       </c>
       <c r="AG37" s="1">
@@ -4065,10 +4270,10 @@
       <c r="D38" s="1">
         <v>2</v>
       </c>
-      <c r="E38" s="4">
+      <c r="E38" s="3">
         <v>2003</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="3" t="s">
         <v>95</v>
       </c>
       <c r="G38" s="1" t="s">
@@ -4119,7 +4324,7 @@
       <c r="V38" s="1">
         <v>0</v>
       </c>
-      <c r="W38" s="4">
+      <c r="W38" s="3">
         <v>0</v>
       </c>
       <c r="X38" s="1">
@@ -4139,10 +4344,10 @@
       <c r="D39" s="1">
         <v>2</v>
       </c>
-      <c r="E39" s="4">
+      <c r="E39" s="3">
         <v>2005</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="F39" s="3" t="s">
         <v>100</v>
       </c>
       <c r="G39" s="1" t="s">
@@ -4193,7 +4398,7 @@
       <c r="V39" s="1">
         <v>0</v>
       </c>
-      <c r="W39" s="4">
+      <c r="W39" s="3">
         <v>0</v>
       </c>
       <c r="X39" s="1">
@@ -4228,7 +4433,7 @@
       <c r="E40" s="1">
         <v>2007</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="F40" s="3" t="s">
         <v>102</v>
       </c>
       <c r="G40" s="1" t="s">
@@ -4279,14 +4484,14 @@
       <c r="V40" s="1">
         <v>0</v>
       </c>
-      <c r="W40" s="4">
+      <c r="W40" s="3">
         <v>0</v>
       </c>
       <c r="X40" s="1">
         <v>0</v>
       </c>
-      <c r="AD40" s="4"/>
-      <c r="AE40" s="4"/>
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
     </row>
     <row r="41" customHeight="1" spans="3:34">
       <c r="R41" s="1">
@@ -4312,7 +4517,7 @@
       <c r="E42" s="1">
         <v>2002</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="F42" s="3" t="s">
         <v>94</v>
       </c>
       <c r="G42" s="1" t="s">
@@ -4363,7 +4568,7 @@
       <c r="V42" s="1">
         <v>0</v>
       </c>
-      <c r="W42" s="4">
+      <c r="W42" s="3">
         <v>0</v>
       </c>
       <c r="X42" s="1">
@@ -4386,7 +4591,7 @@
       <c r="E43" s="1">
         <v>2004</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F43" s="3" t="s">
         <v>98</v>
       </c>
       <c r="G43" s="1" t="s">
@@ -4437,7 +4642,7 @@
       <c r="V43" s="1">
         <v>0</v>
       </c>
-      <c r="W43" s="4">
+      <c r="W43" s="3">
         <v>0</v>
       </c>
       <c r="X43" s="1">
@@ -4449,7 +4654,7 @@
       <c r="AD43" s="1">
         <v>5</v>
       </c>
-      <c r="AE43" s="4">
+      <c r="AE43" s="3">
         <v>999</v>
       </c>
       <c r="AF43" s="1">
@@ -4472,7 +4677,7 @@
       <c r="E44" s="1">
         <v>2007</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F44" s="3" t="s">
         <v>102</v>
       </c>
       <c r="G44" s="1" t="s">
@@ -4523,7 +4728,7 @@
       <c r="V44" s="1">
         <v>0</v>
       </c>
-      <c r="W44" s="4">
+      <c r="W44" s="3">
         <v>0</v>
       </c>
       <c r="X44" s="1">
@@ -4532,13 +4737,13 @@
       <c r="AC44" s="1">
         <v>4</v>
       </c>
-      <c r="AD44" s="4">
+      <c r="AD44" s="3">
         <v>-50</v>
       </c>
-      <c r="AE44" s="4">
+      <c r="AE44" s="3">
         <v>999</v>
       </c>
-      <c r="AF44" s="4">
+      <c r="AF44" s="3">
         <v>1</v>
       </c>
       <c r="AG44" s="1">
@@ -4558,7 +4763,7 @@
       <c r="E46" s="1">
         <v>2002</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F46" s="3" t="s">
         <v>94</v>
       </c>
       <c r="G46" s="1" t="s">
@@ -4609,7 +4814,7 @@
       <c r="V46" s="1">
         <v>0</v>
       </c>
-      <c r="W46" s="4">
+      <c r="W46" s="3">
         <v>0</v>
       </c>
       <c r="X46" s="1">
@@ -4635,7 +4840,7 @@
       <c r="E47" s="1">
         <v>2003</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="F47" s="3" t="s">
         <v>95</v>
       </c>
       <c r="G47" s="1" t="s">
@@ -4686,7 +4891,7 @@
       <c r="V47" s="1">
         <v>0</v>
       </c>
-      <c r="W47" s="4">
+      <c r="W47" s="3">
         <v>0</v>
       </c>
       <c r="X47" s="1">
@@ -4706,7 +4911,7 @@
       <c r="T50" s="1"/>
       <c r="U50" s="1"/>
     </row>
-    <row r="51" s="2" customFormat="1" customHeight="1"/>
+    <row r="51" s="4" customFormat="1" customHeight="1"/>
     <row r="52" customHeight="1" spans="3:34">
       <c r="C52" s="1">
         <v>30011</v>
@@ -4714,10 +4919,10 @@
       <c r="D52" s="1">
         <v>3</v>
       </c>
-      <c r="E52" s="4">
+      <c r="E52" s="3">
         <v>3001</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="F52" s="3" t="s">
         <v>120</v>
       </c>
       <c r="G52" s="1" t="s">
@@ -4768,7 +4973,7 @@
       <c r="V52" s="1">
         <v>0</v>
       </c>
-      <c r="W52" s="4">
+      <c r="W52" s="3">
         <v>0</v>
       </c>
       <c r="X52" s="1">
@@ -4794,10 +4999,10 @@
       <c r="D53" s="1">
         <v>3</v>
       </c>
-      <c r="E53" s="4">
+      <c r="E53" s="3">
         <v>3002</v>
       </c>
-      <c r="F53" s="4" t="s">
+      <c r="F53" s="3" t="s">
         <v>123</v>
       </c>
       <c r="G53" s="1" t="s">
@@ -4848,7 +5053,7 @@
       <c r="V53" s="1">
         <v>0</v>
       </c>
-      <c r="W53" s="4">
+      <c r="W53" s="3">
         <v>0</v>
       </c>
       <c r="X53" s="1">
@@ -4868,10 +5073,10 @@
       <c r="D54" s="1">
         <v>3</v>
       </c>
-      <c r="E54" s="4">
+      <c r="E54" s="3">
         <v>3003</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="F54" s="3" t="s">
         <v>124</v>
       </c>
       <c r="G54" s="1" t="s">
@@ -4922,7 +5127,7 @@
       <c r="V54" s="1">
         <v>0</v>
       </c>
-      <c r="W54" s="4">
+      <c r="W54" s="3">
         <v>0</v>
       </c>
       <c r="X54" s="1">
@@ -4931,13 +5136,13 @@
       <c r="AC54" s="1">
         <v>2</v>
       </c>
-      <c r="AD54" s="4">
+      <c r="AD54" s="3">
         <v>80</v>
       </c>
-      <c r="AE54" s="4">
+      <c r="AE54" s="3">
         <v>999</v>
       </c>
-      <c r="AF54" s="4">
+      <c r="AF54" s="3">
         <v>1</v>
       </c>
       <c r="AG54" s="1">
@@ -4954,10 +5159,10 @@
       <c r="D55" s="1">
         <v>3</v>
       </c>
-      <c r="E55" s="4">
+      <c r="E55" s="3">
         <v>3004</v>
       </c>
-      <c r="F55" s="4" t="s">
+      <c r="F55" s="3" t="s">
         <v>127</v>
       </c>
       <c r="G55" s="1" t="s">
@@ -5008,7 +5213,7 @@
       <c r="V55" s="1">
         <v>0</v>
       </c>
-      <c r="W55" s="4">
+      <c r="W55" s="3">
         <v>0</v>
       </c>
       <c r="X55" s="1">
@@ -5020,7 +5225,7 @@
       <c r="AD55" s="1">
         <v>50</v>
       </c>
-      <c r="AE55" s="4">
+      <c r="AE55" s="3">
         <v>999</v>
       </c>
       <c r="AF55" s="1">
@@ -5040,10 +5245,10 @@
       <c r="D56" s="1">
         <v>3</v>
       </c>
-      <c r="E56" s="4">
+      <c r="E56" s="3">
         <v>3005</v>
       </c>
-      <c r="F56" s="4" t="s">
+      <c r="F56" s="3" t="s">
         <v>130</v>
       </c>
       <c r="G56" s="1" t="s">
@@ -5094,7 +5299,7 @@
       <c r="V56" s="1">
         <v>0</v>
       </c>
-      <c r="W56" s="4">
+      <c r="W56" s="3">
         <v>0</v>
       </c>
       <c r="X56" s="1">
@@ -5114,10 +5319,10 @@
       <c r="D57" s="1">
         <v>3</v>
       </c>
-      <c r="E57" s="4">
+      <c r="E57" s="3">
         <v>3006</v>
       </c>
-      <c r="F57" s="4" t="s">
+      <c r="F57" s="3" t="s">
         <v>131</v>
       </c>
       <c r="G57" s="1" t="s">
@@ -5168,7 +5373,7 @@
       <c r="V57" s="1">
         <v>0</v>
       </c>
-      <c r="W57" s="4">
+      <c r="W57" s="3">
         <v>0</v>
       </c>
       <c r="X57" s="1">
@@ -5188,10 +5393,10 @@
       <c r="D58" s="1">
         <v>3</v>
       </c>
-      <c r="E58" s="4">
+      <c r="E58" s="3">
         <v>3007</v>
       </c>
-      <c r="F58" s="4" t="s">
+      <c r="F58" s="3" t="s">
         <v>133</v>
       </c>
       <c r="G58" s="1" t="s">
@@ -5242,7 +5447,7 @@
       <c r="V58" s="1">
         <v>0</v>
       </c>
-      <c r="W58" s="4">
+      <c r="W58" s="3">
         <v>0</v>
       </c>
       <c r="X58" s="1">
@@ -5262,10 +5467,10 @@
       <c r="D60" s="1">
         <v>3</v>
       </c>
-      <c r="E60" s="4">
+      <c r="E60" s="3">
         <v>3001</v>
       </c>
-      <c r="F60" s="4" t="s">
+      <c r="F60" s="3" t="s">
         <v>120</v>
       </c>
       <c r="G60" s="1" t="s">
@@ -5316,7 +5521,7 @@
       <c r="V60" s="1">
         <v>0</v>
       </c>
-      <c r="W60" s="4">
+      <c r="W60" s="3">
         <v>0</v>
       </c>
       <c r="X60" s="1">
@@ -5342,10 +5547,10 @@
       <c r="D61" s="1">
         <v>3</v>
       </c>
-      <c r="E61" s="4">
+      <c r="E61" s="3">
         <v>3002</v>
       </c>
-      <c r="F61" s="4" t="s">
+      <c r="F61" s="3" t="s">
         <v>123</v>
       </c>
       <c r="G61" s="1" t="s">
@@ -5396,7 +5601,7 @@
       <c r="V61" s="1">
         <v>0</v>
       </c>
-      <c r="W61" s="4">
+      <c r="W61" s="3">
         <v>0</v>
       </c>
       <c r="X61" s="1">
@@ -5428,10 +5633,10 @@
       <c r="D62" s="1">
         <v>3</v>
       </c>
-      <c r="E62" s="4">
+      <c r="E62" s="3">
         <v>3003</v>
       </c>
-      <c r="F62" s="4" t="s">
+      <c r="F62" s="3" t="s">
         <v>124</v>
       </c>
       <c r="G62" s="1" t="s">
@@ -5482,7 +5687,7 @@
       <c r="V62" s="1">
         <v>0</v>
       </c>
-      <c r="W62" s="4">
+      <c r="W62" s="3">
         <v>0</v>
       </c>
       <c r="X62" s="1">
@@ -5494,7 +5699,7 @@
       <c r="AD62" s="1">
         <v>10</v>
       </c>
-      <c r="AE62" s="4">
+      <c r="AE62" s="3">
         <v>999</v>
       </c>
       <c r="AF62" s="1">
@@ -5514,10 +5719,10 @@
       <c r="D63" s="1">
         <v>3</v>
       </c>
-      <c r="E63" s="4">
+      <c r="E63" s="3">
         <v>3005</v>
       </c>
-      <c r="F63" s="4" t="s">
+      <c r="F63" s="3" t="s">
         <v>130</v>
       </c>
       <c r="G63" s="1" t="s">
@@ -5568,7 +5773,7 @@
       <c r="V63" s="1">
         <v>0</v>
       </c>
-      <c r="W63" s="4">
+      <c r="W63" s="3">
         <v>0</v>
       </c>
       <c r="X63" s="1">
@@ -5600,10 +5805,10 @@
       <c r="D65" s="1">
         <v>3</v>
       </c>
-      <c r="E65" s="4">
+      <c r="E65" s="3">
         <v>3002</v>
       </c>
-      <c r="F65" s="4" t="s">
+      <c r="F65" s="3" t="s">
         <v>123</v>
       </c>
       <c r="G65" s="1" t="s">
@@ -5654,7 +5859,7 @@
       <c r="V65" s="1">
         <v>0</v>
       </c>
-      <c r="W65" s="4">
+      <c r="W65" s="3">
         <v>0</v>
       </c>
       <c r="X65" s="1">
@@ -5674,10 +5879,10 @@
       <c r="D66" s="1">
         <v>3</v>
       </c>
-      <c r="E66" s="4">
+      <c r="E66" s="3">
         <v>3003</v>
       </c>
-      <c r="F66" s="4" t="s">
+      <c r="F66" s="3" t="s">
         <v>124</v>
       </c>
       <c r="G66" s="1" t="s">
@@ -5728,7 +5933,7 @@
       <c r="V66" s="1">
         <v>0</v>
       </c>
-      <c r="W66" s="4">
+      <c r="W66" s="3">
         <v>0</v>
       </c>
       <c r="X66" s="1">
@@ -5748,10 +5953,10 @@
       <c r="D67" s="1">
         <v>3</v>
       </c>
-      <c r="E67" s="4">
+      <c r="E67" s="3">
         <v>3004</v>
       </c>
-      <c r="F67" s="4" t="s">
+      <c r="F67" s="3" t="s">
         <v>127</v>
       </c>
       <c r="G67" s="1" t="s">
@@ -5802,7 +6007,7 @@
       <c r="V67" s="1">
         <v>0</v>
       </c>
-      <c r="W67" s="4">
+      <c r="W67" s="3">
         <v>0</v>
       </c>
       <c r="X67" s="1">
@@ -5814,7 +6019,7 @@
       <c r="AD67" s="1">
         <v>10</v>
       </c>
-      <c r="AE67" s="4">
+      <c r="AE67" s="3">
         <v>999</v>
       </c>
       <c r="AF67" s="1">
@@ -5834,10 +6039,10 @@
       <c r="D68" s="1">
         <v>3</v>
       </c>
-      <c r="E68" s="4">
+      <c r="E68" s="3">
         <v>3007</v>
       </c>
-      <c r="F68" s="4" t="s">
+      <c r="F68" s="3" t="s">
         <v>133</v>
       </c>
       <c r="G68" s="1" t="s">
@@ -5888,13 +6093,13 @@
       <c r="V68" s="1">
         <v>0</v>
       </c>
-      <c r="W68" s="4">
+      <c r="W68" s="3">
         <v>0</v>
       </c>
       <c r="X68" s="1">
         <v>0</v>
       </c>
-      <c r="AC68" s="4">
+      <c r="AC68" s="3">
         <v>1001</v>
       </c>
       <c r="AG68" s="1">
@@ -5911,10 +6116,10 @@
       <c r="D70" s="1">
         <v>3</v>
       </c>
-      <c r="E70" s="4">
+      <c r="E70" s="3">
         <v>3002</v>
       </c>
-      <c r="F70" s="4" t="s">
+      <c r="F70" s="3" t="s">
         <v>123</v>
       </c>
       <c r="G70" s="1" t="s">
@@ -5965,7 +6170,7 @@
       <c r="V70" s="1">
         <v>0</v>
       </c>
-      <c r="W70" s="4">
+      <c r="W70" s="3">
         <v>0</v>
       </c>
       <c r="X70" s="1">
@@ -5988,10 +6193,10 @@
       <c r="D71" s="1">
         <v>3</v>
       </c>
-      <c r="E71" s="4">
+      <c r="E71" s="3">
         <v>3003</v>
       </c>
-      <c r="F71" s="4" t="s">
+      <c r="F71" s="3" t="s">
         <v>124</v>
       </c>
       <c r="G71" s="1" t="s">
@@ -6042,7 +6247,7 @@
       <c r="V71" s="1">
         <v>0</v>
       </c>
-      <c r="W71" s="4">
+      <c r="W71" s="3">
         <v>0</v>
       </c>
       <c r="X71" s="1">
@@ -6056,6 +6261,551 @@
       </c>
       <c r="AH71" s="1">
         <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:I5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="C1:AH8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelRow="7"/>
+  <cols>
+    <col min="1" max="6" width="9" style="1"/>
+    <col min="7" max="7" width="12" style="1" customWidth="1"/>
+    <col min="8" max="8" width="36.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.33333333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.375" style="1" customWidth="1"/>
+    <col min="11" max="12" width="8.66666666666667" style="1" customWidth="1"/>
+    <col min="13" max="13" width="6.91666666666667" style="1" customWidth="1"/>
+    <col min="14" max="14" width="7.33333333333333" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.5" style="1" customWidth="1"/>
+    <col min="16" max="17" width="7.75" style="1" customWidth="1"/>
+    <col min="18" max="18" width="7.50833333333333" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="11.25" style="1" customWidth="1"/>
+    <col min="21" max="21" width="10.625" style="1" customWidth="1"/>
+    <col min="22" max="23" width="9.83333333333333" style="1" customWidth="1"/>
+    <col min="24" max="28" width="10.0833333333333" style="1" customWidth="1"/>
+    <col min="29" max="29" width="7.41666666666667" style="1" customWidth="1"/>
+    <col min="30" max="30" width="9.16666666666667" style="1" customWidth="1"/>
+    <col min="31" max="31" width="9.83333333333333" style="1" customWidth="1"/>
+    <col min="32" max="32" width="7.41666666666667" style="1" customWidth="1"/>
+    <col min="33" max="33" width="11" style="1" customWidth="1"/>
+    <col min="34" max="34" width="11.9166666666667" style="1" customWidth="1"/>
+    <col min="35" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:34">
+      <c r="F1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:34">
+      <c r="F2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:34">
+      <c r="C3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:34">
+      <c r="C4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AD4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH4" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:34">
+      <c r="C5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AE5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AF5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AG5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH5" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:34">
+      <c r="C6" s="1">
+        <v>40001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1002</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1">
+        <v>0</v>
+      </c>
+      <c r="S6" s="1">
+        <v>0</v>
+      </c>
+      <c r="T6" s="1">
+        <v>0</v>
+      </c>
+      <c r="U6" s="1">
+        <v>0</v>
+      </c>
+      <c r="V6" s="1">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3">
+        <v>0</v>
+      </c>
+      <c r="X6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:34">
+      <c r="C7" s="1">
+        <v>40002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2002</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1">
+        <v>0</v>
+      </c>
+      <c r="T7" s="1">
+        <v>0</v>
+      </c>
+      <c r="U7" s="1">
+        <v>0</v>
+      </c>
+      <c r="V7" s="1">
+        <v>0</v>
+      </c>
+      <c r="W7" s="3">
+        <v>0</v>
+      </c>
+      <c r="X7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:34">
+      <c r="C8" s="1">
+        <v>40003</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3002</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1">
+        <v>0</v>
+      </c>
+      <c r="P8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>0</v>
+      </c>
+      <c r="R8" s="1">
+        <v>0</v>
+      </c>
+      <c r="S8" s="1">
+        <v>0</v>
+      </c>
+      <c r="T8" s="1">
+        <v>0</v>
+      </c>
+      <c r="U8" s="1">
+        <v>0</v>
+      </c>
+      <c r="V8" s="1">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+      <c r="X8" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/SkillTalentConfig.xlsx
+++ b/Excel/SkillTalentConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="手动配置" sheetId="2" r:id="rId1"/>
@@ -5415,7 +5415,7 @@
         <v>0</v>
       </c>
       <c r="L58" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" s="1">
         <v>0</v>
@@ -5424,7 +5424,7 @@
         <v>0</v>
       </c>
       <c r="O58" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P58" s="1">
         <v>0</v>

--- a/Excel/SkillTalentConfig.xlsx
+++ b/Excel/SkillTalentConfig.xlsx
@@ -5424,7 +5424,7 @@
         <v>0</v>
       </c>
       <c r="O58" s="1">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P58" s="1">
         <v>0</v>
